--- a/docs/file-inventory.xlsx
+++ b/docs/file-inventory.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario de archivos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario de archivos'!$A$1:$F$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File inventory'!$A$1:$F$248</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -64,17 +64,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -492,21 +492,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Categoría</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -516,29 +516,29 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Nombre de archivo</t>
+          <t>File name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Título</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Propósito</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Idioma</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Raíz</t>
+          <t>Root</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -553,24 +553,24 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Instrucciones para Claude (Cowork)</t>
+          <t>Instructions for Claude (Cowork)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>System prompt del proyecto que Cowork lee al inicio: identidad, stack, estructura, convenciones y reglas (incluida la regla de idioma).</t>
+          <t>Project system prompt Cowork reads at startup: identity, stack, structure, conventions, rules (incl. language rule).</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Raíz</t>
+          <t>Root</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -590,19 +590,19 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Presentación del proyecto: identidad, stack técnico, estructura del monorepo y guía de inicio.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Project overview: identity, tech stack, monorepo structure, getting started.</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Config Cowork</t>
+          <t>Cowork config</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -617,24 +617,24 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Memoria persistente de Cowork</t>
+          <t>Cowork persistent memory</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Decisiones tomadas, convenciones aprendidas, estado actual y cosas a evitar, persistente entre sesiones.</t>
+          <t>Decisions made, conventions learned, current status, things to avoid; persists across sessions.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Config editor</t>
+          <t>Editor config</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Extensiones recomendadas (VS Code)</t>
+          <t>Recommended extensions (VS Code)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Lista de extensiones sugeridas para el workspace.</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Inglés</t>
+          <t>Suggested extensions list for the workspace.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Config editor</t>
+          <t>Editor config</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -681,24 +681,24 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Configuración de debug (VS Code)</t>
+          <t>Debug configuration (VS Code)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Perfiles de ejecución/depuración del proyecto.</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Inglés</t>
+          <t>Run/debug profiles for the project.</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Config editor</t>
+          <t>Editor config</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -713,24 +713,24 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Settings del workspace (VS Code)</t>
+          <t>Workspace settings (VS Code)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Ajustes del editor para el proyecto.</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Inglés</t>
+          <t>Editor settings for the project.</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Config editor</t>
+          <t>Editor config</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -745,24 +745,24 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Tasks del workspace (VS Code)</t>
+          <t>Workspace tasks (VS Code)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Tareas automatizadas (build, test, etc.) del editor.</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Inglés</t>
+          <t>Automated editor tasks (build, test, etc.).</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Regla Cursor</t>
+          <t>Cursor rule</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -777,24 +777,24 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Convenciones backend .NET (Cursor)</t>
+          <t>Backend .NET conventions (Cursor)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Regla para archivos C#: Clean Architecture, patrones CQRS/Minimal API, nomenclatura Azure, entidades y regla de idioma.</t>
+          <t>Rule for C# files: Clean Architecture, CQRS/Minimal API patterns, Azure naming, entities, language rule.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Regla Cursor</t>
+          <t>Cursor rule</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -809,56 +809,56 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Convenciones frontend Angular (Cursor)</t>
+          <t>Frontend Angular conventions (Cursor)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Regla para archivos TS/HTML/SCSS: Angular 19 standalone, signals, Tailwind, Cytoscape y regla de idioma.</t>
+          <t>Rule for TS/HTML/SCSS files: Angular 19 standalone, signals, Tailwind, Cytoscape, language rule.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Regla Cursor</t>
+          <t>Cursor rule</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>.cursor/rules/proyecto.mdc</t>
+          <t>.cursor/rules/project.mdc</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>proyecto.mdc</t>
+          <t>project.mdc</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Regla general del proyecto (Cursor)</t>
+          <t>General project rule (Cursor)</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Regla always-apply que replica CLAUDE.md para Cursor: identidad, stack, estructura, releases y reglas obligatorias.</t>
+          <t>Always-apply rule mirroring CLAUDE.md for Cursor: identity, stack, structure, releases, mandatory rules.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Regla Cursor</t>
+          <t>Cursor rule</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -873,17 +873,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Template de work items (Cursor)</t>
+          <t>Work item template (Cursor)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Regla para archivos .md del roadmap: estructura del work item, numeración y regla de idioma (contenido en inglés).</t>
+          <t>Rule for roadmap .md files: work item structure, numbering, English language rule.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Analiza el impacto técnico de un work item y produce un plan de implementación (archivos, decisiones, riesgos).</t>
+          <t>Analyzes the technical impact of a work item and produces an implementation plan (files, decisions, risks).</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Tooling backend: archivos .http, migraciones EF Core, scaffolding CQRS y test data.</t>
+          <t>Backend tooling: .http files, EF Core migrations, CQRS scaffolding, test data.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Verifica la consistencia entre features.md, work items, backlog y docs técnicos.</t>
+          <t>Checks consistency across features.md, work items, backlog, and technical docs.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Crea mockups HTML de las vistas siguiendo las guías de diseño del proyecto.</t>
+          <t>Creates HTML view mockups following the project's design guidelines.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Implementa work items con código production-ready presentando ruta + código (sin tocar archivos directamente).</t>
+          <t>Implements work items with production-ready code, presenting path + code (no direct file edits).</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Skill: developer — referencia [Cowork]</t>
+          <t>Skill: developer — reference [Cowork]</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Estándares de código de apoyo al skill developer: convenciones .NET/Angular, Semantic Kernel, config, nomenclatura e idioma.</t>
+          <t>Code-standards companion to the developer skill: .NET/Angular conventions, Semantic Kernel, config, naming, language.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Estándares y templates de Markdown, diagramas Mermaid y ADRs.</t>
+          <t>Markdown, Mermaid diagram, and ADR standards and templates.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Genera documentación técnica: ADRs, guías de implementación y documentación de API.</t>
+          <t>Generates technical documentation: ADRs, implementation guides, API docs.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Valida y extiende las entidades del dominio legal contra la ontología.</t>
+          <t>Validates and extends legal domain entities against the ontology.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Tooling de IA/RAG: prompt templates YAML, golden sets y plugins de Semantic Kernel.</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>AI/RAG tooling: YAML prompt templates, golden sets, Semantic Kernel plugins.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Tooling de infraestructura: configuración Azure (appsettings, env vars, Key Vault) y GitHub Actions.</t>
+          <t>Infrastructure tooling: Azure config (appsettings, env vars, Key Vault) and GitHub Actions.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Code review contra los estándares del proyecto, con reporte de issues por severidad.</t>
+          <t>Code review against project standards, with an issue report by severity.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Descompone un work item en tasks de implementación concretas con archivos, rutas y pasos.</t>
+          <t>Breaks a work item into concrete implementation tasks with files, paths, and steps.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Genera work items .md siguiendo el template estándar del roadmap.</t>
+          <t>Generates work items following the standard roadmap template.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Analiza el impacto técnico de un work item y produce un plan de implementación (archivos, decisiones, riesgos).</t>
+          <t>Analyzes the technical impact of a work item and produces an implementation plan (files, decisions, risks).</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Tooling backend: archivos .http, migraciones EF Core, scaffolding CQRS y test data.</t>
+          <t>Backend tooling: .http files, EF Core migrations, CQRS scaffolding, test data.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Verifica la consistencia entre features.md, work items, backlog y docs técnicos.</t>
+          <t>Checks consistency across features.md, work items, backlog, and technical docs.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Crea mockups HTML de las vistas siguiendo las guías de diseño del proyecto.</t>
+          <t>Creates HTML view mockups following the project's design guidelines.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Implementa work items con código production-ready presentando ruta + código (sin tocar archivos directamente).</t>
+          <t>Implements work items with production-ready code, presenting path + code (no direct file edits).</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Skill: developer — referencia [Cursor]</t>
+          <t>Skill: developer — reference [Cursor]</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Estándares de código de apoyo al skill developer: convenciones .NET/Angular, Semantic Kernel, config, nomenclatura e idioma.</t>
+          <t>Code-standards companion to the developer skill: .NET/Angular conventions, Semantic Kernel, config, naming, language.</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Estándares y templates de Markdown, diagramas Mermaid y ADRs.</t>
+          <t>Markdown, Mermaid diagram, and ADR standards and templates.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Genera documentación técnica: ADRs, guías de implementación y documentación de API.</t>
+          <t>Generates technical documentation: ADRs, implementation guides, API docs.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Valida y extiende las entidades del dominio legal contra la ontología.</t>
+          <t>Validates and extends legal domain entities against the ontology.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Tooling de IA/RAG: prompt templates YAML, golden sets y plugins de Semantic Kernel.</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>AI/RAG tooling: YAML prompt templates, golden sets, Semantic Kernel plugins.</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Tooling de infraestructura: configuración Azure (appsettings, env vars, Key Vault) y GitHub Actions.</t>
+          <t>Infrastructure tooling: Azure config (appsettings, env vars, Key Vault) and GitHub Actions.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Code review contra los estándares del proyecto, con reporte de issues por severidad.</t>
+          <t>Code review against project standards, with an issue report by severity.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Descompone un work item en tasks de implementación concretas con archivos, rutas y pasos.</t>
+          <t>Breaks a work item into concrete implementation tasks with files, paths, and steps.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Genera work items .md siguiendo el template estándar del roadmap.</t>
+          <t>Generates work items following the standard roadmap template.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1791,27 +1791,27 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>docs/guia-desarrollador.md</t>
+          <t>docs/cowork-setup-tutorial.md</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>guia-desarrollador.md</t>
+          <t>cowork-setup-tutorial.md</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Guía del desarrollador</t>
+          <t>Cowork + Cursor setup tutorial</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Onboarding para un dev nuevo: cómo trabajar desde Cowork o Cursor, anatomía de un work item, skills, flujo completo work item → PR, convenciones y FAQ.</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>How the project AI is configured: CLAUDE.md, memory, the 13 shared skills, Cursor rules, full example workflow.</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1823,59 +1823,59 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>docs/tutorial-cowork-setup.md</t>
+          <t>docs/developer-guide.md</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>tutorial-cowork-setup.md</t>
+          <t>developer-guide.md</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Tutorial de setup Cowork + Cursor</t>
+          <t>Developer Guide</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Cómo está configurado el proyecto para IA: CLAUDE.md, memoria, los 13 skills compartidos, reglas de Cursor y flujo de trabajo completo de ejemplo.</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Onboarding for a new dev: how to work from Cowork or Cursor, work item anatomy, skills, full work item → PR flow, conventions, FAQ.</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Roadmap</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/backlog.md</t>
+          <t>docs/file-inventory.xlsx</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>backlog.md</t>
+          <t>file-inventory.xlsx</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>File inventory (this spreadsheet)</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Lista priorizada de trabajo pendiente del proyecto.</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Inventory of all project files (except mvp) with title, purpose, path, and language.</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1887,27 +1887,27 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/features.md</t>
+          <t>docs/roadmap/backlog.md</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>features.md</t>
+          <t>backlog.md</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Roadmap de features (v2.0)</t>
+          <t>Work item backlog</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Fuente de verdad del roadmap: releases, todas las features (F00-F23, FT01-FT04), endpoints, KPIs y stack.</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Index of the 173 work items grouped by release, with folder tree, links, types, and story points.</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1919,59 +1919,59 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/gap-analysis-mvp-vs-legalkb.md</t>
+          <t>docs/roadmap/features.md</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>gap-analysis-mvp-vs-legalkb.md</t>
+          <t>features.md</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Gap analysis MVP vs. plan</t>
+          <t>Features roadmap (v2.0)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Comparación entre lo que existe en el MVP y lo que falta según el plan objetivo.</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Roadmap source of truth: releases, all features (F00-F23, FT01-FT04), endpoints, KPIs, stack.</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Work item (roadmap)</t>
+          <t>Roadmap</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F00 - Entorno y Estructura de Desarrollo/F00 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/gap-analysis-mvp-vs-plan.md</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>F00 - W01 - Documentacion Integral.md</t>
+          <t>gap-analysis-mvp-vs-plan.md</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>F00 - W01 - Documentacion Integral</t>
+          <t>Gap analysis MVP vs. plan</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F00 (Entorno y Estructura de Desarrollo): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
+          <t>Comparison between what exists in the MVP and what is missing per the target plan.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1983,27 +1983,27 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F00 - Entorno y Estructura de Desarrollo/F00 - W02 - Setup Monorepo y Scaffolding Backend.md</t>
+          <t>docs/roadmap/F00 - Development Environment and Structure/F00 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>F00 - W02 - Setup Monorepo y Scaffolding Backend.md</t>
+          <t>F00 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>F00 - W02 - Setup Monorepo y Scaffolding Backend</t>
+          <t>F00 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>F00 (Entorno y Estructura de Desarrollo) — Setup Monorepo y Scaffolding Backend.</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F00 (Development Environment and Structure): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2015,27 +2015,27 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F00 - Entorno y Estructura de Desarrollo/F00 - W03 - Scaffolding Frontend Angular 19.md</t>
+          <t>docs/roadmap/F00 - Development Environment and Structure/F00 - W02 - Monorepo Setup and Backend Scaffolding.md</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>F00 - W03 - Scaffolding Frontend Angular 19.md</t>
+          <t>F00 - W02 - Monorepo Setup and Backend Scaffolding.md</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>F00 - W03 - Scaffolding Frontend Angular 19</t>
+          <t>F00 - W02 - Monorepo Setup and Backend Scaffolding</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>F00 (Entorno y Estructura de Desarrollo) — Scaffolding Frontend Angular 19.</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F00 (Development Environment and Structure) — Monorepo Setup and Backend Scaffolding.</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F00 - Entorno y Estructura de Desarrollo/F00 - W04 - Configuracion CI GitHub Actions.md</t>
+          <t>docs/roadmap/F00 - Development Environment and Structure/F00 - W03 - Angular 19 Frontend Scaffolding.md</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>F00 - W04 - Configuracion CI GitHub Actions.md</t>
+          <t>F00 - W03 - Angular 19 Frontend Scaffolding.md</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>F00 - W04 - Configuracion CI GitHub Actions</t>
+          <t>F00 - W03 - Angular 19 Frontend Scaffolding</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>F00 (Entorno y Estructura de Desarrollo) — Configuracion CI GitHub Actions.</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F00 (Development Environment and Structure) — Angular 19 Frontend Scaffolding.</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2079,27 +2079,27 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F00 - Entorno y Estructura de Desarrollo/F00 - W05 - Infraestructura Azure con Bicep.md</t>
+          <t>docs/roadmap/F00 - Development Environment and Structure/F00 - W04 - GitHub Actions CI Configuration.md</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>F00 - W05 - Infraestructura Azure con Bicep.md</t>
+          <t>F00 - W04 - GitHub Actions CI Configuration.md</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>F00 - W05 - Infraestructura Azure con Bicep</t>
+          <t>F00 - W04 - GitHub Actions CI Configuration</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>F00 (Entorno y Estructura de Desarrollo) — Infraestructura Azure con Bicep.</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F00 (Development Environment and Structure) — GitHub Actions CI Configuration.</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2111,27 +2111,27 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F00 - Entorno y Estructura de Desarrollo/F00 - W06 - Configuracion CD Pipelines de Deploy.md</t>
+          <t>docs/roadmap/F00 - Development Environment and Structure/F00 - W05 - Azure Infrastructure with Bicep.md</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>F00 - W06 - Configuracion CD Pipelines de Deploy.md</t>
+          <t>F00 - W05 - Azure Infrastructure with Bicep.md</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>F00 - W06 - Configuracion CD Pipelines de Deploy</t>
+          <t>F00 - W05 - Azure Infrastructure with Bicep</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>F00 (Entorno y Estructura de Desarrollo) — Configuracion CD Pipelines de Deploy.</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F00 (Development Environment and Structure) — Azure Infrastructure with Bicep.</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2143,27 +2143,27 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F00 - Entorno y Estructura de Desarrollo/F00 - W07 - Setup Entorno Local y Onboarding Guide.md</t>
+          <t>docs/roadmap/F00 - Development Environment and Structure/F00 - W06 - CD Deployment Pipelines Configuration.md</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>F00 - W07 - Setup Entorno Local y Onboarding Guide.md</t>
+          <t>F00 - W06 - CD Deployment Pipelines Configuration.md</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>F00 - W07 - Setup Entorno Local y Onboarding Guide</t>
+          <t>F00 - W06 - CD Deployment Pipelines Configuration</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>F00 (Entorno y Estructura de Desarrollo) — Setup Entorno Local y Onboarding Guide.</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F00 (Development Environment and Structure) — CD Deployment Pipelines Configuration.</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2175,27 +2175,27 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F00 - Entorno y Estructura de Desarrollo/F00 - W08 - Configuracion Calidad de Codigo.md</t>
+          <t>docs/roadmap/F00 - Development Environment and Structure/F00 - W07 - Local Environment Setup and Onboarding Guide.md</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>F00 - W08 - Configuracion Calidad de Codigo.md</t>
+          <t>F00 - W07 - Local Environment Setup and Onboarding Guide.md</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>F00 - W08 - Configuracion Calidad de Codigo</t>
+          <t>F00 - W07 - Local Environment Setup and Onboarding Guide</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>F00 (Entorno y Estructura de Desarrollo) — Configuracion Calidad de Codigo.</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F00 (Development Environment and Structure) — Local Environment Setup and Onboarding Guide.</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2207,27 +2207,27 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F01 - Autenticacion y Autorizacion/F01 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F00 - Development Environment and Structure/F00 - W08 - Code Quality Configuration.md</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>F01 - W01 - Documentacion Integral.md</t>
+          <t>F00 - W08 - Code Quality Configuration.md</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>F01 - W01 - Documentacion Integral</t>
+          <t>F00 - W08 - Code Quality Configuration</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F01 (Autenticacion y Autorizacion): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F00 (Development Environment and Structure) — Code Quality Configuration.</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2239,27 +2239,27 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F01 - Autenticacion y Autorizacion/F01 - W02 - Backend - Configuracion Entra ID y JWT.md</t>
+          <t>docs/roadmap/F01 - Authentication and Authorization/F01 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>F01 - W02 - Backend - Configuracion Entra ID y JWT.md</t>
+          <t>F01 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>F01 - W02 - Backend - Configuracion Entra ID y JWT</t>
+          <t>F01 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>F01 (Autenticacion y Autorizacion) — Backend: Configuracion Entra ID y JWT.</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F01 (Authentication and Authorization): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2271,27 +2271,27 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F01 - Autenticacion y Autorizacion/F01 - W03 - Backend - Middleware de Autorizacion por Rol.md</t>
+          <t>docs/roadmap/F01 - Authentication and Authorization/F01 - W02 - Backend - Entra ID and JWT Configuration.md</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>F01 - W03 - Backend - Middleware de Autorizacion por Rol.md</t>
+          <t>F01 - W02 - Backend - Entra ID and JWT Configuration.md</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>F01 - W03 - Backend - Middleware de Autorizacion por Rol</t>
+          <t>F01 - W02 - Backend - Entra ID and JWT Configuration</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>F01 (Autenticacion y Autorizacion) — Backend: Middleware de Autorizacion por Rol.</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F01 (Authentication and Authorization) — Backend - Entra ID and JWT Configuration.</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2303,27 +2303,27 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F01 - Autenticacion y Autorizacion/F01 - W04 - Frontend - MSAL Angular Setup y AuthService.md</t>
+          <t>docs/roadmap/F01 - Authentication and Authorization/F01 - W03 - Backend - Role-Based Authorization Middleware.md</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>F01 - W04 - Frontend - MSAL Angular Setup y AuthService.md</t>
+          <t>F01 - W03 - Backend - Role-Based Authorization Middleware.md</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>F01 - W04 - Frontend - MSAL Angular Setup y AuthService</t>
+          <t>F01 - W03 - Backend - Role-Based Authorization Middleware</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>F01 (Autenticacion y Autorizacion) — Frontend: MSAL Angular Setup y AuthService.</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F01 (Authentication and Authorization) — Backend - Role-Based Authorization Middleware.</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2335,27 +2335,27 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F01 - Autenticacion y Autorizacion/F01 - W05 - Frontend - AuthGuard y RoleGuard.md</t>
+          <t>docs/roadmap/F01 - Authentication and Authorization/F01 - W04 - Frontend - MSAL Angular Setup and AuthService.md</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>F01 - W05 - Frontend - AuthGuard y RoleGuard.md</t>
+          <t>F01 - W04 - Frontend - MSAL Angular Setup and AuthService.md</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>F01 - W05 - Frontend - AuthGuard y RoleGuard</t>
+          <t>F01 - W04 - Frontend - MSAL Angular Setup and AuthService</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>F01 (Autenticacion y Autorizacion) — Frontend: AuthGuard y RoleGuard.</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F01 (Authentication and Authorization) — Frontend - MSAL Angular Setup and AuthService.</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2367,27 +2367,27 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F01 - Autenticacion y Autorizacion/F01 - W06 - Frontend - AuthInterceptor y ErrorInterceptor.md</t>
+          <t>docs/roadmap/F01 - Authentication and Authorization/F01 - W05 - Frontend - AuthGuard and RoleGuard.md</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>F01 - W06 - Frontend - AuthInterceptor y ErrorInterceptor.md</t>
+          <t>F01 - W05 - Frontend - AuthGuard and RoleGuard.md</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>F01 - W06 - Frontend - AuthInterceptor y ErrorInterceptor</t>
+          <t>F01 - W05 - Frontend - AuthGuard and RoleGuard</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>F01 (Autenticacion y Autorizacion) — Frontend: AuthInterceptor y ErrorInterceptor.</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F01 (Authentication and Authorization) — Frontend - AuthGuard and RoleGuard.</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2399,27 +2399,27 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F01 - Autenticacion y Autorizacion/F01 - W07 - Testing - Tests de Autenticacion E2E.md</t>
+          <t>docs/roadmap/F01 - Authentication and Authorization/F01 - W06 - Frontend - AuthInterceptor and ErrorInterceptor.md</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>F01 - W07 - Testing - Tests de Autenticacion E2E.md</t>
+          <t>F01 - W06 - Frontend - AuthInterceptor and ErrorInterceptor.md</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>F01 - W07 - Testing - Tests de Autenticacion E2E</t>
+          <t>F01 - W06 - Frontend - AuthInterceptor and ErrorInterceptor</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>F01 (Autenticacion y Autorizacion) — Testing: Tests de Autenticacion E2E.</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F01 (Authentication and Authorization) — Frontend - AuthInterceptor and ErrorInterceptor.</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2431,27 +2431,27 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F02 - Dashboard Principal/F02 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F01 - Authentication and Authorization/F01 - W07 - Testing - E2E Authentication Tests.md</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>F02 - W01 - Documentacion Integral.md</t>
+          <t>F01 - W07 - Testing - E2E Authentication Tests.md</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>F02 - W01 - Documentacion Integral</t>
+          <t>F01 - W07 - Testing - E2E Authentication Tests</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F02 (Dashboard Principal): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F01 (Authentication and Authorization) — Testing - E2E Authentication Tests.</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2463,27 +2463,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F02 - Dashboard Principal/F02 - W02 - Backend - Endpoint Agregador Dashboard.md</t>
+          <t>docs/roadmap/F02 - Main Dashboard/F02 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>F02 - W02 - Backend - Endpoint Agregador Dashboard.md</t>
+          <t>F02 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>F02 - W02 - Backend - Endpoint Agregador Dashboard</t>
+          <t>F02 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>F02 (Dashboard Principal) — Backend: Endpoint Agregador Dashboard.</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F02 (Main Dashboard): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2495,27 +2495,27 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F02 - Dashboard Principal/F02 - W03 - Frontend - Layout Shell Sidebar y Navbar.md</t>
+          <t>docs/roadmap/F02 - Main Dashboard/F02 - W02 - Backend - Dashboard Aggregator Endpoint.md</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>F02 - W03 - Frontend - Layout Shell Sidebar y Navbar.md</t>
+          <t>F02 - W02 - Backend - Dashboard Aggregator Endpoint.md</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>F02 - W03 - Frontend - Layout Shell Sidebar y Navbar</t>
+          <t>F02 - W02 - Backend - Dashboard Aggregator Endpoint</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>F02 (Dashboard Principal) — Frontend: Layout Shell Sidebar y Navbar.</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F02 (Main Dashboard) — Backend - Dashboard Aggregator Endpoint.</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2527,27 +2527,27 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F02 - Dashboard Principal/F02 - W04 - Frontend - Dashboard Component y Widgets.md</t>
+          <t>docs/roadmap/F02 - Main Dashboard/F02 - W03 - Frontend - Shell Layout Sidebar and Navbar.md</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>F02 - W04 - Frontend - Dashboard Component y Widgets.md</t>
+          <t>F02 - W03 - Frontend - Shell Layout Sidebar and Navbar.md</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>F02 - W04 - Frontend - Dashboard Component y Widgets</t>
+          <t>F02 - W03 - Frontend - Shell Layout Sidebar and Navbar</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>F02 (Dashboard Principal) — Frontend: Dashboard Component y Widgets.</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F02 (Main Dashboard) — Frontend - Shell Layout Sidebar and Navbar.</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2559,27 +2559,27 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F02 - Dashboard Principal/F02 - W05 - Frontend - Widget Plazos Proximos.md</t>
+          <t>docs/roadmap/F02 - Main Dashboard/F02 - W04 - Frontend - Dashboard Component and Widgets.md</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>F02 - W05 - Frontend - Widget Plazos Proximos.md</t>
+          <t>F02 - W04 - Frontend - Dashboard Component and Widgets.md</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>F02 - W05 - Frontend - Widget Plazos Proximos</t>
+          <t>F02 - W04 - Frontend - Dashboard Component and Widgets</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>F02 (Dashboard Principal) — Frontend: Widget Plazos Proximos.</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F02 (Main Dashboard) — Frontend - Dashboard Component and Widgets.</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2591,27 +2591,27 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F02 - Dashboard Principal/F02 - W06 - Frontend - Widget Novedades Normativas.md</t>
+          <t>docs/roadmap/F02 - Main Dashboard/F02 - W05 - Frontend - Upcoming Deadlines Widget.md</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>F02 - W06 - Frontend - Widget Novedades Normativas.md</t>
+          <t>F02 - W05 - Frontend - Upcoming Deadlines Widget.md</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>F02 - W06 - Frontend - Widget Novedades Normativas</t>
+          <t>F02 - W05 - Frontend - Upcoming Deadlines Widget</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>F02 (Dashboard Principal) — Frontend: Widget Novedades Normativas.</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F02 (Main Dashboard) — Frontend - Upcoming Deadlines Widget.</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2623,27 +2623,27 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F02 - Dashboard Principal/F02 - W07 - Testing - Tests de Dashboard.md</t>
+          <t>docs/roadmap/F02 - Main Dashboard/F02 - W06 - Frontend - Regulatory Updates Widget.md</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>F02 - W07 - Testing - Tests de Dashboard.md</t>
+          <t>F02 - W06 - Frontend - Regulatory Updates Widget.md</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>F02 - W07 - Testing - Tests de Dashboard</t>
+          <t>F02 - W06 - Frontend - Regulatory Updates Widget</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>F02 (Dashboard Principal) — Testing: Tests de Dashboard.</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F02 (Main Dashboard) — Frontend - Regulatory Updates Widget.</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2655,27 +2655,27 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F03 - Busqueda de Normas/F03 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F02 - Main Dashboard/F02 - W07 - Testing - Dashboard Tests.md</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>F03 - W01 - Documentacion Integral.md</t>
+          <t>F02 - W07 - Testing - Dashboard Tests.md</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>F03 - W01 - Documentacion Integral</t>
+          <t>F02 - W07 - Testing - Dashboard Tests</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F03 (Busqueda de Normas): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F02 (Main Dashboard) — Testing - Dashboard Tests.</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2687,27 +2687,27 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F03 - Busqueda de Normas/F03 - W02 - Backend - Indice AI Search para Normas.md</t>
+          <t>docs/roadmap/F03 - Legal Norm Search/F03 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>F03 - W02 - Backend - Indice AI Search para Normas.md</t>
+          <t>F03 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>F03 - W02 - Backend - Indice AI Search para Normas</t>
+          <t>F03 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>F03 (Busqueda de Normas) — Backend: Indice AI Search para Normas.</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F03 (Legal Norm Search): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2719,27 +2719,27 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F03 - Busqueda de Normas/F03 - W03 - Backend - Scoring Profile Hibrido BM25 y Vectores.md</t>
+          <t>docs/roadmap/F03 - Legal Norm Search/F03 - W02 - Backend - AI Search Index for Legal Norms.md</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>F03 - W03 - Backend - Scoring Profile Hibrido BM25 y Vectores.md</t>
+          <t>F03 - W02 - Backend - AI Search Index for Legal Norms.md</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>F03 - W03 - Backend - Scoring Profile Hibrido BM25 y Vectores</t>
+          <t>F03 - W02 - Backend - AI Search Index for Legal Norms</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>F03 (Busqueda de Normas) — Backend: Scoring Profile Hibrido BM25 y Vectores.</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F03 (Legal Norm Search) — Backend - AI Search Index for Legal Norms.</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2751,27 +2751,27 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F03 - Busqueda de Normas/F03 - W04 - Backend - Endpoint POST Buscar Normas.md</t>
+          <t>docs/roadmap/F03 - Legal Norm Search/F03 - W03 - Backend - Hybrid BM25 and Vector Scoring Profile.md</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>F03 - W04 - Backend - Endpoint POST Buscar Normas.md</t>
+          <t>F03 - W03 - Backend - Hybrid BM25 and Vector Scoring Profile.md</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>F03 - W04 - Backend - Endpoint POST Buscar Normas</t>
+          <t>F03 - W03 - Backend - Hybrid BM25 and Vector Scoring Profile</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>F03 (Busqueda de Normas) — Backend: Endpoint POST Buscar Normas.</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F03 (Legal Norm Search) — Backend - Hybrid BM25 and Vector Scoring Profile.</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2783,27 +2783,27 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F03 - Busqueda de Normas/F03 - W05 - Frontend - SearchBar con Autocompletado.md</t>
+          <t>docs/roadmap/F03 - Legal Norm Search/F03 - W04 - Backend - POST Search Legal Norms Endpoint.md</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>F03 - W05 - Frontend - SearchBar con Autocompletado.md</t>
+          <t>F03 - W04 - Backend - POST Search Legal Norms Endpoint.md</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>F03 - W05 - Frontend - SearchBar con Autocompletado</t>
+          <t>F03 - W04 - Backend - POST Search Legal Norms Endpoint</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>F03 (Busqueda de Normas) — Frontend: SearchBar con Autocompletado.</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F03 (Legal Norm Search) — Backend - POST Search Legal Norms Endpoint.</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2815,27 +2815,27 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F03 - Busqueda de Normas/F03 - W06 - Frontend - Filtros Laterales con Facets.md</t>
+          <t>docs/roadmap/F03 - Legal Norm Search/F03 - W05 - Frontend - SearchBar with Autocomplete.md</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>F03 - W06 - Frontend - Filtros Laterales con Facets.md</t>
+          <t>F03 - W05 - Frontend - SearchBar with Autocomplete.md</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>F03 - W06 - Frontend - Filtros Laterales con Facets</t>
+          <t>F03 - W05 - Frontend - SearchBar with Autocomplete</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>F03 (Busqueda de Normas) — Frontend: Filtros Laterales con Facets.</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F03 (Legal Norm Search) — Frontend - SearchBar with Autocomplete.</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2847,27 +2847,27 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F03 - Busqueda de Normas/F03 - W07 - Frontend - Lista de Resultados con Highlight.md</t>
+          <t>docs/roadmap/F03 - Legal Norm Search/F03 - W06 - Frontend - Sidebar Filters with Facets.md</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>F03 - W07 - Frontend - Lista de Resultados con Highlight.md</t>
+          <t>F03 - W06 - Frontend - Sidebar Filters with Facets.md</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>F03 - W07 - Frontend - Lista de Resultados con Highlight</t>
+          <t>F03 - W06 - Frontend - Sidebar Filters with Facets</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>F03 (Busqueda de Normas) — Frontend: Lista de Resultados con Highlight.</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F03 (Legal Norm Search) — Frontend - Sidebar Filters with Facets.</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2879,27 +2879,27 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F03 - Busqueda de Normas/F03 - W08 - Testing - Tests de Busqueda de Normas.md</t>
+          <t>docs/roadmap/F03 - Legal Norm Search/F03 - W07 - Frontend - Results List with Highlight.md</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>F03 - W08 - Testing - Tests de Busqueda de Normas.md</t>
+          <t>F03 - W07 - Frontend - Results List with Highlight.md</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>F03 - W08 - Testing - Tests de Busqueda de Normas</t>
+          <t>F03 - W07 - Frontend - Results List with Highlight</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>F03 (Busqueda de Normas) — Testing: Tests de Busqueda de Normas.</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F03 (Legal Norm Search) — Frontend - Results List with Highlight.</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2911,27 +2911,27 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F04 - Busqueda de Jurisprudencia/F04 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F03 - Legal Norm Search/F03 - W08 - Testing - Legal Norm Search Tests.md</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>F04 - W01 - Documentacion Integral.md</t>
+          <t>F03 - W08 - Testing - Legal Norm Search Tests.md</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>F04 - W01 - Documentacion Integral</t>
+          <t>F03 - W08 - Testing - Legal Norm Search Tests</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F04 (Busqueda de Jurisprudencia): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F03 (Legal Norm Search) — Testing - Legal Norm Search Tests.</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2943,27 +2943,27 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F04 - Busqueda de Jurisprudencia/F04 - W02 - Backend - Indice AI Search para Jurisprudencia.md</t>
+          <t>docs/roadmap/F04 - Case Law Search/F04 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>F04 - W02 - Backend - Indice AI Search para Jurisprudencia.md</t>
+          <t>F04 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>F04 - W02 - Backend - Indice AI Search para Jurisprudencia</t>
+          <t>F04 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>F04 (Busqueda de Jurisprudencia) — Backend: Indice AI Search para Jurisprudencia.</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F04 (Case Law Search): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -2975,27 +2975,27 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F04 - Busqueda de Jurisprudencia/F04 - W03 - Backend - Endpoint POST Buscar Jurisprudencia.md</t>
+          <t>docs/roadmap/F04 - Case Law Search/F04 - W02 - Backend - AI Search Index for Case Law.md</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>F04 - W03 - Backend - Endpoint POST Buscar Jurisprudencia.md</t>
+          <t>F04 - W02 - Backend - AI Search Index for Case Law.md</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>F04 - W03 - Backend - Endpoint POST Buscar Jurisprudencia</t>
+          <t>F04 - W02 - Backend - AI Search Index for Case Law</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>F04 (Busqueda de Jurisprudencia) — Backend: Endpoint POST Buscar Jurisprudencia.</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F04 (Case Law Search) — Backend - AI Search Index for Case Law.</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3007,27 +3007,27 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F04 - Busqueda de Jurisprudencia/F04 - W04 - Frontend - Pagina Busqueda Jurisprudencia.md</t>
+          <t>docs/roadmap/F04 - Case Law Search/F04 - W03 - Backend - POST Search Case Law Endpoint.md</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>F04 - W04 - Frontend - Pagina Busqueda Jurisprudencia.md</t>
+          <t>F04 - W03 - Backend - POST Search Case Law Endpoint.md</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>F04 - W04 - Frontend - Pagina Busqueda Jurisprudencia</t>
+          <t>F04 - W03 - Backend - POST Search Case Law Endpoint</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>F04 (Busqueda de Jurisprudencia) — Frontend: Pagina Busqueda Jurisprudencia.</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F04 (Case Law Search) — Backend - POST Search Case Law Endpoint.</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3039,27 +3039,27 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F04 - Busqueda de Jurisprudencia/F04 - W05 - Frontend - Card de Resultado de Fallo.md</t>
+          <t>docs/roadmap/F04 - Case Law Search/F04 - W04 - Frontend - Case Law Search Page.md</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>F04 - W05 - Frontend - Card de Resultado de Fallo.md</t>
+          <t>F04 - W04 - Frontend - Case Law Search Page.md</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>F04 - W05 - Frontend - Card de Resultado de Fallo</t>
+          <t>F04 - W04 - Frontend - Case Law Search Page</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>F04 (Busqueda de Jurisprudencia) — Frontend: Card de Resultado de Fallo.</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F04 (Case Law Search) — Frontend - Case Law Search Page.</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3071,27 +3071,27 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F04 - Busqueda de Jurisprudencia/F04 - W06 - Testing - Tests de Busqueda de Jurisprudencia.md</t>
+          <t>docs/roadmap/F04 - Case Law Search/F04 - W05 - Frontend - Ruling Result Card.md</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>F04 - W06 - Testing - Tests de Busqueda de Jurisprudencia.md</t>
+          <t>F04 - W05 - Frontend - Ruling Result Card.md</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>F04 - W06 - Testing - Tests de Busqueda de Jurisprudencia</t>
+          <t>F04 - W05 - Frontend - Ruling Result Card</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>F04 (Busqueda de Jurisprudencia) — Testing: Tests de Busqueda de Jurisprudencia.</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F04 (Case Law Search) — Frontend - Ruling Result Card.</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3103,27 +3103,27 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F05 - Detalle de Norma/F05 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F04 - Case Law Search/F04 - W06 - Testing - Case Law Search Tests.md</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>F05 - W01 - Documentacion Integral.md</t>
+          <t>F04 - W06 - Testing - Case Law Search Tests.md</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>F05 - W01 - Documentacion Integral</t>
+          <t>F04 - W06 - Testing - Case Law Search Tests</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F05 (Detalle de Norma): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F04 (Case Law Search) — Testing - Case Law Search Tests.</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3135,27 +3135,27 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F05 - Detalle de Norma/F05 - W02 - Backend - Endpoint GET Norma Detalle.md</t>
+          <t>docs/roadmap/F05 - Legal Norm Detail/F05 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>F05 - W02 - Backend - Endpoint GET Norma Detalle.md</t>
+          <t>F05 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>F05 - W02 - Backend - Endpoint GET Norma Detalle</t>
+          <t>F05 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>F05 (Detalle de Norma) — Backend: Endpoint GET Norma Detalle.</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F05 (Legal Norm Detail): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3167,27 +3167,27 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F05 - Detalle de Norma/F05 - W03 - Backend - Endpoint GET Norma Grafo SQL Graph.md</t>
+          <t>docs/roadmap/F05 - Legal Norm Detail/F05 - W02 - Backend - GET Legal Norm Detail Endpoint.md</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>F05 - W03 - Backend - Endpoint GET Norma Grafo SQL Graph.md</t>
+          <t>F05 - W02 - Backend - GET Legal Norm Detail Endpoint.md</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>F05 - W03 - Backend - Endpoint GET Norma Grafo SQL Graph</t>
+          <t>F05 - W02 - Backend - GET Legal Norm Detail Endpoint</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>F05 (Detalle de Norma) — Backend: Endpoint GET Norma Grafo SQL Graph.</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F05 (Legal Norm Detail) — Backend - GET Legal Norm Detail Endpoint.</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3199,27 +3199,27 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F05 - Detalle de Norma/F05 - W04 - Backend - Endpoint GET Norma Articulos Paginado.md</t>
+          <t>docs/roadmap/F05 - Legal Norm Detail/F05 - W03 - Backend - GET Legal Norm Graph SQL Graph Endpoint.md</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>F05 - W04 - Backend - Endpoint GET Norma Articulos Paginado.md</t>
+          <t>F05 - W03 - Backend - GET Legal Norm Graph SQL Graph Endpoint.md</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>F05 - W04 - Backend - Endpoint GET Norma Articulos Paginado</t>
+          <t>F05 - W03 - Backend - GET Legal Norm Graph SQL Graph Endpoint</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>F05 (Detalle de Norma) — Backend: Endpoint GET Norma Articulos Paginado.</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F05 (Legal Norm Detail) — Backend - GET Legal Norm Graph SQL Graph Endpoint.</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3231,27 +3231,27 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F05 - Detalle de Norma/F05 - W05 - Frontend - Pagina Detalle de Norma con Tabs.md</t>
+          <t>docs/roadmap/F05 - Legal Norm Detail/F05 - W04 - Backend - GET Legal Norm Articles Paged Endpoint.md</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>F05 - W05 - Frontend - Pagina Detalle de Norma con Tabs.md</t>
+          <t>F05 - W04 - Backend - GET Legal Norm Articles Paged Endpoint.md</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>F05 - W05 - Frontend - Pagina Detalle de Norma con Tabs</t>
+          <t>F05 - W04 - Backend - GET Legal Norm Articles Paged Endpoint</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>F05 (Detalle de Norma) — Frontend: Pagina Detalle de Norma con Tabs.</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F05 (Legal Norm Detail) — Backend - GET Legal Norm Articles Paged Endpoint.</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3263,27 +3263,27 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F05 - Detalle de Norma/F05 - W06 - Frontend - Visualizacion Grafo de Relaciones.md</t>
+          <t>docs/roadmap/F05 - Legal Norm Detail/F05 - W05 - Frontend - Legal Norm Detail Page with Tabs.md</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>F05 - W06 - Frontend - Visualizacion Grafo de Relaciones.md</t>
+          <t>F05 - W05 - Frontend - Legal Norm Detail Page with Tabs.md</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>F05 - W06 - Frontend - Visualizacion Grafo de Relaciones</t>
+          <t>F05 - W05 - Frontend - Legal Norm Detail Page with Tabs</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>F05 (Detalle de Norma) — Frontend: Visualizacion Grafo de Relaciones.</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F05 (Legal Norm Detail) — Frontend - Legal Norm Detail Page with Tabs.</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3295,27 +3295,27 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F05 - Detalle de Norma/F05 - W07 - Frontend - Timeline de Modificaciones.md</t>
+          <t>docs/roadmap/F05 - Legal Norm Detail/F05 - W06 - Frontend - Relationship Graph Visualization.md</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>F05 - W07 - Frontend - Timeline de Modificaciones.md</t>
+          <t>F05 - W06 - Frontend - Relationship Graph Visualization.md</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>F05 - W07 - Frontend - Timeline de Modificaciones</t>
+          <t>F05 - W06 - Frontend - Relationship Graph Visualization</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>F05 (Detalle de Norma) — Frontend: Timeline de Modificaciones.</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F05 (Legal Norm Detail) — Frontend - Relationship Graph Visualization.</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3327,27 +3327,27 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F05 - Detalle de Norma/F05 - W08 - Testing - Tests de Detalle de Norma.md</t>
+          <t>docs/roadmap/F05 - Legal Norm Detail/F05 - W07 - Frontend - Amendments Timeline.md</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>F05 - W08 - Testing - Tests de Detalle de Norma.md</t>
+          <t>F05 - W07 - Frontend - Amendments Timeline.md</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>F05 - W08 - Testing - Tests de Detalle de Norma</t>
+          <t>F05 - W07 - Frontend - Amendments Timeline</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>F05 (Detalle de Norma) — Testing: Tests de Detalle de Norma.</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F05 (Legal Norm Detail) — Frontend - Amendments Timeline.</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F06 - Detalle de Articulo/F06 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F05 - Legal Norm Detail/F05 - W08 - Testing - Legal Norm Detail Tests.md</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>F06 - W01 - Documentacion Integral.md</t>
+          <t>F05 - W08 - Testing - Legal Norm Detail Tests.md</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>F06 - W01 - Documentacion Integral</t>
+          <t>F05 - W08 - Testing - Legal Norm Detail Tests</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F06 (Detalle de Articulo): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F05 (Legal Norm Detail) — Testing - Legal Norm Detail Tests.</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3391,27 +3391,27 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F06 - Detalle de Articulo/F06 - W02 - Backend - Endpoint GET Articulo y Jurisprudencia Relacionada.md</t>
+          <t>docs/roadmap/F06 - Article Detail/F06 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>F06 - W02 - Backend - Endpoint GET Articulo y Jurisprudencia Relacionada.md</t>
+          <t>F06 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>F06 - W02 - Backend - Endpoint GET Articulo y Jurisprudencia Relacionada</t>
+          <t>F06 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>F06 (Detalle de Articulo) — Backend: Endpoint GET Articulo y Jurisprudencia Relacionada.</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F06 (Article Detail): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3423,27 +3423,27 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F06 - Detalle de Articulo/F06 - W03 - Frontend - Pagina Detalle de Articulo.md</t>
+          <t>docs/roadmap/F06 - Article Detail/F06 - W02 - Backend - GET Article and Related Case Law Endpoint.md</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>F06 - W03 - Frontend - Pagina Detalle de Articulo.md</t>
+          <t>F06 - W02 - Backend - GET Article and Related Case Law Endpoint.md</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>F06 - W03 - Frontend - Pagina Detalle de Articulo</t>
+          <t>F06 - W02 - Backend - GET Article and Related Case Law Endpoint</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>F06 (Detalle de Articulo) — Frontend: Pagina Detalle de Articulo.</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F06 (Article Detail) — Backend - GET Article and Related Case Law Endpoint.</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3455,27 +3455,27 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F06 - Detalle de Articulo/F06 - W04 - Frontend - Panel Jurisprudencia Relacionada.md</t>
+          <t>docs/roadmap/F06 - Article Detail/F06 - W03 - Frontend - Article Detail Page.md</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>F06 - W04 - Frontend - Panel Jurisprudencia Relacionada.md</t>
+          <t>F06 - W03 - Frontend - Article Detail Page.md</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>F06 - W04 - Frontend - Panel Jurisprudencia Relacionada</t>
+          <t>F06 - W03 - Frontend - Article Detail Page</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>F06 (Detalle de Articulo) — Frontend: Panel Jurisprudencia Relacionada.</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F06 (Article Detail) — Frontend - Article Detail Page.</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3487,27 +3487,27 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F06 - Detalle de Articulo/F06 - W05 - Testing - Tests de Detalle de Articulo.md</t>
+          <t>docs/roadmap/F06 - Article Detail/F06 - W04 - Frontend - Related Case Law Panel.md</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>F06 - W05 - Testing - Tests de Detalle de Articulo.md</t>
+          <t>F06 - W04 - Frontend - Related Case Law Panel.md</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>F06 - W05 - Testing - Tests de Detalle de Articulo</t>
+          <t>F06 - W04 - Frontend - Related Case Law Panel</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>F06 (Detalle de Articulo) — Testing: Tests de Detalle de Articulo.</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F06 (Article Detail) — Frontend - Related Case Law Panel.</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3519,27 +3519,27 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F07 - Novedades Normativas/F07 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F06 - Article Detail/F06 - W05 - Testing - Article Detail Tests.md</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>F07 - W01 - Documentacion Integral.md</t>
+          <t>F06 - W05 - Testing - Article Detail Tests.md</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>F07 - W01 - Documentacion Integral</t>
+          <t>F06 - W05 - Testing - Article Detail Tests</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F07 (Novedades Normativas): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F06 (Article Detail) — Testing - Article Detail Tests.</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3551,27 +3551,27 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F07 - Novedades Normativas/F07 - W02 - Backend - Azure Function Timer Trigger Boletin Oficial.md</t>
+          <t>docs/roadmap/F07 - Regulatory Updates/F07 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>F07 - W02 - Backend - Azure Function Timer Trigger Boletin Oficial.md</t>
+          <t>F07 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>F07 - W02 - Backend - Azure Function Timer Trigger Boletin Oficial</t>
+          <t>F07 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>F07 (Novedades Normativas) — Backend: Azure Function Timer Trigger Boletin Oficial.</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F07 (Regulatory Updates): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3583,27 +3583,27 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F07 - Novedades Normativas/F07 - W03 - Backend - Endpoint GET Novedades y SignalR Push.md</t>
+          <t>docs/roadmap/F07 - Regulatory Updates/F07 - W02 - Backend - Azure Function Timer Trigger Official Gazette.md</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>F07 - W03 - Backend - Endpoint GET Novedades y SignalR Push.md</t>
+          <t>F07 - W02 - Backend - Azure Function Timer Trigger Official Gazette.md</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>F07 - W03 - Backend - Endpoint GET Novedades y SignalR Push</t>
+          <t>F07 - W02 - Backend - Azure Function Timer Trigger Official Gazette</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>F07 (Novedades Normativas) — Backend: Endpoint GET Novedades y SignalR Push.</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F07 (Regulatory Updates) — Backend - Azure Function Timer Trigger Official Gazette.</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3615,27 +3615,27 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F07 - Novedades Normativas/F07 - W04 - Frontend - Pagina Feed de Novedades.md</t>
+          <t>docs/roadmap/F07 - Regulatory Updates/F07 - W03 - Backend - GET Updates and SignalR Push Endpoint.md</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>F07 - W04 - Frontend - Pagina Feed de Novedades.md</t>
+          <t>F07 - W03 - Backend - GET Updates and SignalR Push Endpoint.md</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>F07 - W04 - Frontend - Pagina Feed de Novedades</t>
+          <t>F07 - W03 - Backend - GET Updates and SignalR Push Endpoint</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>F07 (Novedades Normativas) — Frontend: Pagina Feed de Novedades.</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F07 (Regulatory Updates) — Backend - GET Updates and SignalR Push Endpoint.</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3647,27 +3647,27 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F07 - Novedades Normativas/F07 - W05 - Frontend - Suscripcion a Alertas por Rama.md</t>
+          <t>docs/roadmap/F07 - Regulatory Updates/F07 - W04 - Frontend - Updates Feed Page.md</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>F07 - W05 - Frontend - Suscripcion a Alertas por Rama.md</t>
+          <t>F07 - W04 - Frontend - Updates Feed Page.md</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>F07 - W05 - Frontend - Suscripcion a Alertas por Rama</t>
+          <t>F07 - W04 - Frontend - Updates Feed Page</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>F07 (Novedades Normativas) — Frontend: Suscripcion a Alertas por Rama.</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F07 (Regulatory Updates) — Frontend - Updates Feed Page.</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3679,27 +3679,27 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F07 - Novedades Normativas/F07 - W06 - Testing - Tests de Novedades.md</t>
+          <t>docs/roadmap/F07 - Regulatory Updates/F07 - W05 - Frontend - Alert Subscription by Law Branch.md</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>F07 - W06 - Testing - Tests de Novedades.md</t>
+          <t>F07 - W05 - Frontend - Alert Subscription by Law Branch.md</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>F07 - W06 - Testing - Tests de Novedades</t>
+          <t>F07 - W05 - Frontend - Alert Subscription by Law Branch</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>F07 (Novedades Normativas) — Testing: Tests de Novedades.</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F07 (Regulatory Updates) — Frontend - Alert Subscription by Law Branch.</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3711,27 +3711,27 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F07 - Regulatory Updates/F07 - W06 - Testing - Updates Tests.md</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>F08 - W01 - Documentacion Integral.md</t>
+          <t>F07 - W06 - Testing - Updates Tests.md</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>F08 - W01 - Documentacion Integral</t>
+          <t>F07 - W06 - Testing - Updates Tests</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F08 (Chat con Agentes IA): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F07 (Regulatory Updates) — Testing - Updates Tests.</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3743,27 +3743,27 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W02 - Backend - Semantic Kernel Setup y Orquestador.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>F08 - W02 - Backend - Semantic Kernel Setup y Orquestador.md</t>
+          <t>F08 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>F08 - W02 - Backend - Semantic Kernel Setup y Orquestador</t>
+          <t>F08 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>F08 (Chat con Agentes IA) — Backend: Semantic Kernel Setup y Orquestador.</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F08 (AI Agent Chat): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3775,27 +3775,27 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W03 - Backend - Endpoint POST Chat con SignalR Streaming.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W02 - Backend - Semantic Kernel Setup and Orchestrator.md</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>F08 - W03 - Backend - Endpoint POST Chat con SignalR Streaming.md</t>
+          <t>F08 - W02 - Backend - Semantic Kernel Setup and Orchestrator.md</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>F08 - W03 - Backend - Endpoint POST Chat con SignalR Streaming</t>
+          <t>F08 - W02 - Backend - Semantic Kernel Setup and Orchestrator</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>F08 (Chat con Agentes IA) — Backend: Endpoint POST Chat con SignalR Streaming.</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F08 (AI Agent Chat) — Backend - Semantic Kernel Setup and Orchestrator.</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3807,27 +3807,27 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W04 - Backend - Persistencia de Conversaciones.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W03 - Backend - POST Chat with SignalR Streaming Endpoint.md</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>F08 - W04 - Backend - Persistencia de Conversaciones.md</t>
+          <t>F08 - W03 - Backend - POST Chat with SignalR Streaming Endpoint.md</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>F08 - W04 - Backend - Persistencia de Conversaciones</t>
+          <t>F08 - W03 - Backend - POST Chat with SignalR Streaming Endpoint</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>F08 (Chat con Agentes IA) — Backend: Persistencia de Conversaciones.</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F08 (AI Agent Chat) — Backend - POST Chat with SignalR Streaming Endpoint.</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3839,27 +3839,27 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W05 - Frontend - Chat UI con Markdown Rendering.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W04 - Backend - Conversation Persistence.md</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>F08 - W05 - Frontend - Chat UI con Markdown Rendering.md</t>
+          <t>F08 - W04 - Backend - Conversation Persistence.md</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>F08 - W05 - Frontend - Chat UI con Markdown Rendering</t>
+          <t>F08 - W04 - Backend - Conversation Persistence</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>F08 (Chat con Agentes IA) — Frontend: Chat UI con Markdown Rendering.</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F08 (AI Agent Chat) — Backend - Conversation Persistence.</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3871,27 +3871,27 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W06 - Frontend - SignalR Client para Streaming.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W05 - Frontend - Chat UI with Markdown Rendering.md</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>F08 - W06 - Frontend - SignalR Client para Streaming.md</t>
+          <t>F08 - W05 - Frontend - Chat UI with Markdown Rendering.md</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>F08 - W06 - Frontend - SignalR Client para Streaming</t>
+          <t>F08 - W05 - Frontend - Chat UI with Markdown Rendering</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>F08 (Chat con Agentes IA) — Frontend: SignalR Client para Streaming.</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F08 (AI Agent Chat) — Frontend - Chat UI with Markdown Rendering.</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3903,27 +3903,27 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W07 - Frontend - Panel de Fuentes Citadas.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W06 - Frontend - SignalR Client for Streaming.md</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>F08 - W07 - Frontend - Panel de Fuentes Citadas.md</t>
+          <t>F08 - W06 - Frontend - SignalR Client for Streaming.md</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>F08 - W07 - Frontend - Panel de Fuentes Citadas</t>
+          <t>F08 - W06 - Frontend - SignalR Client for Streaming</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>F08 (Chat con Agentes IA) — Frontend: Panel de Fuentes Citadas.</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F08 (AI Agent Chat) — Frontend - SignalR Client for Streaming.</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3935,27 +3935,27 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W08 - Frontend - Historial de Conversaciones.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W07 - Frontend - Cited Sources Panel.md</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>F08 - W08 - Frontend - Historial de Conversaciones.md</t>
+          <t>F08 - W07 - Frontend - Cited Sources Panel.md</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>F08 - W08 - Frontend - Historial de Conversaciones</t>
+          <t>F08 - W07 - Frontend - Cited Sources Panel</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>F08 (Chat con Agentes IA) — Frontend: Historial de Conversaciones.</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F08 (AI Agent Chat) — Frontend - Cited Sources Panel.</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3967,27 +3967,27 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F08 - Chat con Agentes IA/F08 - W09 - Testing - Tests de Chat E2E.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W08 - Frontend - Conversation History.md</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>F08 - W09 - Testing - Tests de Chat E2E.md</t>
+          <t>F08 - W08 - Frontend - Conversation History.md</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>F08 - W09 - Testing - Tests de Chat E2E</t>
+          <t>F08 - W08 - Frontend - Conversation History</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>F08 (Chat con Agentes IA) — Testing: Tests de Chat E2E.</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F08 (AI Agent Chat) — Frontend - Conversation History.</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -3999,27 +3999,27 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F09 - Agente Normativo/F09 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F08 - AI Agent Chat/F08 - W09 - Testing - E2E Chat Tests.md</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>F09 - W01 - Documentacion Integral.md</t>
+          <t>F08 - W09 - Testing - E2E Chat Tests.md</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>F09 - W01 - Documentacion Integral</t>
+          <t>F08 - W09 - Testing - E2E Chat Tests</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F09 (Agente Normativo): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F08 (AI Agent Chat) — Testing - E2E Chat Tests.</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4031,27 +4031,27 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F09 - Agente Normativo/F09 - W02 - Backend - Plugin AgenteNormativo Functions.md</t>
+          <t>docs/roadmap/F09 - Regulatory Agent/F09 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>F09 - W02 - Backend - Plugin AgenteNormativo Functions.md</t>
+          <t>F09 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>F09 - W02 - Backend - Plugin AgenteNormativo Functions</t>
+          <t>F09 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>F09 (Agente Normativo) — Backend: Plugin AgenteNormativo Functions.</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F09 (Regulatory Agent): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4063,27 +4063,27 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F09 - Agente Normativo/F09 - W03 - Backend - Prompts Semanticos del Agente.md</t>
+          <t>docs/roadmap/F09 - Regulatory Agent/F09 - W02 - Backend - RegulatoryAgent Plugin Functions.md</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>F09 - W03 - Backend - Prompts Semanticos del Agente.md</t>
+          <t>F09 - W02 - Backend - RegulatoryAgent Plugin Functions.md</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>F09 - W03 - Backend - Prompts Semanticos del Agente</t>
+          <t>F09 - W02 - Backend - RegulatoryAgent Plugin Functions</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>F09 (Agente Normativo) — Backend: Prompts Semanticos del Agente.</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F09 (Regulatory Agent) — Backend - RegulatoryAgent Plugin Functions.</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4095,27 +4095,27 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F09 - Agente Normativo/F09 - W04 - Backend - Integracion con AI Search y SQL Graph.md</t>
+          <t>docs/roadmap/F09 - Regulatory Agent/F09 - W03 - Backend - Agent Semantic Prompts.md</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>F09 - W04 - Backend - Integracion con AI Search y SQL Graph.md</t>
+          <t>F09 - W03 - Backend - Agent Semantic Prompts.md</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>F09 - W04 - Backend - Integracion con AI Search y SQL Graph</t>
+          <t>F09 - W03 - Backend - Agent Semantic Prompts</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>F09 (Agente Normativo) — Backend: Integracion con AI Search y SQL Graph.</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F09 (Regulatory Agent) — Backend - Agent Semantic Prompts.</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4127,27 +4127,27 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F09 - Agente Normativo/F09 - W05 - Testing - Evaluacion con 15 Consultas Tipificadas.md</t>
+          <t>docs/roadmap/F09 - Regulatory Agent/F09 - W04 - Backend - Integration with AI Search and SQL Graph.md</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>F09 - W05 - Testing - Evaluacion con 15 Consultas Tipificadas.md</t>
+          <t>F09 - W04 - Backend - Integration with AI Search and SQL Graph.md</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>F09 - W05 - Testing - Evaluacion con 15 Consultas Tipificadas</t>
+          <t>F09 - W04 - Backend - Integration with AI Search and SQL Graph</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>F09 (Agente Normativo) — Testing: Evaluacion con 15 Consultas Tipificadas.</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F09 (Regulatory Agent) — Backend - Integration with AI Search and SQL Graph.</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4159,27 +4159,27 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F10 - Agente Jurisprudencial/F10 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F09 - Regulatory Agent/F09 - W05 - Testing - Evaluation with 15 Typified Queries.md</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>F10 - W01 - Documentacion Integral.md</t>
+          <t>F09 - W05 - Testing - Evaluation with 15 Typified Queries.md</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>F10 - W01 - Documentacion Integral</t>
+          <t>F09 - W05 - Testing - Evaluation with 15 Typified Queries</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F10 (Agente Jurisprudencial): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F09 (Regulatory Agent) — Testing - Evaluation with 15 Typified Queries.</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4191,27 +4191,27 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F10 - Agente Jurisprudencial/F10 - W02 - Backend - Plugin AgenteJurisprudencial Functions.md</t>
+          <t>docs/roadmap/F10 - Case Law Agent/F10 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>F10 - W02 - Backend - Plugin AgenteJurisprudencial Functions.md</t>
+          <t>F10 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>F10 - W02 - Backend - Plugin AgenteJurisprudencial Functions</t>
+          <t>F10 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>F10 (Agente Jurisprudencial) — Backend: Plugin AgenteJurisprudencial Functions.</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F10 (Case Law Agent): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4223,27 +4223,27 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F10 - Agente Jurisprudencial/F10 - W03 - Backend - RAG Pipeline sobre Jurisprudencia.md</t>
+          <t>docs/roadmap/F10 - Case Law Agent/F10 - W02 - Backend - CaseLawAgent Plugin Functions.md</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>F10 - W03 - Backend - RAG Pipeline sobre Jurisprudencia.md</t>
+          <t>F10 - W02 - Backend - CaseLawAgent Plugin Functions.md</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>F10 - W03 - Backend - RAG Pipeline sobre Jurisprudencia</t>
+          <t>F10 - W02 - Backend - CaseLawAgent Plugin Functions</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>F10 (Agente Jurisprudencial) — Backend: RAG Pipeline sobre Jurisprudencia.</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F10 (Case Law Agent) — Backend - CaseLawAgent Plugin Functions.</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4255,27 +4255,27 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F10 - Agente Jurisprudencial/F10 - W04 - Backend - Graph Traversal Fallo a Articulo.md</t>
+          <t>docs/roadmap/F10 - Case Law Agent/F10 - W03 - Backend - RAG Pipeline over Case Law.md</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>F10 - W04 - Backend - Graph Traversal Fallo a Articulo.md</t>
+          <t>F10 - W03 - Backend - RAG Pipeline over Case Law.md</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>F10 - W04 - Backend - Graph Traversal Fallo a Articulo</t>
+          <t>F10 - W03 - Backend - RAG Pipeline over Case Law</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>F10 (Agente Jurisprudencial) — Backend: Graph Traversal Fallo a Articulo.</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F10 (Case Law Agent) — Backend - RAG Pipeline over Case Law.</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4287,27 +4287,27 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F10 - Agente Jurisprudencial/F10 - W05 - Testing - Evaluacion con 15 Consultas Tipificadas.md</t>
+          <t>docs/roadmap/F10 - Case Law Agent/F10 - W04 - Backend - Graph Traversal Ruling to Article.md</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>F10 - W05 - Testing - Evaluacion con 15 Consultas Tipificadas.md</t>
+          <t>F10 - W04 - Backend - Graph Traversal Ruling to Article.md</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>F10 - W05 - Testing - Evaluacion con 15 Consultas Tipificadas</t>
+          <t>F10 - W04 - Backend - Graph Traversal Ruling to Article</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>F10 (Agente Jurisprudencial) — Testing: Evaluacion con 15 Consultas Tipificadas.</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F10 (Case Law Agent) — Backend - Graph Traversal Ruling to Article.</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4319,27 +4319,27 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F11 - Agente Procesal/F11 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F10 - Case Law Agent/F10 - W05 - Testing - Evaluation with 15 Typified Queries.md</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>F11 - W01 - Documentacion Integral.md</t>
+          <t>F10 - W05 - Testing - Evaluation with 15 Typified Queries.md</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>F11 - W01 - Documentacion Integral</t>
+          <t>F10 - W05 - Testing - Evaluation with 15 Typified Queries</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F11 (Agente Procesal): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F10 (Case Law Agent) — Testing - Evaluation with 15 Typified Queries.</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4351,27 +4351,27 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F11 - Agente Procesal/F11 - W02 - Backend - Plugin AgenteProcesal Functions.md</t>
+          <t>docs/roadmap/F11 - Procedural Agent/F11 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>F11 - W02 - Backend - Plugin AgenteProcesal Functions.md</t>
+          <t>F11 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>F11 - W02 - Backend - Plugin AgenteProcesal Functions</t>
+          <t>F11 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>F11 (Agente Procesal) — Backend: Plugin AgenteProcesal Functions.</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F11 (Procedural Agent): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4383,27 +4383,27 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F11 - Agente Procesal/F11 - W03 - Backend - Motor de Calculo de Dias Habiles.md</t>
+          <t>docs/roadmap/F11 - Procedural Agent/F11 - W02 - Backend - ProceduralAgent Plugin Functions.md</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>F11 - W03 - Backend - Motor de Calculo de Dias Habiles.md</t>
+          <t>F11 - W02 - Backend - ProceduralAgent Plugin Functions.md</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>F11 - W03 - Backend - Motor de Calculo de Dias Habiles</t>
+          <t>F11 - W02 - Backend - ProceduralAgent Plugin Functions</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>F11 (Agente Procesal) — Backend: Motor de Calculo de Dias Habiles.</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F11 (Procedural Agent) — Backend - ProceduralAgent Plugin Functions.</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4415,27 +4415,27 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F11 - Agente Procesal/F11 - W04 - Backend - Calendario de Feriados Nacionales y Judiciales.md</t>
+          <t>docs/roadmap/F11 - Procedural Agent/F11 - W03 - Backend - Business Days Calculation Engine.md</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>F11 - W04 - Backend - Calendario de Feriados Nacionales y Judiciales.md</t>
+          <t>F11 - W03 - Backend - Business Days Calculation Engine.md</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>F11 - W04 - Backend - Calendario de Feriados Nacionales y Judiciales</t>
+          <t>F11 - W03 - Backend - Business Days Calculation Engine</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>F11 (Agente Procesal) — Backend: Calendario de Feriados Nacionales y Judiciales.</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F11 (Procedural Agent) — Backend - Business Days Calculation Engine.</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4447,27 +4447,27 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F11 - Agente Procesal/F11 - W05 - Testing - Evaluacion con 10 Consultas Tipificadas.md</t>
+          <t>docs/roadmap/F11 - Procedural Agent/F11 - W04 - Backend - National and Court Holidays Calendar.md</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>F11 - W05 - Testing - Evaluacion con 10 Consultas Tipificadas.md</t>
+          <t>F11 - W04 - Backend - National and Court Holidays Calendar.md</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>F11 - W05 - Testing - Evaluacion con 10 Consultas Tipificadas</t>
+          <t>F11 - W04 - Backend - National and Court Holidays Calendar</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>F11 (Agente Procesal) — Testing: Evaluacion con 10 Consultas Tipificadas.</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F11 (Procedural Agent) — Backend - National and Court Holidays Calendar.</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4479,27 +4479,27 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F11 - Procedural Agent/F11 - W05 - Testing - Evaluation with 10 Typified Queries.md</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>F12 - W01 - Documentacion Integral.md</t>
+          <t>F11 - W05 - Testing - Evaluation with 10 Typified Queries.md</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>F12 - W01 - Documentacion Integral</t>
+          <t>F11 - W05 - Testing - Evaluation with 10 Typified Queries</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F12 (Gestion de Expedientes): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F11 (Procedural Agent) — Testing - Evaluation with 10 Typified Queries.</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4511,27 +4511,27 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W02 - Backend - Modelo EF Core Expediente y Migraciones.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>F12 - W02 - Backend - Modelo EF Core Expediente y Migraciones.md</t>
+          <t>F12 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>F12 - W02 - Backend - Modelo EF Core Expediente y Migraciones</t>
+          <t>F12 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Backend: Modelo EF Core Expediente y Migraciones.</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F12 (Case File Management): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4543,27 +4543,27 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W03 - Backend - CRUD Endpoints Expedientes.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W02 - Backend - EF Core Case File Model and Migrations.md</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>F12 - W03 - Backend - CRUD Endpoints Expedientes.md</t>
+          <t>F12 - W02 - Backend - EF Core Case File Model and Migrations.md</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>F12 - W03 - Backend - CRUD Endpoints Expedientes</t>
+          <t>F12 - W02 - Backend - EF Core Case File Model and Migrations</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Backend: CRUD Endpoints Expedientes.</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Backend - EF Core Case File Model and Migrations.</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4575,27 +4575,27 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W04 - Backend - Subrecursos Movimientos y Documentos.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W03 - Backend - Case File CRUD Endpoints.md</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>F12 - W04 - Backend - Subrecursos Movimientos y Documentos.md</t>
+          <t>F12 - W03 - Backend - Case File CRUD Endpoints.md</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>F12 - W04 - Backend - Subrecursos Movimientos y Documentos</t>
+          <t>F12 - W03 - Backend - Case File CRUD Endpoints</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Backend: Subrecursos Movimientos y Documentos.</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Backend - Case File CRUD Endpoints.</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4607,27 +4607,27 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W05 - Backend - Upload Documentos a Blob Storage.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W04 - Backend - Movements and Documents Subresources.md</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>F12 - W05 - Backend - Upload Documentos a Blob Storage.md</t>
+          <t>F12 - W04 - Backend - Movements and Documents Subresources.md</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>F12 - W05 - Backend - Upload Documentos a Blob Storage</t>
+          <t>F12 - W04 - Backend - Movements and Documents Subresources</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Backend: Upload Documentos a Blob Storage.</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Backend - Movements and Documents Subresources.</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4639,27 +4639,27 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W06 - Frontend - Lista de Expedientes con DataTable.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W05 - Backend - Upload Documents to Blob Storage.md</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>F12 - W06 - Frontend - Lista de Expedientes con DataTable.md</t>
+          <t>F12 - W05 - Backend - Upload Documents to Blob Storage.md</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>F12 - W06 - Frontend - Lista de Expedientes con DataTable</t>
+          <t>F12 - W05 - Backend - Upload Documents to Blob Storage</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Frontend: Lista de Expedientes con DataTable.</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Backend - Upload Documents to Blob Storage.</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4671,27 +4671,27 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W07 - Frontend - Formulario Alta y Edicion Expediente.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W06 - Frontend - Case File List with DataTable.md</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>F12 - W07 - Frontend - Formulario Alta y Edicion Expediente.md</t>
+          <t>F12 - W06 - Frontend - Case File List with DataTable.md</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>F12 - W07 - Frontend - Formulario Alta y Edicion Expediente</t>
+          <t>F12 - W06 - Frontend - Case File List with DataTable</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Frontend: Formulario Alta y Edicion Expediente.</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Frontend - Case File List with DataTable.</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4703,27 +4703,27 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W08 - Frontend - Detalle Expediente con Tabs.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W07 - Frontend - Case File Create and Edit Form.md</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>F12 - W08 - Frontend - Detalle Expediente con Tabs.md</t>
+          <t>F12 - W07 - Frontend - Case File Create and Edit Form.md</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>F12 - W08 - Frontend - Detalle Expediente con Tabs</t>
+          <t>F12 - W07 - Frontend - Case File Create and Edit Form</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Frontend: Detalle Expediente con Tabs.</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Frontend - Case File Create and Edit Form.</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4735,27 +4735,27 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W09 - Frontend - Timeline de Movimientos.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W08 - Frontend - Case File Detail with Tabs.md</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>F12 - W09 - Frontend - Timeline de Movimientos.md</t>
+          <t>F12 - W08 - Frontend - Case File Detail with Tabs.md</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>F12 - W09 - Frontend - Timeline de Movimientos</t>
+          <t>F12 - W08 - Frontend - Case File Detail with Tabs</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Frontend: Timeline de Movimientos.</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Frontend - Case File Detail with Tabs.</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4767,27 +4767,27 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W10 - Frontend - Gestion de Documentos Adjuntos.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W09 - Frontend - Movements Timeline.md</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>F12 - W10 - Frontend - Gestion de Documentos Adjuntos.md</t>
+          <t>F12 - W09 - Frontend - Movements Timeline.md</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>F12 - W10 - Frontend - Gestion de Documentos Adjuntos</t>
+          <t>F12 - W09 - Frontend - Movements Timeline</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Frontend: Gestion de Documentos Adjuntos.</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Frontend - Movements Timeline.</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4799,27 +4799,27 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F12 - Gestion de Expedientes/F12 - W11 - Testing - Tests CRUD Expedientes.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W10 - Frontend - Attached Documents Management.md</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>F12 - W11 - Testing - Tests CRUD Expedientes.md</t>
+          <t>F12 - W10 - Frontend - Attached Documents Management.md</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>F12 - W11 - Testing - Tests CRUD Expedientes</t>
+          <t>F12 - W10 - Frontend - Attached Documents Management</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>F12 (Gestion de Expedientes) — Testing: Tests CRUD Expedientes.</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Frontend - Attached Documents Management.</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4831,27 +4831,27 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F13 - Gestion de Plazos/F13 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F12 - Case File Management/F12 - W11 - Testing - Case File CRUD Tests.md</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>F13 - W01 - Documentacion Integral.md</t>
+          <t>F12 - W11 - Testing - Case File CRUD Tests.md</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>F13 - W01 - Documentacion Integral</t>
+          <t>F12 - W11 - Testing - Case File CRUD Tests</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F13 (Gestion de Plazos): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F12 (Case File Management) — Testing - Case File CRUD Tests.</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4863,27 +4863,27 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F13 - Gestion de Plazos/F13 - W02 - Backend - Modelo EF Core Plazo y Migraciones.md</t>
+          <t>docs/roadmap/F13 - Deadline Management/F13 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>F13 - W02 - Backend - Modelo EF Core Plazo y Migraciones.md</t>
+          <t>F13 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>F13 - W02 - Backend - Modelo EF Core Plazo y Migraciones</t>
+          <t>F13 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>F13 (Gestion de Plazos) — Backend: Modelo EF Core Plazo y Migraciones.</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F13 (Deadline Management): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4895,27 +4895,27 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F13 - Gestion de Plazos/F13 - W03 - Backend - CRUD Endpoints Plazos.md</t>
+          <t>docs/roadmap/F13 - Deadline Management/F13 - W02 - Backend - EF Core Deadline Model and Migrations.md</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>F13 - W03 - Backend - CRUD Endpoints Plazos.md</t>
+          <t>F13 - W02 - Backend - EF Core Deadline Model and Migrations.md</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>F13 - W03 - Backend - CRUD Endpoints Plazos</t>
+          <t>F13 - W02 - Backend - EF Core Deadline Model and Migrations</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>F13 (Gestion de Plazos) — Backend: CRUD Endpoints Plazos.</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F13 (Deadline Management) — Backend - EF Core Deadline Model and Migrations.</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4927,27 +4927,27 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F13 - Gestion de Plazos/F13 - W04 - Backend - Azure Function Evaluacion Diaria de Plazos.md</t>
+          <t>docs/roadmap/F13 - Deadline Management/F13 - W03 - Backend - Deadline CRUD Endpoints.md</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>F13 - W04 - Backend - Azure Function Evaluacion Diaria de Plazos.md</t>
+          <t>F13 - W03 - Backend - Deadline CRUD Endpoints.md</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>F13 - W04 - Backend - Azure Function Evaluacion Diaria de Plazos</t>
+          <t>F13 - W03 - Backend - Deadline CRUD Endpoints</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>F13 (Gestion de Plazos) — Backend: Azure Function Evaluacion Diaria de Plazos.</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F13 (Deadline Management) — Backend - Deadline CRUD Endpoints.</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4959,27 +4959,27 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F13 - Gestion de Plazos/F13 - W05 - Backend - Generacion de Alertas via Storage Queue.md</t>
+          <t>docs/roadmap/F13 - Deadline Management/F13 - W04 - Backend - Azure Function Daily Deadline Evaluation.md</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>F13 - W05 - Backend - Generacion de Alertas via Storage Queue.md</t>
+          <t>F13 - W04 - Backend - Azure Function Daily Deadline Evaluation.md</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>F13 - W05 - Backend - Generacion de Alertas via Storage Queue</t>
+          <t>F13 - W04 - Backend - Azure Function Daily Deadline Evaluation</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>F13 (Gestion de Plazos) — Backend: Generacion de Alertas via Storage Queue.</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F13 (Deadline Management) — Backend - Azure Function Daily Deadline Evaluation.</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -4991,27 +4991,27 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F13 - Gestion de Plazos/F13 - W06 - Frontend - Lista de Plazos con Semaforo Visual.md</t>
+          <t>docs/roadmap/F13 - Deadline Management/F13 - W05 - Backend - Alert Generation via Storage Queue.md</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>F13 - W06 - Frontend - Lista de Plazos con Semaforo Visual.md</t>
+          <t>F13 - W05 - Backend - Alert Generation via Storage Queue.md</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>F13 - W06 - Frontend - Lista de Plazos con Semaforo Visual</t>
+          <t>F13 - W05 - Backend - Alert Generation via Storage Queue</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>F13 (Gestion de Plazos) — Frontend: Lista de Plazos con Semaforo Visual.</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F13 (Deadline Management) — Backend - Alert Generation via Storage Queue.</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5023,27 +5023,27 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F13 - Gestion de Plazos/F13 - W07 - Frontend - Formulario Alta Plazo con Calculo Habiles.md</t>
+          <t>docs/roadmap/F13 - Deadline Management/F13 - W06 - Frontend - Deadline List with Visual Traffic Light.md</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>F13 - W07 - Frontend - Formulario Alta Plazo con Calculo Habiles.md</t>
+          <t>F13 - W06 - Frontend - Deadline List with Visual Traffic Light.md</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>F13 - W07 - Frontend - Formulario Alta Plazo con Calculo Habiles</t>
+          <t>F13 - W06 - Frontend - Deadline List with Visual Traffic Light</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>F13 (Gestion de Plazos) — Frontend: Formulario Alta Plazo con Calculo Habiles.</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F13 (Deadline Management) — Frontend - Deadline List with Visual Traffic Light.</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5055,27 +5055,27 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F13 - Gestion de Plazos/F13 - W08 - Testing - Tests de Plazos y Calculo de Habiles.md</t>
+          <t>docs/roadmap/F13 - Deadline Management/F13 - W07 - Frontend - Deadline Create Form with Business Days Calculation.md</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>F13 - W08 - Testing - Tests de Plazos y Calculo de Habiles.md</t>
+          <t>F13 - W07 - Frontend - Deadline Create Form with Business Days Calculation.md</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>F13 - W08 - Testing - Tests de Plazos y Calculo de Habiles</t>
+          <t>F13 - W07 - Frontend - Deadline Create Form with Business Days Calculation</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>F13 (Gestion de Plazos) — Testing: Tests de Plazos y Calculo de Habiles.</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F13 (Deadline Management) — Frontend - Deadline Create Form with Business Days Calculation.</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5087,27 +5087,27 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F14 - Calendario Legal/F14 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F13 - Deadline Management/F13 - W08 - Testing - Deadline and Business Days Calculation Tests.md</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>F14 - W01 - Documentacion Integral.md</t>
+          <t>F13 - W08 - Testing - Deadline and Business Days Calculation Tests.md</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>F14 - W01 - Documentacion Integral</t>
+          <t>F13 - W08 - Testing - Deadline and Business Days Calculation Tests</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F14 (Calendario Legal): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F13 (Deadline Management) — Testing - Deadline and Business Days Calculation Tests.</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5119,27 +5119,27 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F14 - Calendario Legal/F14 - W02 - Backend - Endpoint GET Calendario Agregado.md</t>
+          <t>docs/roadmap/F14 - Legal Calendar/F14 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>F14 - W02 - Backend - Endpoint GET Calendario Agregado.md</t>
+          <t>F14 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>F14 - W02 - Backend - Endpoint GET Calendario Agregado</t>
+          <t>F14 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>F14 (Calendario Legal) — Backend: Endpoint GET Calendario Agregado.</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F14 (Legal Calendar): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5151,27 +5151,27 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F14 - Calendario Legal/F14 - W03 - Frontend - Integracion FullCalendar Angular.md</t>
+          <t>docs/roadmap/F14 - Legal Calendar/F14 - W02 - Backend - GET Aggregated Calendar Endpoint.md</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>F14 - W03 - Frontend - Integracion FullCalendar Angular.md</t>
+          <t>F14 - W02 - Backend - GET Aggregated Calendar Endpoint.md</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>F14 - W03 - Frontend - Integracion FullCalendar Angular</t>
+          <t>F14 - W02 - Backend - GET Aggregated Calendar Endpoint</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>F14 (Calendario Legal) — Frontend: Integracion FullCalendar Angular.</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F14 (Legal Calendar) — Backend - GET Aggregated Calendar Endpoint.</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5183,27 +5183,27 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F14 - Calendario Legal/F14 - W04 - Frontend - Filtros y Navegacion de Calendario.md</t>
+          <t>docs/roadmap/F14 - Legal Calendar/F14 - W03 - Frontend - FullCalendar Angular Integration.md</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>F14 - W04 - Frontend - Filtros y Navegacion de Calendario.md</t>
+          <t>F14 - W03 - Frontend - FullCalendar Angular Integration.md</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>F14 - W04 - Frontend - Filtros y Navegacion de Calendario</t>
+          <t>F14 - W03 - Frontend - FullCalendar Angular Integration</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>F14 (Calendario Legal) — Frontend: Filtros y Navegacion de Calendario.</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F14 (Legal Calendar) — Frontend - FullCalendar Angular Integration.</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5215,27 +5215,27 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F14 - Calendario Legal/F14 - W05 - Testing - Tests de Calendario.md</t>
+          <t>docs/roadmap/F14 - Legal Calendar/F14 - W04 - Frontend - Calendar Filters and Navigation.md</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>F14 - W05 - Testing - Tests de Calendario.md</t>
+          <t>F14 - W04 - Frontend - Calendar Filters and Navigation.md</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>F14 - W05 - Testing - Tests de Calendario</t>
+          <t>F14 - W04 - Frontend - Calendar Filters and Navigation</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>F14 (Calendario Legal) — Testing: Tests de Calendario.</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F14 (Legal Calendar) — Frontend - Calendar Filters and Navigation.</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5247,27 +5247,27 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F15 - Analisis de Riesgo Legal/F15 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F14 - Legal Calendar/F14 - W05 - Testing - Calendar Tests.md</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>F15 - W01 - Documentacion Integral.md</t>
+          <t>F14 - W05 - Testing - Calendar Tests.md</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>F15 - W01 - Documentacion Integral</t>
+          <t>F14 - W05 - Testing - Calendar Tests</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F15 (Analisis de Riesgo Legal): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F14 (Legal Calendar) — Testing - Calendar Tests.</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F15 - Analisis de Riesgo Legal/F15 - W02 - Backend - Plugin AgenteRiesgo Semantic Kernel.md</t>
+          <t>docs/roadmap/F15 - Legal Risk Analysis/F15 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>F15 - W02 - Backend - Plugin AgenteRiesgo Semantic Kernel.md</t>
+          <t>F15 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>F15 - W02 - Backend - Plugin AgenteRiesgo Semantic Kernel</t>
+          <t>F15 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>F15 (Analisis de Riesgo Legal) — Backend: Plugin AgenteRiesgo Semantic Kernel.</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F15 (Legal Risk Analysis): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5311,27 +5311,27 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F15 - Analisis de Riesgo Legal/F15 - W03 - Backend - Modelo de Taxonomia de Riesgos.md</t>
+          <t>docs/roadmap/F15 - Legal Risk Analysis/F15 - W02 - Backend - RiskAgent Semantic Kernel Plugin.md</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>F15 - W03 - Backend - Modelo de Taxonomia de Riesgos.md</t>
+          <t>F15 - W02 - Backend - RiskAgent Semantic Kernel Plugin.md</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>F15 - W03 - Backend - Modelo de Taxonomia de Riesgos</t>
+          <t>F15 - W02 - Backend - RiskAgent Semantic Kernel Plugin</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>F15 (Analisis de Riesgo Legal) — Backend: Modelo de Taxonomia de Riesgos.</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F15 (Legal Risk Analysis) — Backend - RiskAgent Semantic Kernel Plugin.</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5343,27 +5343,27 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F15 - Analisis de Riesgo Legal/F15 - W04 - Backend - Endpoint POST Analizar Riesgo.md</t>
+          <t>docs/roadmap/F15 - Legal Risk Analysis/F15 - W03 - Backend - Risk Taxonomy Model.md</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>F15 - W04 - Backend - Endpoint POST Analizar Riesgo.md</t>
+          <t>F15 - W03 - Backend - Risk Taxonomy Model.md</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>F15 - W04 - Backend - Endpoint POST Analizar Riesgo</t>
+          <t>F15 - W03 - Backend - Risk Taxonomy Model</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>F15 (Analisis de Riesgo Legal) — Backend: Endpoint POST Analizar Riesgo.</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F15 (Legal Risk Analysis) — Backend - Risk Taxonomy Model.</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5375,27 +5375,27 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F15 - Analisis de Riesgo Legal/F15 - W05 - Backend - Persistencia de Analisis en SQL.md</t>
+          <t>docs/roadmap/F15 - Legal Risk Analysis/F15 - W04 - Backend - POST Analyze Risk Endpoint.md</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>F15 - W05 - Backend - Persistencia de Analisis en SQL.md</t>
+          <t>F15 - W04 - Backend - POST Analyze Risk Endpoint.md</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>F15 - W05 - Backend - Persistencia de Analisis en SQL</t>
+          <t>F15 - W04 - Backend - POST Analyze Risk Endpoint</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>F15 (Analisis de Riesgo Legal) — Backend: Persistencia de Analisis en SQL.</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F15 (Legal Risk Analysis) — Backend - POST Analyze Risk Endpoint.</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5407,27 +5407,27 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F15 - Analisis de Riesgo Legal/F15 - W06 - Frontend - Formulario de Ingreso de Caso.md</t>
+          <t>docs/roadmap/F15 - Legal Risk Analysis/F15 - W05 - Backend - Analysis Persistence in SQL.md</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>F15 - W06 - Frontend - Formulario de Ingreso de Caso.md</t>
+          <t>F15 - W05 - Backend - Analysis Persistence in SQL.md</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>F15 - W06 - Frontend - Formulario de Ingreso de Caso</t>
+          <t>F15 - W05 - Backend - Analysis Persistence in SQL</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>F15 (Analisis de Riesgo Legal) — Frontend: Formulario de Ingreso de Caso.</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F15 (Legal Risk Analysis) — Backend - Analysis Persistence in SQL.</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5439,27 +5439,27 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F15 - Analisis de Riesgo Legal/F15 - W07 - Frontend - Vista de Resultado con Score Visual.md</t>
+          <t>docs/roadmap/F15 - Legal Risk Analysis/F15 - W06 - Frontend - Case Input Form.md</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>F15 - W07 - Frontend - Vista de Resultado con Score Visual.md</t>
+          <t>F15 - W06 - Frontend - Case Input Form.md</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>F15 - W07 - Frontend - Vista de Resultado con Score Visual</t>
+          <t>F15 - W06 - Frontend - Case Input Form</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>F15 (Analisis de Riesgo Legal) — Frontend: Vista de Resultado con Score Visual.</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F15 (Legal Risk Analysis) — Frontend - Case Input Form.</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5471,27 +5471,27 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F15 - Analisis de Riesgo Legal/F15 - W08 - Testing - Evaluacion de Analisis de Riesgo.md</t>
+          <t>docs/roadmap/F15 - Legal Risk Analysis/F15 - W07 - Frontend - Result View with Visual Score.md</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>F15 - W08 - Testing - Evaluacion de Analisis de Riesgo.md</t>
+          <t>F15 - W07 - Frontend - Result View with Visual Score.md</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>F15 - W08 - Testing - Evaluacion de Analisis de Riesgo</t>
+          <t>F15 - W07 - Frontend - Result View with Visual Score</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>F15 (Analisis de Riesgo Legal) — Testing: Evaluacion de Analisis de Riesgo.</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F15 (Legal Risk Analysis) — Frontend - Result View with Visual Score.</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5503,27 +5503,27 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F16 - Historial de Analisis de Riesgo/F16 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F15 - Legal Risk Analysis/F15 - W08 - Testing - Risk Analysis Evaluation.md</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>F16 - W01 - Documentacion Integral.md</t>
+          <t>F15 - W08 - Testing - Risk Analysis Evaluation.md</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>F16 - W01 - Documentacion Integral</t>
+          <t>F15 - W08 - Testing - Risk Analysis Evaluation</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F16 (Historial de Analisis de Riesgo): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F15 (Legal Risk Analysis) — Testing - Risk Analysis Evaluation.</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5535,27 +5535,27 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F16 - Historial de Analisis de Riesgo/F16 - W02 - Backend - Endpoint GET Historial y Re-analisis.md</t>
+          <t>docs/roadmap/F16 - Risk Analysis History/F16 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>F16 - W02 - Backend - Endpoint GET Historial y Re-analisis.md</t>
+          <t>F16 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>F16 - W02 - Backend - Endpoint GET Historial y Re-analisis</t>
+          <t>F16 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>F16 (Historial de Analisis de Riesgo) — Backend: Endpoint GET Historial y Re-analisis.</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F16 (Risk Analysis History): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5567,27 +5567,27 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F16 - Historial de Analisis de Riesgo/F16 - W03 - Frontend - Lista Historial con DataTable.md</t>
+          <t>docs/roadmap/F16 - Risk Analysis History/F16 - W02 - Backend - GET History and Re-analysis Endpoint.md</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>F16 - W03 - Frontend - Lista Historial con DataTable.md</t>
+          <t>F16 - W02 - Backend - GET History and Re-analysis Endpoint.md</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>F16 - W03 - Frontend - Lista Historial con DataTable</t>
+          <t>F16 - W02 - Backend - GET History and Re-analysis Endpoint</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>F16 (Historial de Analisis de Riesgo) — Frontend: Lista Historial con DataTable.</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F16 (Risk Analysis History) — Backend - GET History and Re-analysis Endpoint.</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5599,27 +5599,27 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F16 - Historial de Analisis de Riesgo/F16 - W04 - Frontend - Diff Visual entre Analisis.md</t>
+          <t>docs/roadmap/F16 - Risk Analysis History/F16 - W03 - Frontend - History List with DataTable.md</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>F16 - W04 - Frontend - Diff Visual entre Analisis.md</t>
+          <t>F16 - W03 - Frontend - History List with DataTable.md</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>F16 - W04 - Frontend - Diff Visual entre Analisis</t>
+          <t>F16 - W03 - Frontend - History List with DataTable</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>F16 (Historial de Analisis de Riesgo) — Frontend: Diff Visual entre Analisis.</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F16 (Risk Analysis History) — Frontend - History List with DataTable.</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5631,27 +5631,27 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F16 - Historial de Analisis de Riesgo/F16 - W05 - Testing - Tests de Historial.md</t>
+          <t>docs/roadmap/F16 - Risk Analysis History/F16 - W04 - Frontend - Visual Diff Between Analyses.md</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>F16 - W05 - Testing - Tests de Historial.md</t>
+          <t>F16 - W04 - Frontend - Visual Diff Between Analyses.md</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>F16 - W05 - Testing - Tests de Historial</t>
+          <t>F16 - W04 - Frontend - Visual Diff Between Analyses</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>F16 (Historial de Analisis de Riesgo) — Testing: Tests de Historial.</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F16 (Risk Analysis History) — Frontend - Visual Diff Between Analyses.</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5663,27 +5663,27 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F17 - Generacion de Informes Legales/F17 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F16 - Risk Analysis History/F16 - W05 - Testing - History Tests.md</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>F17 - W01 - Documentacion Integral.md</t>
+          <t>F16 - W05 - Testing - History Tests.md</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>F17 - W01 - Documentacion Integral</t>
+          <t>F16 - W05 - Testing - History Tests</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F17 (Generacion de Informes Legales): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F16 (Risk Analysis History) — Testing - History Tests.</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5695,27 +5695,27 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F17 - Generacion de Informes Legales/F17 - W02 - Backend - Motor de Templates OpenXml.md</t>
+          <t>docs/roadmap/F17 - Legal Report Generation/F17 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>F17 - W02 - Backend - Motor de Templates OpenXml.md</t>
+          <t>F17 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>F17 - W02 - Backend - Motor de Templates OpenXml</t>
+          <t>F17 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>F17 (Generacion de Informes Legales) — Backend: Motor de Templates OpenXml.</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F17 (Legal Report Generation): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5727,27 +5727,27 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F17 - Generacion de Informes Legales/F17 - W03 - Backend - Templates de Informes en Blob Storage.md</t>
+          <t>docs/roadmap/F17 - Legal Report Generation/F17 - W02 - Backend - OpenXml Template Engine.md</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>F17 - W03 - Backend - Templates de Informes en Blob Storage.md</t>
+          <t>F17 - W02 - Backend - OpenXml Template Engine.md</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>F17 - W03 - Backend - Templates de Informes en Blob Storage</t>
+          <t>F17 - W02 - Backend - OpenXml Template Engine</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>F17 (Generacion de Informes Legales) — Backend: Templates de Informes en Blob Storage.</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F17 (Legal Report Generation) — Backend - OpenXml Template Engine.</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5759,27 +5759,27 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F17 - Generacion de Informes Legales/F17 - W04 - Backend - Endpoint POST Generar Informe.md</t>
+          <t>docs/roadmap/F17 - Legal Report Generation/F17 - W03 - Backend - Report Templates in Blob Storage.md</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>F17 - W04 - Backend - Endpoint POST Generar Informe.md</t>
+          <t>F17 - W03 - Backend - Report Templates in Blob Storage.md</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>F17 - W04 - Backend - Endpoint POST Generar Informe</t>
+          <t>F17 - W03 - Backend - Report Templates in Blob Storage</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>F17 (Generacion de Informes Legales) — Backend: Endpoint POST Generar Informe.</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F17 (Legal Report Generation) — Backend - Report Templates in Blob Storage.</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5791,27 +5791,27 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F17 - Generacion de Informes Legales/F17 - W05 - Frontend - Selector de Tipo de Informe.md</t>
+          <t>docs/roadmap/F17 - Legal Report Generation/F17 - W04 - Backend - POST Generate Report Endpoint.md</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>F17 - W05 - Frontend - Selector de Tipo de Informe.md</t>
+          <t>F17 - W04 - Backend - POST Generate Report Endpoint.md</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>F17 - W05 - Frontend - Selector de Tipo de Informe</t>
+          <t>F17 - W04 - Backend - POST Generate Report Endpoint</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>F17 (Generacion de Informes Legales) — Frontend: Selector de Tipo de Informe.</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F17 (Legal Report Generation) — Backend - POST Generate Report Endpoint.</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5823,27 +5823,27 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F17 - Generacion de Informes Legales/F17 - W06 - Frontend - Preview y Descarga de Informe.md</t>
+          <t>docs/roadmap/F17 - Legal Report Generation/F17 - W05 - Frontend - Report Type Selector.md</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>F17 - W06 - Frontend - Preview y Descarga de Informe.md</t>
+          <t>F17 - W05 - Frontend - Report Type Selector.md</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>F17 - W06 - Frontend - Preview y Descarga de Informe</t>
+          <t>F17 - W05 - Frontend - Report Type Selector</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>F17 (Generacion de Informes Legales) — Frontend: Preview y Descarga de Informe.</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F17 (Legal Report Generation) — Frontend - Report Type Selector.</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5855,27 +5855,27 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F17 - Generacion de Informes Legales/F17 - W07 - Testing - Tests de Generacion de Informes.md</t>
+          <t>docs/roadmap/F17 - Legal Report Generation/F17 - W06 - Frontend - Report Preview and Download.md</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>F17 - W07 - Testing - Tests de Generacion de Informes.md</t>
+          <t>F17 - W06 - Frontend - Report Preview and Download.md</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>F17 - W07 - Testing - Tests de Generacion de Informes</t>
+          <t>F17 - W06 - Frontend - Report Preview and Download</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>F17 (Generacion de Informes Legales) — Testing: Tests de Generacion de Informes.</t>
-        </is>
-      </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F17 (Legal Report Generation) — Frontend - Report Preview and Download.</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5887,27 +5887,27 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F18 - Reportes Operativos/F18 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F17 - Legal Report Generation/F17 - W07 - Testing - Report Generation Tests.md</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>F18 - W01 - Documentacion Integral.md</t>
+          <t>F17 - W07 - Testing - Report Generation Tests.md</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>F18 - W01 - Documentacion Integral</t>
+          <t>F17 - W07 - Testing - Report Generation Tests</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F18 (Reportes Operativos): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F169" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F17 (Legal Report Generation) — Testing - Report Generation Tests.</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5919,27 +5919,27 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F18 - Reportes Operativos/F18 - W02 - Backend - Endpoints de Reportes Agregados.md</t>
+          <t>docs/roadmap/F18 - Operational Reports/F18 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>F18 - W02 - Backend - Endpoints de Reportes Agregados.md</t>
+          <t>F18 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>F18 - W02 - Backend - Endpoints de Reportes Agregados</t>
+          <t>F18 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>F18 (Reportes Operativos) — Backend: Endpoints de Reportes Agregados.</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F18 (Operational Reports): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5951,27 +5951,27 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F18 - Reportes Operativos/F18 - W03 - Frontend - Graficos con ngx-charts.md</t>
+          <t>docs/roadmap/F18 - Operational Reports/F18 - W02 - Backend - Aggregated Reports Endpoints.md</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>F18 - W03 - Frontend - Graficos con ngx-charts.md</t>
+          <t>F18 - W02 - Backend - Aggregated Reports Endpoints.md</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>F18 - W03 - Frontend - Graficos con ngx-charts</t>
+          <t>F18 - W02 - Backend - Aggregated Reports Endpoints</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>F18 (Reportes Operativos) — Frontend: Graficos con ngx-charts.</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F18 (Operational Reports) — Backend - Aggregated Reports Endpoints.</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -5983,27 +5983,27 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F18 - Reportes Operativos/F18 - W04 - Frontend - Export a PDF y Excel.md</t>
+          <t>docs/roadmap/F18 - Operational Reports/F18 - W03 - Frontend - Charts with ngx-charts.md</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>F18 - W04 - Frontend - Export a PDF y Excel.md</t>
+          <t>F18 - W03 - Frontend - Charts with ngx-charts.md</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>F18 - W04 - Frontend - Export a PDF y Excel</t>
+          <t>F18 - W03 - Frontend - Charts with ngx-charts</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>F18 (Reportes Operativos) — Frontend: Export a PDF y Excel.</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F18 (Operational Reports) — Frontend - Charts with ngx-charts.</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6015,27 +6015,27 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F18 - Reportes Operativos/F18 - W05 - Testing - Tests de Reportes.md</t>
+          <t>docs/roadmap/F18 - Operational Reports/F18 - W04 - Frontend - Export to PDF and Excel.md</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>F18 - W05 - Testing - Tests de Reportes.md</t>
+          <t>F18 - W04 - Frontend - Export to PDF and Excel.md</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>F18 - W05 - Testing - Tests de Reportes</t>
+          <t>F18 - W04 - Frontend - Export to PDF and Excel</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>F18 (Reportes Operativos) — Testing: Tests de Reportes.</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F18 (Operational Reports) — Frontend - Export to PDF and Excel.</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6047,27 +6047,27 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F19 - Administracion de Usuarios/F19 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F18 - Operational Reports/F18 - W05 - Testing - Reports Tests.md</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>F19 - W01 - Documentacion Integral.md</t>
+          <t>F18 - W05 - Testing - Reports Tests.md</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>F19 - W01 - Documentacion Integral</t>
+          <t>F18 - W05 - Testing - Reports Tests</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F19 (Administracion de Usuarios): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F18 (Operational Reports) — Testing - Reports Tests.</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6079,27 +6079,27 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F19 - Administracion de Usuarios/F19 - W02 - Backend - CRUD Usuarios y Permisos Custom.md</t>
+          <t>docs/roadmap/F19 - User Administration/F19 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>F19 - W02 - Backend - CRUD Usuarios y Permisos Custom.md</t>
+          <t>F19 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>F19 - W02 - Backend - CRUD Usuarios y Permisos Custom</t>
+          <t>F19 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>F19 (Administracion de Usuarios) — Backend: CRUD Usuarios y Permisos Custom.</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F19 (User Administration): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6111,27 +6111,27 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F19 - Administracion de Usuarios/F19 - W03 - Backend - Audit Log en Azure SQL.md</t>
+          <t>docs/roadmap/F19 - User Administration/F19 - W02 - Backend - User CRUD and Custom Permissions.md</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>F19 - W03 - Backend - Audit Log en Azure SQL.md</t>
+          <t>F19 - W02 - Backend - User CRUD and Custom Permissions.md</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>F19 - W03 - Backend - Audit Log en Azure SQL</t>
+          <t>F19 - W02 - Backend - User CRUD and Custom Permissions</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>F19 (Administracion de Usuarios) — Backend: Audit Log en Azure SQL.</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F19 (User Administration) — Backend - User CRUD and Custom Permissions.</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6143,27 +6143,27 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F19 - Administracion de Usuarios/F19 - W04 - Frontend - Pagina Admin Usuarios.md</t>
+          <t>docs/roadmap/F19 - User Administration/F19 - W03 - Backend - Audit Log in Azure SQL.md</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>F19 - W04 - Frontend - Pagina Admin Usuarios.md</t>
+          <t>F19 - W03 - Backend - Audit Log in Azure SQL.md</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>F19 - W04 - Frontend - Pagina Admin Usuarios</t>
+          <t>F19 - W03 - Backend - Audit Log in Azure SQL</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>F19 (Administracion de Usuarios) — Frontend: Pagina Admin Usuarios.</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F19 (User Administration) — Backend - Audit Log in Azure SQL.</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F19 - Administracion de Usuarios/F19 - W05 - Frontend - Log de Auditoria.md</t>
+          <t>docs/roadmap/F19 - User Administration/F19 - W04 - Frontend - User Admin Page.md</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>F19 - W05 - Frontend - Log de Auditoria.md</t>
+          <t>F19 - W04 - Frontend - User Admin Page.md</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>F19 - W05 - Frontend - Log de Auditoria</t>
+          <t>F19 - W04 - Frontend - User Admin Page</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>F19 (Administracion de Usuarios) — Frontend: Log de Auditoria.</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F19 (User Administration) — Frontend - User Admin Page.</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6207,27 +6207,27 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F19 - Administracion de Usuarios/F19 - W06 - Testing - Tests de Admin.md</t>
+          <t>docs/roadmap/F19 - User Administration/F19 - W05 - Frontend - Audit Log.md</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>F19 - W06 - Testing - Tests de Admin.md</t>
+          <t>F19 - W05 - Frontend - Audit Log.md</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>F19 - W06 - Testing - Tests de Admin</t>
+          <t>F19 - W05 - Frontend - Audit Log</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>F19 (Administracion de Usuarios) — Testing: Tests de Admin.</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F19 (User Administration) — Frontend - Audit Log.</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6239,27 +6239,27 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F20 - Configuracion de Alertas Avanzadas/F20 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F19 - User Administration/F19 - W06 - Testing - Admin Tests.md</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>F20 - W01 - Documentacion Integral.md</t>
+          <t>F19 - W06 - Testing - Admin Tests.md</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>F20 - W01 - Documentacion Integral</t>
+          <t>F19 - W06 - Testing - Admin Tests</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F20 (Configuracion de Alertas Avanzadas): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F19 (User Administration) — Testing - Admin Tests.</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6271,27 +6271,27 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F20 - Configuracion de Alertas Avanzadas/F20 - W02 - Backend - CRUD Configuracion de Alertas.md</t>
+          <t>docs/roadmap/F20 - Advanced Alert Configuration/F20 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>F20 - W02 - Backend - CRUD Configuracion de Alertas.md</t>
+          <t>F20 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>F20 - W02 - Backend - CRUD Configuracion de Alertas</t>
+          <t>F20 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>F20 (Configuracion de Alertas Avanzadas) — Backend: CRUD Configuracion de Alertas.</t>
-        </is>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F20 (Advanced Alert Configuration): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6303,27 +6303,27 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F20 - Configuracion de Alertas Avanzadas/F20 - W03 - Backend - Azure Function Evaluacion de Condiciones.md</t>
+          <t>docs/roadmap/F20 - Advanced Alert Configuration/F20 - W02 - Backend - Alert Configuration CRUD.md</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>F20 - W03 - Backend - Azure Function Evaluacion de Condiciones.md</t>
+          <t>F20 - W02 - Backend - Alert Configuration CRUD.md</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>F20 - W03 - Backend - Azure Function Evaluacion de Condiciones</t>
+          <t>F20 - W02 - Backend - Alert Configuration CRUD</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>F20 (Configuracion de Alertas Avanzadas) — Backend: Azure Function Evaluacion de Condiciones.</t>
-        </is>
-      </c>
-      <c r="F182" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F20 (Advanced Alert Configuration) — Backend - Alert Configuration CRUD.</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6335,27 +6335,27 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F20 - Configuracion de Alertas Avanzadas/F20 - W04 - Backend - Envio de Email con SendGrid o SMTP.md</t>
+          <t>docs/roadmap/F20 - Advanced Alert Configuration/F20 - W03 - Backend - Azure Function Condition Evaluation.md</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>F20 - W04 - Backend - Envio de Email con SendGrid o SMTP.md</t>
+          <t>F20 - W03 - Backend - Azure Function Condition Evaluation.md</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>F20 - W04 - Backend - Envio de Email con SendGrid o SMTP</t>
+          <t>F20 - W03 - Backend - Azure Function Condition Evaluation</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>F20 (Configuracion de Alertas Avanzadas) — Backend: Envio de Email con SendGrid o SMTP.</t>
-        </is>
-      </c>
-      <c r="F183" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F20 (Advanced Alert Configuration) — Backend - Azure Function Condition Evaluation.</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6367,27 +6367,27 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F20 - Configuracion de Alertas Avanzadas/F20 - W05 - Frontend - Wizard Configuracion de Alerta.md</t>
+          <t>docs/roadmap/F20 - Advanced Alert Configuration/F20 - W04 - Backend - Email Sending with SendGrid or SMTP.md</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>F20 - W05 - Frontend - Wizard Configuracion de Alerta.md</t>
+          <t>F20 - W04 - Backend - Email Sending with SendGrid or SMTP.md</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>F20 - W05 - Frontend - Wizard Configuracion de Alerta</t>
+          <t>F20 - W04 - Backend - Email Sending with SendGrid or SMTP</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>F20 (Configuracion de Alertas Avanzadas) — Frontend: Wizard Configuracion de Alerta.</t>
-        </is>
-      </c>
-      <c r="F184" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F20 (Advanced Alert Configuration) — Backend - Email Sending with SendGrid or SMTP.</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6399,27 +6399,27 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F20 - Configuracion de Alertas Avanzadas/F20 - W06 - Frontend - Centro de Alertas Inbox.md</t>
+          <t>docs/roadmap/F20 - Advanced Alert Configuration/F20 - W05 - Frontend - Alert Configuration Wizard.md</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>F20 - W06 - Frontend - Centro de Alertas Inbox.md</t>
+          <t>F20 - W05 - Frontend - Alert Configuration Wizard.md</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>F20 - W06 - Frontend - Centro de Alertas Inbox</t>
+          <t>F20 - W05 - Frontend - Alert Configuration Wizard</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>F20 (Configuracion de Alertas Avanzadas) — Frontend: Centro de Alertas Inbox.</t>
-        </is>
-      </c>
-      <c r="F185" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F20 (Advanced Alert Configuration) — Frontend - Alert Configuration Wizard.</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6431,27 +6431,27 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F20 - Configuracion de Alertas Avanzadas/F20 - W07 - Testing - Tests de Alertas.md</t>
+          <t>docs/roadmap/F20 - Advanced Alert Configuration/F20 - W06 - Frontend - Alert Center Inbox.md</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>F20 - W07 - Testing - Tests de Alertas.md</t>
+          <t>F20 - W06 - Frontend - Alert Center Inbox.md</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>F20 - W07 - Testing - Tests de Alertas</t>
+          <t>F20 - W06 - Frontend - Alert Center Inbox</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>F20 (Configuracion de Alertas Avanzadas) — Testing: Tests de Alertas.</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F20 (Advanced Alert Configuration) — Frontend - Alert Center Inbox.</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6463,27 +6463,27 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F21 - Explorador de Grafo Legal/F21 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F20 - Advanced Alert Configuration/F20 - W07 - Testing - Alert Tests.md</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>F21 - W01 - Documentacion Integral.md</t>
+          <t>F20 - W07 - Testing - Alert Tests.md</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>F21 - W01 - Documentacion Integral</t>
+          <t>F20 - W07 - Testing - Alert Tests</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F21 (Explorador de Grafo Legal): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F187" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F20 (Advanced Alert Configuration) — Testing - Alert Tests.</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6495,27 +6495,27 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F21 - Explorador de Grafo Legal/F21 - W02 - Backend - Endpoint GET Grafo Explorar con Profundidad.md</t>
+          <t>docs/roadmap/F21 - Legal Graph Explorer/F21 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>F21 - W02 - Backend - Endpoint GET Grafo Explorar con Profundidad.md</t>
+          <t>F21 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>F21 - W02 - Backend - Endpoint GET Grafo Explorar con Profundidad</t>
+          <t>F21 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>F21 (Explorador de Grafo Legal) — Backend: Endpoint GET Grafo Explorar con Profundidad.</t>
-        </is>
-      </c>
-      <c r="F188" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F21 (Legal Graph Explorer): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6527,27 +6527,27 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F21 - Explorador de Grafo Legal/F21 - W03 - Frontend - Componente Grafo Interactivo D3 o Cytoscape.md</t>
+          <t>docs/roadmap/F21 - Legal Graph Explorer/F21 - W02 - Backend - GET Explore Graph with Depth Endpoint.md</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>F21 - W03 - Frontend - Componente Grafo Interactivo D3 o Cytoscape.md</t>
+          <t>F21 - W02 - Backend - GET Explore Graph with Depth Endpoint.md</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>F21 - W03 - Frontend - Componente Grafo Interactivo D3 o Cytoscape</t>
+          <t>F21 - W02 - Backend - GET Explore Graph with Depth Endpoint</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>F21 (Explorador de Grafo Legal) — Frontend: Componente Grafo Interactivo D3 o Cytoscape.</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F21 (Legal Graph Explorer) — Backend - GET Explore Graph with Depth Endpoint.</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6559,27 +6559,27 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F21 - Explorador de Grafo Legal/F21 - W04 - Frontend - Panel Detalle de Nodo Seleccionado.md</t>
+          <t>docs/roadmap/F21 - Legal Graph Explorer/F21 - W03 - Frontend - Interactive Graph Component D3 or Cytoscape.md</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>F21 - W04 - Frontend - Panel Detalle de Nodo Seleccionado.md</t>
+          <t>F21 - W03 - Frontend - Interactive Graph Component D3 or Cytoscape.md</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>F21 - W04 - Frontend - Panel Detalle de Nodo Seleccionado</t>
+          <t>F21 - W03 - Frontend - Interactive Graph Component D3 or Cytoscape</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>F21 (Explorador de Grafo Legal) — Frontend: Panel Detalle de Nodo Seleccionado.</t>
-        </is>
-      </c>
-      <c r="F190" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F21 (Legal Graph Explorer) — Frontend - Interactive Graph Component D3 or Cytoscape.</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6591,27 +6591,27 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F21 - Explorador de Grafo Legal/F21 - W05 - Frontend - Filtros por Tipo de Relacion.md</t>
+          <t>docs/roadmap/F21 - Legal Graph Explorer/F21 - W04 - Frontend - Selected Node Detail Panel.md</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>F21 - W05 - Frontend - Filtros por Tipo de Relacion.md</t>
+          <t>F21 - W04 - Frontend - Selected Node Detail Panel.md</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>F21 - W05 - Frontend - Filtros por Tipo de Relacion</t>
+          <t>F21 - W04 - Frontend - Selected Node Detail Panel</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>F21 (Explorador de Grafo Legal) — Frontend: Filtros por Tipo de Relacion.</t>
-        </is>
-      </c>
-      <c r="F191" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F21 (Legal Graph Explorer) — Frontend - Selected Node Detail Panel.</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6623,27 +6623,27 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F21 - Explorador de Grafo Legal/F21 - W06 - Testing - Tests de Explorador de Grafo.md</t>
+          <t>docs/roadmap/F21 - Legal Graph Explorer/F21 - W05 - Frontend - Filters by Relationship Type.md</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>F21 - W06 - Testing - Tests de Explorador de Grafo.md</t>
+          <t>F21 - W05 - Frontend - Filters by Relationship Type.md</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>F21 - W06 - Testing - Tests de Explorador de Grafo</t>
+          <t>F21 - W05 - Frontend - Filters by Relationship Type</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>F21 (Explorador de Grafo Legal) — Testing: Tests de Explorador de Grafo.</t>
-        </is>
-      </c>
-      <c r="F192" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F21 (Legal Graph Explorer) — Frontend - Filters by Relationship Type.</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6655,27 +6655,27 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F22 - Feedback y Mejora de Agentes/F22 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F21 - Legal Graph Explorer/F21 - W06 - Testing - Graph Explorer Tests.md</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>F22 - W01 - Documentacion Integral.md</t>
+          <t>F21 - W06 - Testing - Graph Explorer Tests.md</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>F22 - W01 - Documentacion Integral</t>
+          <t>F21 - W06 - Testing - Graph Explorer Tests</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F22 (Feedback y Mejora de Agentes): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F193" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F21 (Legal Graph Explorer) — Testing - Graph Explorer Tests.</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6687,27 +6687,27 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F22 - Feedback y Mejora de Agentes/F22 - W02 - Backend - Endpoint POST Feedback y Modelo SQL.md</t>
+          <t>docs/roadmap/F22 - Agent Feedback and Improvement/F22 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>F22 - W02 - Backend - Endpoint POST Feedback y Modelo SQL.md</t>
+          <t>F22 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>F22 - W02 - Backend - Endpoint POST Feedback y Modelo SQL</t>
+          <t>F22 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>F22 (Feedback y Mejora de Agentes) — Backend: Endpoint POST Feedback y Modelo SQL.</t>
-        </is>
-      </c>
-      <c r="F194" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F22 (Agent Feedback and Improvement): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6719,27 +6719,27 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F22 - Feedback y Mejora de Agentes/F22 - W03 - Backend - Azure Function Analisis Semanal de Feedback.md</t>
+          <t>docs/roadmap/F22 - Agent Feedback and Improvement/F22 - W02 - Backend - POST Feedback Endpoint and SQL Model.md</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>F22 - W03 - Backend - Azure Function Analisis Semanal de Feedback.md</t>
+          <t>F22 - W02 - Backend - POST Feedback Endpoint and SQL Model.md</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>F22 - W03 - Backend - Azure Function Analisis Semanal de Feedback</t>
+          <t>F22 - W02 - Backend - POST Feedback Endpoint and SQL Model</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>F22 (Feedback y Mejora de Agentes) — Backend: Azure Function Analisis Semanal de Feedback.</t>
-        </is>
-      </c>
-      <c r="F195" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F22 (Agent Feedback and Improvement) — Backend - POST Feedback Endpoint and SQL Model.</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6751,27 +6751,27 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F22 - Feedback y Mejora de Agentes/F22 - W04 - Frontend - Botones Feedback en Chat.md</t>
+          <t>docs/roadmap/F22 - Agent Feedback and Improvement/F22 - W03 - Backend - Azure Function Weekly Feedback Analysis.md</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>F22 - W04 - Frontend - Botones Feedback en Chat.md</t>
+          <t>F22 - W03 - Backend - Azure Function Weekly Feedback Analysis.md</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>F22 - W04 - Frontend - Botones Feedback en Chat</t>
+          <t>F22 - W03 - Backend - Azure Function Weekly Feedback Analysis</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>F22 (Feedback y Mejora de Agentes) — Frontend: Botones Feedback en Chat.</t>
-        </is>
-      </c>
-      <c r="F196" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F22 (Agent Feedback and Improvement) — Backend - Azure Function Weekly Feedback Analysis.</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6783,27 +6783,27 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F22 - Feedback y Mejora de Agentes/F22 - W05 - Frontend - Dashboard Metricas de Satisfaccion.md</t>
+          <t>docs/roadmap/F22 - Agent Feedback and Improvement/F22 - W04 - Frontend - Feedback Buttons in Chat.md</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>F22 - W05 - Frontend - Dashboard Metricas de Satisfaccion.md</t>
+          <t>F22 - W04 - Frontend - Feedback Buttons in Chat.md</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>F22 - W05 - Frontend - Dashboard Metricas de Satisfaccion</t>
+          <t>F22 - W04 - Frontend - Feedback Buttons in Chat</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>F22 (Feedback y Mejora de Agentes) — Frontend: Dashboard Metricas de Satisfaccion.</t>
-        </is>
-      </c>
-      <c r="F197" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F22 (Agent Feedback and Improvement) — Frontend - Feedback Buttons in Chat.</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6815,27 +6815,27 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F22 - Feedback y Mejora de Agentes/F22 - W06 - Testing - Tests de Feedback.md</t>
+          <t>docs/roadmap/F22 - Agent Feedback and Improvement/F22 - W05 - Frontend - Satisfaction Metrics Dashboard.md</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>F22 - W06 - Testing - Tests de Feedback.md</t>
+          <t>F22 - W05 - Frontend - Satisfaction Metrics Dashboard.md</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>F22 - W06 - Testing - Tests de Feedback</t>
+          <t>F22 - W05 - Frontend - Satisfaction Metrics Dashboard</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>F22 (Feedback y Mejora de Agentes) — Testing: Tests de Feedback.</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F22 (Agent Feedback and Improvement) — Frontend - Satisfaction Metrics Dashboard.</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6847,27 +6847,27 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F23 - Modo Offline PWA/F23 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F22 - Agent Feedback and Improvement/F22 - W06 - Testing - Feedback Tests.md</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>F23 - W01 - Documentacion Integral.md</t>
+          <t>F22 - W06 - Testing - Feedback Tests.md</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>F23 - W01 - Documentacion Integral</t>
+          <t>F22 - W06 - Testing - Feedback Tests</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature F23 (Modo Offline PWA): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F22 (Agent Feedback and Improvement) — Testing - Feedback Tests.</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6879,27 +6879,27 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F23 - Modo Offline PWA/F23 - W02 - Backend - ETags y Caching Headers.md</t>
+          <t>docs/roadmap/F23 - PWA Offline Mode/F23 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>F23 - W02 - Backend - ETags y Caching Headers.md</t>
+          <t>F23 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>F23 - W02 - Backend - ETags y Caching Headers</t>
+          <t>F23 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>F23 (Modo Offline PWA) — Backend: ETags y Caching Headers.</t>
-        </is>
-      </c>
-      <c r="F200" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature F23 (PWA Offline Mode): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6911,27 +6911,27 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F23 - Modo Offline PWA/F23 - W03 - Frontend - Angular Service Worker Setup.md</t>
+          <t>docs/roadmap/F23 - PWA Offline Mode/F23 - W02 - Backend - ETags and Caching Headers.md</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>F23 - W03 - Frontend - Angular Service Worker Setup.md</t>
+          <t>F23 - W02 - Backend - ETags and Caching Headers.md</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>F23 - W03 - Frontend - Angular Service Worker Setup</t>
+          <t>F23 - W02 - Backend - ETags and Caching Headers</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>F23 (Modo Offline PWA) — Frontend: Angular Service Worker Setup.</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F23 (PWA Offline Mode) — Backend - ETags and Caching Headers.</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6943,27 +6943,27 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F23 - Modo Offline PWA/F23 - W04 - Frontend - IndexedDB para Cache Offline.md</t>
+          <t>docs/roadmap/F23 - PWA Offline Mode/F23 - W03 - Frontend - Angular Service Worker Setup.md</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>F23 - W04 - Frontend - IndexedDB para Cache Offline.md</t>
+          <t>F23 - W03 - Frontend - Angular Service Worker Setup.md</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>F23 - W04 - Frontend - IndexedDB para Cache Offline</t>
+          <t>F23 - W03 - Frontend - Angular Service Worker Setup</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>F23 (Modo Offline PWA) — Frontend: IndexedDB para Cache Offline.</t>
-        </is>
-      </c>
-      <c r="F202" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F23 (PWA Offline Mode) — Frontend - Angular Service Worker Setup.</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -6975,27 +6975,27 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F23 - Modo Offline PWA/F23 - W05 - Frontend - Sync al Reconectar.md</t>
+          <t>docs/roadmap/F23 - PWA Offline Mode/F23 - W04 - Frontend - IndexedDB for Offline Cache.md</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>F23 - W05 - Frontend - Sync al Reconectar.md</t>
+          <t>F23 - W04 - Frontend - IndexedDB for Offline Cache.md</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>F23 - W05 - Frontend - Sync al Reconectar</t>
+          <t>F23 - W04 - Frontend - IndexedDB for Offline Cache</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>F23 (Modo Offline PWA) — Frontend: Sync al Reconectar.</t>
-        </is>
-      </c>
-      <c r="F203" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F23 (PWA Offline Mode) — Frontend - IndexedDB for Offline Cache.</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7007,27 +7007,27 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/F23 - Modo Offline PWA/F23 - W06 - Testing - Tests Offline.md</t>
+          <t>docs/roadmap/F23 - PWA Offline Mode/F23 - W05 - Frontend - Sync on Reconnect.md</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>F23 - W06 - Testing - Tests Offline.md</t>
+          <t>F23 - W05 - Frontend - Sync on Reconnect.md</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>F23 - W06 - Testing - Tests Offline</t>
+          <t>F23 - W05 - Frontend - Sync on Reconnect</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>F23 (Modo Offline PWA) — Testing: Tests Offline.</t>
-        </is>
-      </c>
-      <c r="F204" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F23 (PWA Offline Mode) — Frontend - Sync on Reconnect.</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7039,27 +7039,27 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT01 - Notificaciones en Tiempo Real/FT01 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/F23 - PWA Offline Mode/F23 - W06 - Testing - Offline Tests.md</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>FT01 - W01 - Documentacion Integral.md</t>
+          <t>F23 - W06 - Testing - Offline Tests.md</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>FT01 - W01 - Documentacion Integral</t>
+          <t>F23 - W06 - Testing - Offline Tests</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature FT01 (Notificaciones en Tiempo Real): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>F23 (PWA Offline Mode) — Testing - Offline Tests.</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7071,27 +7071,27 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT01 - Notificaciones en Tiempo Real/FT01 - W02 - Backend - SignalR Hub NotificacionHub.md</t>
+          <t>docs/roadmap/FT01 - Real-Time Notifications/FT01 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>FT01 - W02 - Backend - SignalR Hub NotificacionHub.md</t>
+          <t>FT01 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>FT01 - W02 - Backend - SignalR Hub NotificacionHub</t>
+          <t>FT01 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>FT01 (Notificaciones en Tiempo Real) — Backend: SignalR Hub NotificacionHub.</t>
-        </is>
-      </c>
-      <c r="F206" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature FT01 (Real-Time Notifications): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7103,27 +7103,27 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT01 - Notificaciones en Tiempo Real/FT01 - W03 - Backend - Worker Storage Queue a SignalR.md</t>
+          <t>docs/roadmap/FT01 - Real-Time Notifications/FT01 - W02 - Backend - SignalR NotificationHub.md</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>FT01 - W03 - Backend - Worker Storage Queue a SignalR.md</t>
+          <t>FT01 - W02 - Backend - SignalR NotificationHub.md</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>FT01 - W03 - Backend - Worker Storage Queue a SignalR</t>
+          <t>FT01 - W02 - Backend - SignalR NotificationHub</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>FT01 (Notificaciones en Tiempo Real) — Backend: Worker Storage Queue a SignalR.</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT01 (Real-Time Notifications) — Backend - SignalR NotificationHub.</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7135,27 +7135,27 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT01 - Notificaciones en Tiempo Real/FT01 - W04 - Frontend - NotificacionService SignalR Client.md</t>
+          <t>docs/roadmap/FT01 - Real-Time Notifications/FT01 - W03 - Backend - Worker Storage Queue to SignalR.md</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>FT01 - W04 - Frontend - NotificacionService SignalR Client.md</t>
+          <t>FT01 - W03 - Backend - Worker Storage Queue to SignalR.md</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>FT01 - W04 - Frontend - NotificacionService SignalR Client</t>
+          <t>FT01 - W03 - Backend - Worker Storage Queue to SignalR</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>FT01 (Notificaciones en Tiempo Real) — Frontend: NotificacionService SignalR Client.</t>
-        </is>
-      </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT01 (Real-Time Notifications) — Backend - Worker Storage Queue to SignalR.</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7167,27 +7167,27 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT01 - Notificaciones en Tiempo Real/FT01 - W05 - Frontend - Badge y Toast Components.md</t>
+          <t>docs/roadmap/FT01 - Real-Time Notifications/FT01 - W04 - Frontend - NotificationService SignalR Client.md</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>FT01 - W05 - Frontend - Badge y Toast Components.md</t>
+          <t>FT01 - W04 - Frontend - NotificationService SignalR Client.md</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>FT01 - W05 - Frontend - Badge y Toast Components</t>
+          <t>FT01 - W04 - Frontend - NotificationService SignalR Client</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>FT01 (Notificaciones en Tiempo Real) — Frontend: Badge y Toast Components.</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT01 (Real-Time Notifications) — Frontend - NotificationService SignalR Client.</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7199,27 +7199,27 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT01 - Notificaciones en Tiempo Real/FT01 - W06 - Frontend - Centro de Notificaciones.md</t>
+          <t>docs/roadmap/FT01 - Real-Time Notifications/FT01 - W05 - Frontend - Badge and Toast Components.md</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>FT01 - W06 - Frontend - Centro de Notificaciones.md</t>
+          <t>FT01 - W05 - Frontend - Badge and Toast Components.md</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>FT01 - W06 - Frontend - Centro de Notificaciones</t>
+          <t>FT01 - W05 - Frontend - Badge and Toast Components</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>FT01 (Notificaciones en Tiempo Real) — Frontend: Centro de Notificaciones.</t>
-        </is>
-      </c>
-      <c r="F210" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT01 (Real-Time Notifications) — Frontend - Badge and Toast Components.</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7231,27 +7231,27 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT01 - Notificaciones en Tiempo Real/FT01 - W07 - Testing - Tests de Notificaciones.md</t>
+          <t>docs/roadmap/FT01 - Real-Time Notifications/FT01 - W06 - Frontend - Notification Center.md</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>FT01 - W07 - Testing - Tests de Notificaciones.md</t>
+          <t>FT01 - W06 - Frontend - Notification Center.md</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>FT01 - W07 - Testing - Tests de Notificaciones</t>
+          <t>FT01 - W06 - Frontend - Notification Center</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>FT01 (Notificaciones en Tiempo Real) — Testing: Tests de Notificaciones.</t>
-        </is>
-      </c>
-      <c r="F211" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT01 (Real-Time Notifications) — Frontend - Notification Center.</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7263,27 +7263,27 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT02 - Busqueda Global Omnisearch/FT02 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/FT01 - Real-Time Notifications/FT01 - W07 - Testing - Notification Tests.md</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>FT02 - W01 - Documentacion Integral.md</t>
+          <t>FT01 - W07 - Testing - Notification Tests.md</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>FT02 - W01 - Documentacion Integral</t>
+          <t>FT01 - W07 - Testing - Notification Tests</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature FT02 (Busqueda Global Omnisearch): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F212" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT01 (Real-Time Notifications) — Testing - Notification Tests.</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7295,27 +7295,27 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT02 - Busqueda Global Omnisearch/FT02 - W02 - Backend - Endpoint GET Buscar Global Multi-Index.md</t>
+          <t>docs/roadmap/FT02 - Global Omnisearch/FT02 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>FT02 - W02 - Backend - Endpoint GET Buscar Global Multi-Index.md</t>
+          <t>FT02 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>FT02 - W02 - Backend - Endpoint GET Buscar Global Multi-Index</t>
+          <t>FT02 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>FT02 (Busqueda Global Omnisearch) — Backend: Endpoint GET Buscar Global Multi-Index.</t>
-        </is>
-      </c>
-      <c r="F213" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature FT02 (Global Omnisearch): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7327,27 +7327,27 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT02 - Busqueda Global Omnisearch/FT02 - W03 - Frontend - Modal Omnisearch con Keyboard Nav.md</t>
+          <t>docs/roadmap/FT02 - Global Omnisearch/FT02 - W02 - Backend - GET Global Search Multi-Index Endpoint.md</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>FT02 - W03 - Frontend - Modal Omnisearch con Keyboard Nav.md</t>
+          <t>FT02 - W02 - Backend - GET Global Search Multi-Index Endpoint.md</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>FT02 - W03 - Frontend - Modal Omnisearch con Keyboard Nav</t>
+          <t>FT02 - W02 - Backend - GET Global Search Multi-Index Endpoint</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>FT02 (Busqueda Global Omnisearch) — Frontend: Modal Omnisearch con Keyboard Nav.</t>
-        </is>
-      </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT02 (Global Omnisearch) — Backend - GET Global Search Multi-Index Endpoint.</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7359,27 +7359,27 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT02 - Busqueda Global Omnisearch/FT02 - W04 - Frontend - Resultados Agrupados por Tipo.md</t>
+          <t>docs/roadmap/FT02 - Global Omnisearch/FT02 - W03 - Frontend - Omnisearch Modal with Keyboard Nav.md</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>FT02 - W04 - Frontend - Resultados Agrupados por Tipo.md</t>
+          <t>FT02 - W03 - Frontend - Omnisearch Modal with Keyboard Nav.md</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>FT02 - W04 - Frontend - Resultados Agrupados por Tipo</t>
+          <t>FT02 - W03 - Frontend - Omnisearch Modal with Keyboard Nav</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>FT02 (Busqueda Global Omnisearch) — Frontend: Resultados Agrupados por Tipo.</t>
-        </is>
-      </c>
-      <c r="F215" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT02 (Global Omnisearch) — Frontend - Omnisearch Modal with Keyboard Nav.</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7391,27 +7391,27 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT02 - Busqueda Global Omnisearch/FT02 - W05 - Testing - Tests de Omnisearch.md</t>
+          <t>docs/roadmap/FT02 - Global Omnisearch/FT02 - W04 - Frontend - Results Grouped by Type.md</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>FT02 - W05 - Testing - Tests de Omnisearch.md</t>
+          <t>FT02 - W04 - Frontend - Results Grouped by Type.md</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>FT02 - W05 - Testing - Tests de Omnisearch</t>
+          <t>FT02 - W04 - Frontend - Results Grouped by Type</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>FT02 (Busqueda Global Omnisearch) — Testing: Tests de Omnisearch.</t>
-        </is>
-      </c>
-      <c r="F216" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT02 (Global Omnisearch) — Frontend - Results Grouped by Type.</t>
+        </is>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7423,27 +7423,27 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT03 - Tema y Accesibilidad/FT03 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/FT02 - Global Omnisearch/FT02 - W05 - Testing - Omnisearch Tests.md</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>FT03 - W01 - Documentacion Integral.md</t>
+          <t>FT02 - W05 - Testing - Omnisearch Tests.md</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>FT03 - W01 - Documentacion Integral</t>
+          <t>FT02 - W05 - Testing - Omnisearch Tests</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature FT03 (Tema y Accesibilidad): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F217" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT02 (Global Omnisearch) — Testing - Omnisearch Tests.</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7455,27 +7455,27 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT03 - Tema y Accesibilidad/FT03 - W02 - Frontend - Angular Material Theming Claro y Oscuro.md</t>
+          <t>docs/roadmap/FT03 - Theme and Accessibility/FT03 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>FT03 - W02 - Frontend - Angular Material Theming Claro y Oscuro.md</t>
+          <t>FT03 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>FT03 - W02 - Frontend - Angular Material Theming Claro y Oscuro</t>
+          <t>FT03 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>FT03 (Tema y Accesibilidad) — Frontend: Angular Material Theming Claro y Oscuro.</t>
-        </is>
-      </c>
-      <c r="F218" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature FT03 (Theme and Accessibility): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7487,27 +7487,27 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT03 - Tema y Accesibilidad/FT03 - W03 - Frontend - Tailwind Config y Design Tokens.md</t>
+          <t>docs/roadmap/FT03 - Theme and Accessibility/FT03 - W02 - Frontend - Angular Material Light and Dark Theming.md</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>FT03 - W03 - Frontend - Tailwind Config y Design Tokens.md</t>
+          <t>FT03 - W02 - Frontend - Angular Material Light and Dark Theming.md</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>FT03 - W03 - Frontend - Tailwind Config y Design Tokens</t>
+          <t>FT03 - W02 - Frontend - Angular Material Light and Dark Theming</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>FT03 (Tema y Accesibilidad) — Frontend: Tailwind Config y Design Tokens.</t>
-        </is>
-      </c>
-      <c r="F219" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT03 (Theme and Accessibility) — Frontend - Angular Material Light and Dark Theming.</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7519,27 +7519,27 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT03 - Tema y Accesibilidad/FT03 - W04 - Frontend - Accesibilidad WCAG 2.1 AA.md</t>
+          <t>docs/roadmap/FT03 - Theme and Accessibility/FT03 - W03 - Frontend - Tailwind Config and Design Tokens.md</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>FT03 - W04 - Frontend - Accesibilidad WCAG 2.1 AA.md</t>
+          <t>FT03 - W03 - Frontend - Tailwind Config and Design Tokens.md</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>FT03 - W04 - Frontend - Accesibilidad WCAG 2.1 AA</t>
+          <t>FT03 - W03 - Frontend - Tailwind Config and Design Tokens</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>FT03 (Tema y Accesibilidad) — Frontend: Accesibilidad WCAG 2.1 AA.</t>
-        </is>
-      </c>
-      <c r="F220" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT03 (Theme and Accessibility) — Frontend - Tailwind Config and Design Tokens.</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7551,27 +7551,27 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT03 - Tema y Accesibilidad/FT03 - W05 - Testing - Audit de Accesibilidad.md</t>
+          <t>docs/roadmap/FT03 - Theme and Accessibility/FT03 - W04 - Frontend - WCAG 2.1 AA Accessibility.md</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>FT03 - W05 - Testing - Audit de Accesibilidad.md</t>
+          <t>FT03 - W04 - Frontend - WCAG 2.1 AA Accessibility.md</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>FT03 - W05 - Testing - Audit de Accesibilidad</t>
+          <t>FT03 - W04 - Frontend - WCAG 2.1 AA Accessibility</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>FT03 (Tema y Accesibilidad) — Testing: Audit de Accesibilidad.</t>
-        </is>
-      </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT03 (Theme and Accessibility) — Frontend - WCAG 2.1 AA Accessibility.</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7583,27 +7583,27 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT04 - Auditoria y Logging/FT04 - W01 - Documentacion Integral.md</t>
+          <t>docs/roadmap/FT03 - Theme and Accessibility/FT03 - W05 - Testing - Accessibility Audit.md</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>FT04 - W01 - Documentacion Integral.md</t>
+          <t>FT03 - W05 - Testing - Accessibility Audit.md</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>FT04 - W01 - Documentacion Integral</t>
+          <t>FT03 - W05 - Testing - Accessibility Audit</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Documentación integral de la feature FT04 (Auditoria y Logging): arquitectura, endpoints, modelos de datos y criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="F222" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT03 (Theme and Accessibility) — Testing - Accessibility Audit.</t>
+        </is>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7615,27 +7615,27 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT04 - Auditoria y Logging/FT04 - W02 - Backend - Middleware de Auditoria NET 10.md</t>
+          <t>docs/roadmap/FT04 - Audit and Logging/FT04 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>FT04 - W02 - Backend - Middleware de Auditoria NET 10.md</t>
+          <t>FT04 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>FT04 - W02 - Backend - Middleware de Auditoria NET 10</t>
+          <t>FT04 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>FT04 (Auditoria y Logging) — Backend: Middleware de Auditoria NET 10.</t>
-        </is>
-      </c>
-      <c r="F223" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>Comprehensive documentation of feature FT04 (Audit and Logging): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7647,27 +7647,27 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT04 - Auditoria y Logging/FT04 - W03 - Backend - Tabla AuditLog y Retention Policy.md</t>
+          <t>docs/roadmap/FT04 - Audit and Logging/FT04 - W02 - Backend - Audit Middleware .NET 10.md</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>FT04 - W03 - Backend - Tabla AuditLog y Retention Policy.md</t>
+          <t>FT04 - W02 - Backend - Audit Middleware .NET 10.md</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>FT04 - W03 - Backend - Tabla AuditLog y Retention Policy</t>
+          <t>FT04 - W02 - Backend - Audit Middleware .NET 10</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>FT04 (Auditoria y Logging) — Backend: Tabla AuditLog y Retention Policy.</t>
-        </is>
-      </c>
-      <c r="F224" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT04 (Audit and Logging) — Backend - Audit Middleware .NET 10.</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7679,27 +7679,27 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT04 - Auditoria y Logging/FT04 - W04 - Backend - Application Insights Integration.md</t>
+          <t>docs/roadmap/FT04 - Audit and Logging/FT04 - W03 - Backend - AuditLog Table and Retention Policy.md</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>FT04 - W04 - Backend - Application Insights Integration.md</t>
+          <t>FT04 - W03 - Backend - AuditLog Table and Retention Policy.md</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>FT04 - W04 - Backend - Application Insights Integration</t>
+          <t>FT04 - W03 - Backend - AuditLog Table and Retention Policy</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>FT04 (Auditoria y Logging) — Backend: Application Insights Integration.</t>
-        </is>
-      </c>
-      <c r="F225" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT04 (Audit and Logging) — Backend - AuditLog Table and Retention Policy.</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -7711,448 +7711,736 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>docs/roadmap/FT04 - Auditoria y Logging/FT04 - W05 - Testing - Tests de Auditoria.md</t>
+          <t>docs/roadmap/FT04 - Audit and Logging/FT04 - W04 - Backend - Application Insights Integration.md</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>FT04 - W05 - Testing - Tests de Auditoria.md</t>
+          <t>FT04 - W04 - Backend - Application Insights Integration.md</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>FT04 - W05 - Testing - Tests de Auditoria</t>
+          <t>FT04 - W04 - Backend - Application Insights Integration</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>FT04 (Auditoria y Logging) — Testing: Tests de Auditoria.</t>
-        </is>
-      </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>Parte y parte</t>
+          <t>FT04 (Audit and Logging) — Backend - Application Insights Integration.</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Work item (roadmap)</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/01-rag-retrieval.md</t>
+          <t>docs/roadmap/FT04 - Audit and Logging/FT04 - W05 - Testing - Audit Tests.md</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>01-rag-retrieval.md</t>
+          <t>FT04 - W05 - Testing - Audit Tests.md</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 01 — RAG &amp; Retrieval</t>
+          <t>FT04 - W05 - Testing - Audit Tests</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>Búsqueda híbrida (BM25 + vectores), GraphRAG y contextual retrieval.</t>
-        </is>
-      </c>
-      <c r="F227" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>FT04 (Audit and Logging) — Testing - Audit Tests.</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Work item (roadmap)</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/02-arquitectura-agentica.md</t>
+          <t>docs/roadmap/FT05 - Delivery and Hosting/FT05 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>02-arquitectura-agentica.md</t>
+          <t>FT05 - W01 - Comprehensive Documentation.md</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 02 — Arquitectura agéntica</t>
+          <t>FT05 - W01 - Comprehensive Documentation</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Diseño multi-agente, router, tool calling y orquestación sobre Semantic Kernel.</t>
-        </is>
-      </c>
-      <c r="F228" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Comprehensive documentation of feature FT05 (Delivery and Hosting): architecture, endpoints, data models, acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Work item (roadmap)</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/03-prompt-engineering.md</t>
+          <t>docs/roadmap/FT05 - Delivery and Hosting/FT05 - W02 - GitHub - CI and CD to Azure Staging.md</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>03-prompt-engineering.md</t>
+          <t>FT05 - W02 - GitHub - CI and CD to Azure Staging.md</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 03 — Prompt engineering</t>
+          <t>FT05 - W02 - GitHub - CI and CD to Azure Staging</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>Gestión de prompts, system prompts, templates y structured output.</t>
-        </is>
-      </c>
-      <c r="F229" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>FT05 (Delivery and Hosting) — GitHub - CI and CD to Azure Staging.</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Work item (roadmap)</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/04-ingesta-procesamiento.md</t>
+          <t>docs/roadmap/FT05 - Delivery and Hosting/FT05 - W03 - GCaaS - Helm Chart and Knative Deployment.md</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>04-ingesta-procesamiento.md</t>
+          <t>FT05 - W03 - GCaaS - Helm Chart and Knative Deployment.md</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 04 — Ingesta &amp; procesamiento</t>
+          <t>FT05 - W03 - GCaaS - Helm Chart and Knative Deployment</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Pipeline de ingesta de documentos de 6 etapas, NER y clasificación.</t>
-        </is>
-      </c>
-      <c r="F230" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>FT05 (Delivery and Hosting) — GCaaS - Helm Chart and Knative Deployment.</t>
+        </is>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Work item (roadmap)</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/05-evaluacion-calidad-ia.md</t>
+          <t>docs/roadmap/FT05 - Delivery and Hosting/FT05 - W04 - GCaaS - Platform Authentication id_token Cookie.md</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>05-evaluacion-calidad-ia.md</t>
+          <t>FT05 - W04 - GCaaS - Platform Authentication id_token Cookie.md</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 05 — Evaluación &amp; calidad de IA</t>
+          <t>FT05 - W04 - GCaaS - Platform Authentication id_token Cookie</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>Golden sets, métricas y LLM-as-judge para evaluar agentes.</t>
-        </is>
-      </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>FT05 (Delivery and Hosting) — GCaaS - Platform Authentication id_token Cookie.</t>
+        </is>
+      </c>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Work item (roadmap)</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/06-seguridad-compliance-ia.md</t>
+          <t>docs/roadmap/FT05 - Delivery and Hosting/FT05 - W05 - GCaaS - Vault Secrets and ConfigMap Wiring.md</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>06-seguridad-compliance-ia.md</t>
+          <t>FT05 - W05 - GCaaS - Vault Secrets and ConfigMap Wiring.md</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 06 — Seguridad &amp; compliance IA</t>
+          <t>FT05 - W05 - GCaaS - Vault Secrets and ConfigMap Wiring</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>Content filtering, PII y secreto profesional.</t>
-        </is>
-      </c>
-      <c r="F232" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>FT05 (Delivery and Hosting) — GCaaS - Vault Secrets and ConfigMap Wiring.</t>
+        </is>
+      </c>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Work item (roadmap)</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/07-observabilidad-llmops.md</t>
+          <t>docs/roadmap/FT05 - Delivery and Hosting/FT05 - W06 - GCaaS - Post-Deploy Verification and Rollback Runbook.md</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>07-observabilidad-llmops.md</t>
+          <t>FT05 - W06 - GCaaS - Post-Deploy Verification and Rollback Runbook.md</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 07 — Observabilidad &amp; LLMOps</t>
+          <t>FT05 - W06 - GCaaS - Post-Deploy Verification and Rollback Runbook</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>Tracing, uso de tokens, circuit breaker y operación de LLMs.</t>
-        </is>
-      </c>
-      <c r="F233" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>FT05 (Delivery and Hosting) — GCaaS - Post-Deploy Verification and Rollback Runbook.</t>
+        </is>
+      </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/08-ux-ia-legal.md</t>
+          <t>docs/technical/01-rag-retrieval.md</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>08-ux-ia-legal.md</t>
+          <t>01-rag-retrieval.md</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 08 — UX de IA legal</t>
+          <t>Tech doc 01 — RAG &amp; Retrieval</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>Streaming, citación inline y feedback loops en la UI de chat.</t>
-        </is>
-      </c>
-      <c r="F234" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Hybrid search (BM25 + vectors), GraphRAG, contextual retrieval.</t>
+        </is>
+      </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/09-data-knowledge-management.md</t>
+          <t>docs/technical/02-agentic-architecture.md</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>09-data-knowledge-management.md</t>
+          <t>02-agentic-architecture.md</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>Doc técnico 09 — Data &amp; knowledge management</t>
+          <t>Tech doc 02 — Agentic architecture</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>Taxonomía, versionado temporal y mantenimiento del grafo de conocimiento.</t>
-        </is>
-      </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Multi-agent design, router, tool calling, Semantic Kernel orchestration.</t>
+        </is>
+      </c>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>docs/tecnicas/README.md</t>
+          <t>docs/technical/03-prompt-engineering.md</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>03-prompt-engineering.md</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Índice de documentos técnicos</t>
+          <t>Tech doc 03 — Prompt engineering</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>Índice y guía de los 9 documentos técnicos del proyecto.</t>
-        </is>
-      </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Prompt management, system prompts, templates, structured output.</t>
+        </is>
+      </c>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Ontología</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>docs/ontologia/fuentes_datos_ontologia.md</t>
+          <t>docs/technical/04-ingestion-processing.md</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>fuentes_datos_ontologia.md</t>
+          <t>04-ingestion-processing.md</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>Fuentes de datos de la ontología</t>
+          <t>Tech doc 04 — Ingestion &amp; processing</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>Fuentes primarias y secundarias por clase del modelo de dominio.</t>
-        </is>
-      </c>
-      <c r="F237" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>6-stage document ingestion pipeline, NER, classification.</t>
+        </is>
+      </c>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Ontología</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>docs/ontologia/ontologia_legal_argentina.md</t>
+          <t>docs/technical/05-ai-quality-evaluation.md</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>ontologia_legal_argentina.md</t>
+          <t>05-ai-quality-evaluation.md</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Ontología legal argentina</t>
+          <t>Tech doc 05 — AI quality &amp; evaluation</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>Modelo de dominio: clases, propiedades, relaciones y cardinalidades del ordenamiento jurídico argentino.</t>
-        </is>
-      </c>
-      <c r="F238" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Golden sets, metrics, LLM-as-judge for evaluating agents.</t>
+        </is>
+      </c>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Ontología</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>docs/ontologia/ontologia_legal_argentina.mermaid</t>
+          <t>docs/technical/06-ai-security-compliance.md</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>ontologia_legal_argentina.mermaid</t>
+          <t>06-ai-security-compliance.md</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>Diagrama de la ontología (Mermaid)</t>
+          <t>Tech doc 06 — AI security &amp; compliance</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>Diagrama de clases del modelo de dominio legal argentino en formato Mermaid.</t>
-        </is>
-      </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>Castellano</t>
+          <t>Content filtering, PII, attorney-client privilege.</t>
+        </is>
+      </c>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Technical doc</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>docs/technical/07-observability-llmops.md</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>07-observability-llmops.md</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Tech doc 07 — Observability &amp; LLMOps</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>Tracing, token usage, circuit breaker, LLM operations.</t>
+        </is>
+      </c>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Technical doc</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>docs/technical/08-legal-ai-ux.md</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>08-legal-ai-ux.md</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Tech doc 08 — Legal AI UX</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>Streaming, inline citation, feedback loops in the chat UI.</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Technical doc</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>docs/technical/09-data-knowledge-management.md</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>09-data-knowledge-management.md</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Tech doc 09 — Data &amp; knowledge management</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>Taxonomy, temporal versioning, knowledge graph maintenance.</t>
+        </is>
+      </c>
+      <c r="F242" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Technical doc</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>docs/technical/README.md</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Technical docs index</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>Index and guide to the project's 9 technical documents.</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Ontology</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>docs/ontology/argentine-legal-ontology.md</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>argentine-legal-ontology.md</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Argentine legal ontology</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Domain model: classes, properties, relationships, cardinalities of the Argentine legal system.</t>
+        </is>
+      </c>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Ontology</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>docs/ontology/argentine-legal-ontology.mermaid</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>argentine-legal-ontology.mermaid</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Ontology diagram (Mermaid)</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>Class diagram of the Argentine legal domain model in Mermaid format.</t>
+        </is>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Ontology</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>docs/ontology/ontology-data-sources.md</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>ontology-data-sources.md</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Ontology data sources</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>Primary and secondary sources per domain-model class.</t>
+        </is>
+      </c>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Delivery doc</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>docs/deployment/gcaas-hosting.md</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>gcaas-hosting.md</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>GCaaS Hosting</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>PwC corporate hosting: Knative/Istio Helm deploy, Entra SSO (id_token cookie), Vault secrets, session model. Self-contained; replaces the MVP gcaas-usage doc.</t>
+        </is>
+      </c>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Delivery doc</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>docs/deployment/github-delivery.md</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>github-delivery.md</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Delivery</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>Source control, CI quality gates, and CD to Azure staging (API + SPA). Self-contained; replaces the MVP github-usage doc.</t>
+        </is>
+      </c>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F239"/>
+  <autoFilter ref="A1:F248"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8163,17 +8451,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Resumen del inventario</t>
+          <t>File inventory summary</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -8181,30 +8469,30 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Total de archivos (excluye mvp)</t>
+          <t>Total files (excludes mvp)</t>
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Por categoría</t>
+          <t>By category</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Cantidad</t>
+          <t>Count</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Raíz</t>
+          <t>Root</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
@@ -8214,7 +8502,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Config Cowork</t>
+          <t>Cowork config</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -8224,7 +8512,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Config editor</t>
+          <t>Editor config</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -8234,7 +8522,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Regla Cursor</t>
+          <t>Cursor rule</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -8268,7 +8556,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -8288,13 +8576,13 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Doc técnico</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -8304,54 +8592,64 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Ontología</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Por idioma</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Delivery doc</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Inglés</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>4</v>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>By language</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Castellano</t>
+          <t>English</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Parte y parte</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>215</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/file-inventory.xlsx
+++ b/docs/file-inventory.xlsx
@@ -2257,9 +2257,9 @@
           <t>Comprehensive documentation of feature F01 (Authentication and Authorization): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2289,9 +2289,9 @@
           <t>F01 (Authentication and Authorization) — Backend - Entra ID and JWT Configuration.</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2321,9 +2321,9 @@
           <t>F01 (Authentication and Authorization) — Backend - Role-Based Authorization Middleware.</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2353,9 +2353,9 @@
           <t>F01 (Authentication and Authorization) — Frontend - MSAL Angular Setup and AuthService.</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2385,9 +2385,9 @@
           <t>F01 (Authentication and Authorization) — Frontend - AuthGuard and RoleGuard.</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2417,9 +2417,9 @@
           <t>F01 (Authentication and Authorization) — Frontend - AuthInterceptor and ErrorInterceptor.</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2449,9 +2449,9 @@
           <t>F01 (Authentication and Authorization) — Testing - E2E Authentication Tests.</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2481,9 +2481,9 @@
           <t>Comprehensive documentation of feature F02 (Main Dashboard): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2513,9 +2513,9 @@
           <t>F02 (Main Dashboard) — Backend - Dashboard Aggregator Endpoint.</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2545,9 +2545,9 @@
           <t>F02 (Main Dashboard) — Frontend - Shell Layout Sidebar and Navbar.</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2577,9 +2577,9 @@
           <t>F02 (Main Dashboard) — Frontend - Dashboard Component and Widgets.</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2609,9 +2609,9 @@
           <t>F02 (Main Dashboard) — Frontend - Upcoming Deadlines Widget.</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2641,9 +2641,9 @@
           <t>F02 (Main Dashboard) — Frontend - Regulatory Updates Widget.</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2673,9 +2673,9 @@
           <t>F02 (Main Dashboard) — Testing - Dashboard Tests.</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2705,9 +2705,9 @@
           <t>Comprehensive documentation of feature F03 (Legal Norm Search): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2737,9 +2737,9 @@
           <t>F03 (Legal Norm Search) — Backend - AI Search Index for Legal Norms.</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2769,9 +2769,9 @@
           <t>F03 (Legal Norm Search) — Backend - Hybrid BM25 and Vector Scoring Profile.</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2801,9 +2801,9 @@
           <t>F03 (Legal Norm Search) — Backend - POST Search Legal Norms Endpoint.</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2833,9 +2833,9 @@
           <t>F03 (Legal Norm Search) — Frontend - SearchBar with Autocomplete.</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2865,9 +2865,9 @@
           <t>F03 (Legal Norm Search) — Frontend - Sidebar Filters with Facets.</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2897,9 +2897,9 @@
           <t>F03 (Legal Norm Search) — Frontend - Results List with Highlight.</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2929,9 +2929,9 @@
           <t>F03 (Legal Norm Search) — Testing - Legal Norm Search Tests.</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2961,9 +2961,9 @@
           <t>Comprehensive documentation of feature F04 (Case Law Search): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2993,9 +2993,9 @@
           <t>F04 (Case Law Search) — Backend - AI Search Index for Case Law.</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3025,9 +3025,9 @@
           <t>F04 (Case Law Search) — Backend - POST Search Case Law Endpoint.</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3057,9 +3057,9 @@
           <t>F04 (Case Law Search) — Frontend - Case Law Search Page.</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3089,9 +3089,9 @@
           <t>F04 (Case Law Search) — Frontend - Ruling Result Card.</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3121,9 +3121,9 @@
           <t>F04 (Case Law Search) — Testing - Case Law Search Tests.</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3153,9 +3153,9 @@
           <t>Comprehensive documentation of feature F05 (Legal Norm Detail): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3185,9 +3185,9 @@
           <t>F05 (Legal Norm Detail) — Backend - GET Legal Norm Detail Endpoint.</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3217,9 +3217,9 @@
           <t>F05 (Legal Norm Detail) — Backend - GET Legal Norm Graph SQL Graph Endpoint.</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3249,9 +3249,9 @@
           <t>F05 (Legal Norm Detail) — Backend - GET Legal Norm Articles Paged Endpoint.</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3281,9 +3281,9 @@
           <t>F05 (Legal Norm Detail) — Frontend - Legal Norm Detail Page with Tabs.</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3313,9 +3313,9 @@
           <t>F05 (Legal Norm Detail) — Frontend - Relationship Graph Visualization.</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3345,9 +3345,9 @@
           <t>F05 (Legal Norm Detail) — Frontend - Amendments Timeline.</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3377,9 +3377,9 @@
           <t>F05 (Legal Norm Detail) — Testing - Legal Norm Detail Tests.</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3409,9 +3409,9 @@
           <t>Comprehensive documentation of feature F06 (Article Detail): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3441,9 +3441,9 @@
           <t>F06 (Article Detail) — Backend - GET Article and Related Case Law Endpoint.</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3473,9 +3473,9 @@
           <t>F06 (Article Detail) — Frontend - Article Detail Page.</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3505,9 +3505,9 @@
           <t>F06 (Article Detail) — Frontend - Related Case Law Panel.</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3537,9 +3537,9 @@
           <t>F06 (Article Detail) — Testing - Article Detail Tests.</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3569,9 +3569,9 @@
           <t>Comprehensive documentation of feature F07 (Regulatory Updates): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3601,9 +3601,9 @@
           <t>F07 (Regulatory Updates) — Backend - Azure Function Timer Trigger Official Gazette.</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3633,9 +3633,9 @@
           <t>F07 (Regulatory Updates) — Backend - GET Updates and SignalR Push Endpoint.</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3665,9 +3665,9 @@
           <t>F07 (Regulatory Updates) — Frontend - Updates Feed Page.</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3697,9 +3697,9 @@
           <t>F07 (Regulatory Updates) — Frontend - Alert Subscription by Law Branch.</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3729,9 +3729,9 @@
           <t>F07 (Regulatory Updates) — Testing - Updates Tests.</t>
         </is>
       </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3761,9 +3761,9 @@
           <t>Comprehensive documentation of feature F08 (AI Agent Chat): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3793,9 +3793,9 @@
           <t>F08 (AI Agent Chat) — Backend - Semantic Kernel Setup and Orchestrator.</t>
         </is>
       </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3825,9 +3825,9 @@
           <t>F08 (AI Agent Chat) — Backend - POST Chat with SignalR Streaming Endpoint.</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3857,9 +3857,9 @@
           <t>F08 (AI Agent Chat) — Backend - Conversation Persistence.</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3889,9 +3889,9 @@
           <t>F08 (AI Agent Chat) — Frontend - Chat UI with Markdown Rendering.</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3921,9 +3921,9 @@
           <t>F08 (AI Agent Chat) — Frontend - SignalR Client for Streaming.</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3953,9 +3953,9 @@
           <t>F08 (AI Agent Chat) — Frontend - Cited Sources Panel.</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3985,9 +3985,9 @@
           <t>F08 (AI Agent Chat) — Frontend - Conversation History.</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4017,9 +4017,9 @@
           <t>F08 (AI Agent Chat) — Testing - E2E Chat Tests.</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4049,9 +4049,9 @@
           <t>Comprehensive documentation of feature F09 (Regulatory Agent): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F111" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4081,9 +4081,9 @@
           <t>F09 (Regulatory Agent) — Backend - RegulatoryAgent Plugin Functions.</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4113,9 +4113,9 @@
           <t>F09 (Regulatory Agent) — Backend - Agent Semantic Prompts.</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4145,9 +4145,9 @@
           <t>F09 (Regulatory Agent) — Backend - Integration with AI Search and SQL Graph.</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4177,9 +4177,9 @@
           <t>F09 (Regulatory Agent) — Testing - Evaluation with 15 Typified Queries.</t>
         </is>
       </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4209,9 +4209,9 @@
           <t>Comprehensive documentation of feature F10 (Case Law Agent): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4241,9 +4241,9 @@
           <t>F10 (Case Law Agent) — Backend - CaseLawAgent Plugin Functions.</t>
         </is>
       </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4273,9 +4273,9 @@
           <t>F10 (Case Law Agent) — Backend - RAG Pipeline over Case Law.</t>
         </is>
       </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4305,9 +4305,9 @@
           <t>F10 (Case Law Agent) — Backend - Graph Traversal Ruling to Article.</t>
         </is>
       </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4337,9 +4337,9 @@
           <t>F10 (Case Law Agent) — Testing - Evaluation with 15 Typified Queries.</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4369,9 +4369,9 @@
           <t>Comprehensive documentation of feature F11 (Procedural Agent): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4401,9 +4401,9 @@
           <t>F11 (Procedural Agent) — Backend - ProceduralAgent Plugin Functions.</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4433,9 +4433,9 @@
           <t>F11 (Procedural Agent) — Backend - Business Days Calculation Engine.</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4465,9 +4465,9 @@
           <t>F11 (Procedural Agent) — Backend - National and Court Holidays Calendar.</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4497,9 +4497,9 @@
           <t>F11 (Procedural Agent) — Testing - Evaluation with 10 Typified Queries.</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4529,9 +4529,9 @@
           <t>Comprehensive documentation of feature F12 (Case File Management): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4561,9 +4561,9 @@
           <t>F12 (Case File Management) — Backend - EF Core Case File Model and Migrations.</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4593,9 +4593,9 @@
           <t>F12 (Case File Management) — Backend - Case File CRUD Endpoints.</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4625,9 +4625,9 @@
           <t>F12 (Case File Management) — Backend - Movements and Documents Subresources.</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4657,9 +4657,9 @@
           <t>F12 (Case File Management) — Backend - Upload Documents to Blob Storage.</t>
         </is>
       </c>
-      <c r="F130" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4689,9 +4689,9 @@
           <t>F12 (Case File Management) — Frontend - Case File List with DataTable.</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4721,9 +4721,9 @@
           <t>F12 (Case File Management) — Frontend - Case File Create and Edit Form.</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4753,9 +4753,9 @@
           <t>F12 (Case File Management) — Frontend - Case File Detail with Tabs.</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4785,9 +4785,9 @@
           <t>F12 (Case File Management) — Frontend - Movements Timeline.</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4817,9 +4817,9 @@
           <t>F12 (Case File Management) — Frontend - Attached Documents Management.</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4849,9 +4849,9 @@
           <t>F12 (Case File Management) — Testing - Case File CRUD Tests.</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4881,9 +4881,9 @@
           <t>Comprehensive documentation of feature F13 (Deadline Management): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4913,9 +4913,9 @@
           <t>F13 (Deadline Management) — Backend - EF Core Deadline Model and Migrations.</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4945,9 +4945,9 @@
           <t>F13 (Deadline Management) — Backend - Deadline CRUD Endpoints.</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -4977,9 +4977,9 @@
           <t>F13 (Deadline Management) — Backend - Azure Function Daily Deadline Evaluation.</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5009,9 +5009,9 @@
           <t>F13 (Deadline Management) — Backend - Alert Generation via Storage Queue.</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5041,9 +5041,9 @@
           <t>F13 (Deadline Management) — Frontend - Deadline List with Visual Traffic Light.</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5073,9 +5073,9 @@
           <t>F13 (Deadline Management) — Frontend - Deadline Create Form with Business Days Calculation.</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5105,9 +5105,9 @@
           <t>F13 (Deadline Management) — Testing - Deadline and Business Days Calculation Tests.</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5137,9 +5137,9 @@
           <t>Comprehensive documentation of feature F14 (Legal Calendar): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5169,9 +5169,9 @@
           <t>F14 (Legal Calendar) — Backend - GET Aggregated Calendar Endpoint.</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5201,9 +5201,9 @@
           <t>F14 (Legal Calendar) — Frontend - FullCalendar Angular Integration.</t>
         </is>
       </c>
-      <c r="F147" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5233,9 +5233,9 @@
           <t>F14 (Legal Calendar) — Frontend - Calendar Filters and Navigation.</t>
         </is>
       </c>
-      <c r="F148" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5265,9 +5265,9 @@
           <t>F14 (Legal Calendar) — Testing - Calendar Tests.</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5297,9 +5297,9 @@
           <t>Comprehensive documentation of feature F15 (Legal Risk Analysis): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F150" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5329,9 +5329,9 @@
           <t>F15 (Legal Risk Analysis) — Backend - RiskAgent Semantic Kernel Plugin.</t>
         </is>
       </c>
-      <c r="F151" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5361,9 +5361,9 @@
           <t>F15 (Legal Risk Analysis) — Backend - Risk Taxonomy Model.</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5393,9 +5393,9 @@
           <t>F15 (Legal Risk Analysis) — Backend - POST Analyze Risk Endpoint.</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5425,9 +5425,9 @@
           <t>F15 (Legal Risk Analysis) — Backend - Analysis Persistence in SQL.</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5457,9 +5457,9 @@
           <t>F15 (Legal Risk Analysis) — Frontend - Case Input Form.</t>
         </is>
       </c>
-      <c r="F155" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5489,9 +5489,9 @@
           <t>F15 (Legal Risk Analysis) — Frontend - Result View with Visual Score.</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5521,9 +5521,9 @@
           <t>F15 (Legal Risk Analysis) — Testing - Risk Analysis Evaluation.</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5553,9 +5553,9 @@
           <t>Comprehensive documentation of feature F16 (Risk Analysis History): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F158" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5585,9 +5585,9 @@
           <t>F16 (Risk Analysis History) — Backend - GET History and Re-analysis Endpoint.</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5617,9 +5617,9 @@
           <t>F16 (Risk Analysis History) — Frontend - History List with DataTable.</t>
         </is>
       </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5649,9 +5649,9 @@
           <t>F16 (Risk Analysis History) — Frontend - Visual Diff Between Analyses.</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5681,9 +5681,9 @@
           <t>F16 (Risk Analysis History) — Testing - History Tests.</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5713,9 +5713,9 @@
           <t>Comprehensive documentation of feature F17 (Legal Report Generation): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5745,9 +5745,9 @@
           <t>F17 (Legal Report Generation) — Backend - OpenXml Template Engine.</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5777,9 +5777,9 @@
           <t>F17 (Legal Report Generation) — Backend - Report Templates in Blob Storage.</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5809,9 +5809,9 @@
           <t>F17 (Legal Report Generation) — Backend - POST Generate Report Endpoint.</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5841,9 +5841,9 @@
           <t>F17 (Legal Report Generation) — Frontend - Report Type Selector.</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5873,9 +5873,9 @@
           <t>F17 (Legal Report Generation) — Frontend - Report Preview and Download.</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5905,9 +5905,9 @@
           <t>F17 (Legal Report Generation) — Testing - Report Generation Tests.</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5937,9 +5937,9 @@
           <t>Comprehensive documentation of feature F18 (Operational Reports): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -5969,9 +5969,9 @@
           <t>F18 (Operational Reports) — Backend - Aggregated Reports Endpoints.</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6001,9 +6001,9 @@
           <t>F18 (Operational Reports) — Frontend - Charts with ngx-charts.</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6033,9 +6033,9 @@
           <t>F18 (Operational Reports) — Frontend - Export to PDF and Excel.</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6065,9 +6065,9 @@
           <t>F18 (Operational Reports) — Testing - Reports Tests.</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6097,9 +6097,9 @@
           <t>Comprehensive documentation of feature F19 (User Administration): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F175" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6129,9 +6129,9 @@
           <t>F19 (User Administration) — Backend - User CRUD and Custom Permissions.</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6161,9 +6161,9 @@
           <t>F19 (User Administration) — Backend - Audit Log in Azure SQL.</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6193,9 +6193,9 @@
           <t>F19 (User Administration) — Frontend - User Admin Page.</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6225,9 +6225,9 @@
           <t>F19 (User Administration) — Frontend - Audit Log.</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6257,9 +6257,9 @@
           <t>F19 (User Administration) — Testing - Admin Tests.</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6289,9 +6289,9 @@
           <t>Comprehensive documentation of feature F20 (Advanced Alert Configuration): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6321,9 +6321,9 @@
           <t>F20 (Advanced Alert Configuration) — Backend - Alert Configuration CRUD.</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6353,9 +6353,9 @@
           <t>F20 (Advanced Alert Configuration) — Backend - Azure Function Condition Evaluation.</t>
         </is>
       </c>
-      <c r="F183" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6385,9 +6385,9 @@
           <t>F20 (Advanced Alert Configuration) — Backend - Email Sending with SendGrid or SMTP.</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6417,9 +6417,9 @@
           <t>F20 (Advanced Alert Configuration) — Frontend - Alert Configuration Wizard.</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6449,9 +6449,9 @@
           <t>F20 (Advanced Alert Configuration) — Frontend - Alert Center Inbox.</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6481,9 +6481,9 @@
           <t>F20 (Advanced Alert Configuration) — Testing - Alert Tests.</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6513,9 +6513,9 @@
           <t>Comprehensive documentation of feature F21 (Legal Graph Explorer): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6545,9 +6545,9 @@
           <t>F21 (Legal Graph Explorer) — Backend - GET Explore Graph with Depth Endpoint.</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6577,9 +6577,9 @@
           <t>F21 (Legal Graph Explorer) — Frontend - Interactive Graph Component D3 or Cytoscape.</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6609,9 +6609,9 @@
           <t>F21 (Legal Graph Explorer) — Frontend - Selected Node Detail Panel.</t>
         </is>
       </c>
-      <c r="F191" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6641,9 +6641,9 @@
           <t>F21 (Legal Graph Explorer) — Frontend - Filters by Relationship Type.</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6673,9 +6673,9 @@
           <t>F21 (Legal Graph Explorer) — Testing - Graph Explorer Tests.</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6705,9 +6705,9 @@
           <t>Comprehensive documentation of feature F22 (Agent Feedback and Improvement): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6737,9 +6737,9 @@
           <t>F22 (Agent Feedback and Improvement) — Backend - POST Feedback Endpoint and SQL Model.</t>
         </is>
       </c>
-      <c r="F195" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6769,9 +6769,9 @@
           <t>F22 (Agent Feedback and Improvement) — Backend - Azure Function Weekly Feedback Analysis.</t>
         </is>
       </c>
-      <c r="F196" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6801,9 +6801,9 @@
           <t>F22 (Agent Feedback and Improvement) — Frontend - Feedback Buttons in Chat.</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6833,9 +6833,9 @@
           <t>F22 (Agent Feedback and Improvement) — Frontend - Satisfaction Metrics Dashboard.</t>
         </is>
       </c>
-      <c r="F198" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6865,9 +6865,9 @@
           <t>F22 (Agent Feedback and Improvement) — Testing - Feedback Tests.</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6897,9 +6897,9 @@
           <t>Comprehensive documentation of feature F23 (PWA Offline Mode): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F200" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6929,9 +6929,9 @@
           <t>F23 (PWA Offline Mode) — Backend - ETags and Caching Headers.</t>
         </is>
       </c>
-      <c r="F201" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6961,9 +6961,9 @@
           <t>F23 (PWA Offline Mode) — Frontend - Angular Service Worker Setup.</t>
         </is>
       </c>
-      <c r="F202" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -6993,9 +6993,9 @@
           <t>F23 (PWA Offline Mode) — Frontend - IndexedDB for Offline Cache.</t>
         </is>
       </c>
-      <c r="F203" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7025,9 +7025,9 @@
           <t>F23 (PWA Offline Mode) — Frontend - Sync on Reconnect.</t>
         </is>
       </c>
-      <c r="F204" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7057,9 +7057,9 @@
           <t>F23 (PWA Offline Mode) — Testing - Offline Tests.</t>
         </is>
       </c>
-      <c r="F205" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7089,9 +7089,9 @@
           <t>Comprehensive documentation of feature FT01 (Real-Time Notifications): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F206" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7121,9 +7121,9 @@
           <t>FT01 (Real-Time Notifications) — Backend - SignalR NotificationHub.</t>
         </is>
       </c>
-      <c r="F207" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7153,9 +7153,9 @@
           <t>FT01 (Real-Time Notifications) — Backend - Worker Storage Queue to SignalR.</t>
         </is>
       </c>
-      <c r="F208" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7185,9 +7185,9 @@
           <t>FT01 (Real-Time Notifications) — Frontend - NotificationService SignalR Client.</t>
         </is>
       </c>
-      <c r="F209" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7217,9 +7217,9 @@
           <t>FT01 (Real-Time Notifications) — Frontend - Badge and Toast Components.</t>
         </is>
       </c>
-      <c r="F210" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7249,9 +7249,9 @@
           <t>FT01 (Real-Time Notifications) — Frontend - Notification Center.</t>
         </is>
       </c>
-      <c r="F211" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7281,9 +7281,9 @@
           <t>FT01 (Real-Time Notifications) — Testing - Notification Tests.</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7313,9 +7313,9 @@
           <t>Comprehensive documentation of feature FT02 (Global Omnisearch): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7345,9 +7345,9 @@
           <t>FT02 (Global Omnisearch) — Backend - GET Global Search Multi-Index Endpoint.</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7377,9 +7377,9 @@
           <t>FT02 (Global Omnisearch) — Frontend - Omnisearch Modal with Keyboard Nav.</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7409,9 +7409,9 @@
           <t>FT02 (Global Omnisearch) — Frontend - Results Grouped by Type.</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7441,9 +7441,9 @@
           <t>FT02 (Global Omnisearch) — Testing - Omnisearch Tests.</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7473,9 +7473,9 @@
           <t>Comprehensive documentation of feature FT03 (Theme and Accessibility): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F218" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7505,9 +7505,9 @@
           <t>FT03 (Theme and Accessibility) — Frontend - Angular Material Light and Dark Theming.</t>
         </is>
       </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7537,9 +7537,9 @@
           <t>FT03 (Theme and Accessibility) — Frontend - Tailwind Config and Design Tokens.</t>
         </is>
       </c>
-      <c r="F220" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7569,9 +7569,9 @@
           <t>FT03 (Theme and Accessibility) — Frontend - WCAG 2.1 AA Accessibility.</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7601,9 +7601,9 @@
           <t>FT03 (Theme and Accessibility) — Testing - Accessibility Audit.</t>
         </is>
       </c>
-      <c r="F222" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7633,9 +7633,9 @@
           <t>Comprehensive documentation of feature FT04 (Audit and Logging): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F223" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7665,9 +7665,9 @@
           <t>FT04 (Audit and Logging) — Backend - Audit Middleware .NET 10.</t>
         </is>
       </c>
-      <c r="F224" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7697,9 +7697,9 @@
           <t>FT04 (Audit and Logging) — Backend - AuditLog Table and Retention Policy.</t>
         </is>
       </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7729,9 +7729,9 @@
           <t>FT04 (Audit and Logging) — Backend - Application Insights Integration.</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -7761,9 +7761,9 @@
           <t>FT04 (Audit and Logging) — Testing - Audit Tests.</t>
         </is>
       </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>64</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20">
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>181</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">

--- a/docs/file-inventory.xlsx
+++ b/docs/file-inventory.xlsx
@@ -50,7 +50,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,11 +70,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -119,9 +114,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2001,9 +1993,9 @@
           <t>Comprehensive documentation of feature F00 (Development Environment and Structure): architecture, endpoints, data models, acceptance criteria.</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2033,9 +2025,9 @@
           <t>F00 (Development Environment and Structure) — Monorepo Setup and Backend Scaffolding.</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2065,9 +2057,9 @@
           <t>F00 (Development Environment and Structure) — Angular 19 Frontend Scaffolding.</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2097,9 +2089,9 @@
           <t>F00 (Development Environment and Structure) — GitHub Actions CI Configuration.</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2129,9 +2121,9 @@
           <t>F00 (Development Environment and Structure) — Azure Infrastructure with Bicep.</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2161,9 +2153,9 @@
           <t>F00 (Development Environment and Structure) — CD Deployment Pipelines Configuration.</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2193,9 +2185,9 @@
           <t>F00 (Development Environment and Structure) — Local Environment Setup and Onboarding Guide.</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -2225,9 +2217,9 @@
           <t>F00 (Development Environment and Structure) — Code Quality Configuration.</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8459,7 +8451,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>File inventory summary</t>
         </is>
@@ -8467,188 +8459,178 @@
       <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Total files (excludes mvp)</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="7" t="n">
         <v>247</v>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>By category</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Root</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Cowork config</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Editor config</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="7" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Cursor rule</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Skill (Cowork)</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Skill (Cursor)</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Doc</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="7" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Work item (roadmap)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Work item (roadmap)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
         <v>187</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Technical doc</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="7" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Ontology</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="7" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Delivery doc</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>By language</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>237</v>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>245</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Spanish</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B20" s="7" t="n">
         <v>2</v>
       </c>
     </row>

--- a/docs/file-inventory.xlsx
+++ b/docs/file-inventory.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File inventory'!$A$1:$G$566</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File inventory'!$A$1:$G$578</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G566"/>
+  <dimension ref="A1:G578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9698,10 +9698,14 @@
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>13-saij-thesaurus-ingestion.md</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr"/>
+          <t>Tech doc 13 — SAIJ thesaurus ingestion</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>SAIJ thesaurus pipeline as implemented: 3-phase TemaTres crawl, BT/NT/UF/RT relations, synonym maps, keyword normalization, query expansion, API.</t>
+        </is>
+      </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
           <t>English</t>
@@ -9709,7 +9713,7 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Imported (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -9721,22 +9725,22 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>docs/technical/README.md</t>
+          <t>docs/technical/14-csjn-ruling-ingestion.md</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>14-csjn-ruling-ingestion.md</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Technical docs index</t>
+          <t>Tech doc 14 — CSJN ruling ingestion</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>Index and guide to the project's 9 technical documents.</t>
+          <t>CSJN fallos ingestion pipeline as implemented: 3 discovery sources, sjconsulta 8-endpoint API, parsing, LLM enrichment, chunking, indexing, config/throttling.</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
@@ -9758,28 +9762,32 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>docs/technical/diagrams/c4-component.mermaid</t>
+          <t>docs/technical/15-saij-web-ingestion.md</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>c4-component.mermaid</t>
+          <t>15-saij-web-ingestion.md</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>c4-component.mermaid</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr"/>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tech doc 15 — SAIJ web ingestion</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>SAIJ open-data API ingestion of legislation (Statute) and jurisprudence: discovery endpoints, self-contained no-LLM flow, Statute/NormRelation data model, rule-based classification, config.</t>
+        </is>
+      </c>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Imported (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -9791,28 +9799,32 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>docs/technical/diagrams/c4-component.puml</t>
+          <t>docs/technical/16-chat-rag-agents.md</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>c4-component.puml</t>
+          <t>16-chat-rag-agents.md</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>c4-component.puml</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr"/>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tech doc 16 — Chat, RAG &amp; agent pipeline</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>Agentic RAG chat as implemented: POST /api/chat SSE streaming, guardrail pipeline (input/output/enricher/finalizer), tool-calling loop, 13 tools, hybrid + GraphRAG retrieval, config.</t>
+        </is>
+      </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Imported (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -9824,28 +9836,32 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>docs/technical/diagrams/c4-container-simple.puml</t>
+          <t>docs/technical/17-kb-data-model.md</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>c4-container-simple.puml</t>
+          <t>17-kb-data-model.md</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>c4-container-simple.puml</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr"/>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tech doc 17 — KB data model</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>The ~44 EF Core entities in Azure SQL: legal content, actors/courts/proceedings, citation &amp; graph layer, ingestion bookkeeping, embeddings, provenance &amp; audit, modeling notes.</t>
+        </is>
+      </c>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Imported (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -9857,28 +9873,32 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>docs/technical/diagrams/c4-container.mermaid</t>
+          <t>docs/technical/18-frontend-architecture.md</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>c4-container.mermaid</t>
+          <t>18-frontend-architecture.md</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>c4-container.mermaid</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr"/>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tech doc 18 — Frontend architecture</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>Angular SPA as implemented: standalone components, lazy routes/navigation (ontological spaces + tools + admin), cookie auth, fetch+ReadableStream SSE chat client, Cytoscape graph explorer, environments.</t>
+        </is>
+      </c>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Imported (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -9890,28 +9910,32 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>docs/technical/diagrams/c4-container.puml</t>
+          <t>docs/technical/19-admin-pipeline-operations.md</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>c4-container.puml</t>
+          <t>19-admin-pipeline-operations.md</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>c4-container.puml</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="inlineStr"/>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tech doc 19 — Admin &amp; pipeline operations</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>Operations layer as implemented: admin API (crawlers/jobs/pipeline/DLQ/infra/reprocess/users), job tracking &amp; traceability, SignalR worker control (pause/resume + infra incidents), DLQ/requeue, failure recovery &amp; reconciliation, config.</t>
+        </is>
+      </c>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Imported (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -9923,28 +9947,32 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>docs/technical/diagrams/c4-context.mermaid</t>
+          <t>docs/technical/20-legal-data-sources.md</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>c4-context.mermaid</t>
+          <t>20-legal-data-sources.md</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>c4-context.mermaid</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr"/>
-      <c r="F256" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tech doc 20 — Legal data sources catalog</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>Catalog of known Argentine legal data sources: integrated (CSJN/SAIJ), national &amp; provincial jurisprudence portals, administrative dictámenes, legislation databases — with URLs and integration status.</t>
+        </is>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Imported (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -9956,157 +9984,153 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>docs/technical/diagrams/c4-context.puml</t>
+          <t>docs/technical/README.md</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>c4-context.puml</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>c4-context.puml</t>
-        </is>
-      </c>
-      <c r="E257" s="3" t="inlineStr"/>
-      <c r="F257" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Technical docs index</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>Index and guide to the project's 9 technical documents.</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Imported (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/argentine-legal-ontology.md</t>
+          <t>docs/technical/diagrams/c4-component.mermaid</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>argentine-legal-ontology.md</t>
+          <t>c4-component.mermaid</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Argentine legal ontology</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="inlineStr">
-        <is>
-          <t>Domain model: classes, properties, relationships, cardinalities of the Argentine legal system.</t>
-        </is>
-      </c>
-      <c r="F258" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>c4-component.mermaid</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr"/>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Imported (MVP)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/argentine-legal-ontology.mermaid</t>
+          <t>docs/technical/diagrams/c4-component.puml</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>argentine-legal-ontology.mermaid</t>
+          <t>c4-component.puml</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Ontology diagram (Mermaid)</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="inlineStr">
-        <is>
-          <t>Class diagram of the Argentine legal domain model in Mermaid format.</t>
-        </is>
-      </c>
-      <c r="F259" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>c4-component.puml</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr"/>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Imported (MVP)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-diagrams/README-visio-export.md</t>
+          <t>docs/technical/diagrams/c4-container-simple.puml</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>README-visio-export.md</t>
+          <t>c4-container-simple.puml</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>README-visio-export.md</t>
+          <t>c4-container-simple.puml</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr"/>
-      <c r="F260" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Reference (MVP)</t>
+          <t>Imported (MVP)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-diagrams/generate_visio_export.py</t>
+          <t>docs/technical/diagrams/c4-container.mermaid</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>generate_visio_export.py</t>
+          <t>c4-container.mermaid</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>generate_visio_export.py</t>
+          <t>c4-container.mermaid</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr"/>
@@ -10117,29 +10141,29 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Reference (MVP)</t>
+          <t>Imported (MVP)</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1-class-hierarchy.mermaid</t>
+          <t>docs/technical/diagrams/c4-container.puml</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1-class-hierarchy.mermaid</t>
+          <t>c4-container.puml</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1-class-hierarchy.mermaid</t>
+          <t>c4-container.puml</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr"/>
@@ -10150,29 +10174,29 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Reference (MVP)</t>
+          <t>Imported (MVP)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1-implementation-status.mermaid</t>
+          <t>docs/technical/diagrams/c4-context.mermaid</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1-implementation-status.mermaid</t>
+          <t>c4-context.mermaid</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1-implementation-status.mermaid</t>
+          <t>c4-context.mermaid</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr"/>
@@ -10183,29 +10207,29 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Reference (MVP)</t>
+          <t>Imported (MVP)</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Ontology</t>
+          <t>Technical doc</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1-relationships.mermaid</t>
+          <t>docs/technical/diagrams/c4-context.puml</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1-relationships.mermaid</t>
+          <t>c4-context.puml</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1-relationships.mermaid</t>
+          <t>c4-context.puml</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr"/>
@@ -10216,7 +10240,7 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Reference (MVP)</t>
+          <t>Imported (MVP)</t>
         </is>
       </c>
     </row>
@@ -10228,28 +10252,32 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1.svg</t>
+          <t>docs/ontology/argentine-legal-ontology.md</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1.svg</t>
+          <t>argentine-legal-ontology.md</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1.svg</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="inlineStr"/>
-      <c r="F265" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Argentine legal ontology</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>Domain model: classes, properties, relationships, cardinalities of the Argentine legal system.</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>Reference (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -10261,28 +10289,32 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1.visio.vdx</t>
+          <t>docs/ontology/argentine-legal-ontology.mermaid</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1.visio.vdx</t>
+          <t>argentine-legal-ontology.mermaid</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>legal-ai-ar-ontology-v2.1.visio.vdx</t>
-        </is>
-      </c>
-      <c r="E266" s="3" t="inlineStr"/>
-      <c r="F266" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Ontology diagram (Mermaid)</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>Class diagram of the Argentine legal domain model in Mermaid format.</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Reference (MVP)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -10294,23 +10326,27 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-prompts/court-hierarchy-context.md</t>
+          <t>docs/ontology/kb-domain-model.md</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>court-hierarchy-context.md</t>
+          <t>kb-domain-model.md</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>court-hierarchy-context.md</t>
-        </is>
-      </c>
-      <c r="E267" s="3" t="inlineStr"/>
-      <c r="F267" s="5" t="inlineStr">
-        <is>
-          <t>Mixed</t>
+          <t>KB target domain model (ported reference)</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>Target conceptual model of the KB based on natural legal entities. Ported MVP reference (Spanish).</t>
+        </is>
+      </c>
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
@@ -10327,23 +10363,23 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-prompts/legal-branches-context.md</t>
+          <t>docs/ontology/mvp-diagrams/README-visio-export.md</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>legal-branches-context.md</t>
+          <t>README-visio-export.md</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>legal-branches-context.md</t>
+          <t>README-visio-export.md</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr"/>
-      <c r="F268" s="5" t="inlineStr">
-        <is>
-          <t>Mixed</t>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
@@ -10360,23 +10396,23 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-prompts/normative-pyramid-context.md</t>
+          <t>docs/ontology/mvp-diagrams/generate_visio_export.py</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>normative-pyramid-context.md</t>
+          <t>generate_visio_export.py</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>normative-pyramid-context.md</t>
+          <t>generate_visio_export.py</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr"/>
-      <c r="F269" s="5" t="inlineStr">
-        <is>
-          <t>Mixed</t>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -10393,23 +10429,23 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/mvp-prompts/reasoning-flows.md</t>
+          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1-class-hierarchy.mermaid</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>reasoning-flows.md</t>
+          <t>legal-ai-ar-ontology-v2.1-class-hierarchy.mermaid</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>reasoning-flows.md</t>
+          <t>legal-ai-ar-ontology-v2.1-class-hierarchy.mermaid</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr"/>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>Mixed</t>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
@@ -10426,32 +10462,28 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/ontology-data-sources.md</t>
+          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1-implementation-status.mermaid</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>ontology-data-sources.md</t>
+          <t>legal-ai-ar-ontology-v2.1-implementation-status.mermaid</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>Ontology data sources</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="inlineStr">
-        <is>
-          <t>Primary and secondary sources per domain-model class.</t>
-        </is>
-      </c>
-      <c r="F271" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>legal-ai-ar-ontology-v2.1-implementation-status.mermaid</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
@@ -10463,27 +10495,23 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>docs/ontology/ontology-mvp.md</t>
+          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1-relationships.mermaid</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>ontology-mvp.md</t>
+          <t>legal-ai-ar-ontology-v2.1-relationships.mermaid</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Ontology — MVP reference (Spanish)</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="inlineStr">
-        <is>
-          <t>Preserved MVP ontology: KB mapping, reasoning flows, treaties, enum glossary. Reference; the applied ontology is argentine-legal-ontology.md.</t>
-        </is>
-      </c>
-      <c r="F272" s="6" t="inlineStr">
-        <is>
-          <t>Spanish</t>
+          <t>legal-ai-ar-ontology-v2.1-relationships.mermaid</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr"/>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -10495,231 +10523,227 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>Delivery doc</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>docs/deployment/gcaas-hosting.md</t>
+          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1.svg</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>gcaas-hosting.md</t>
+          <t>legal-ai-ar-ontology-v2.1.svg</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>GCaaS Hosting</t>
-        </is>
-      </c>
-      <c r="E273" s="3" t="inlineStr">
-        <is>
-          <t>PwC corporate hosting: Knative/Istio Helm deploy, Entra SSO (id_token cookie), Vault secrets, session model. Self-contained; replaces the MVP gcaas-usage doc.</t>
-        </is>
-      </c>
-      <c r="F273" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>legal-ai-ar-ontology-v2.1.svg</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Delivery doc</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>docs/deployment/github-delivery.md</t>
+          <t>docs/ontology/mvp-diagrams/legal-ai-ar-ontology-v2.1.visio.vdx</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>github-delivery.md</t>
+          <t>legal-ai-ar-ontology-v2.1.visio.vdx</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>GitHub Delivery</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>Source control, CI quality gates, and CD to Azure staging (API + SPA). Self-contained; replaces the MVP github-usage doc.</t>
-        </is>
-      </c>
-      <c r="F274" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>legal-ai-ar-ontology-v2.1.visio.vdx</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr"/>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/AGENTS.md</t>
+          <t>docs/ontology/mvp-prompts/court-hierarchy-context.md</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>AGENTS.md</t>
+          <t>court-hierarchy-context.md</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>AGENTS.md</t>
+          <t>court-hierarchy-context.md</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr"/>
-      <c r="F275" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/INDEX.md</t>
+          <t>docs/ontology/mvp-prompts/legal-branches-context.md</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>INDEX.md</t>
+          <t>legal-branches-context.md</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>INDEX.md</t>
+          <t>legal-branches-context.md</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr"/>
-      <c r="F276" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/README.md</t>
+          <t>docs/ontology/mvp-prompts/normative-pyramid-context.md</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>normative-pyramid-context.md</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>normative-pyramid-context.md</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr"/>
-      <c r="F277" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/accessibility/README.md</t>
+          <t>docs/ontology/mvp-prompts/reasoning-flows.md</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>reasoning-flows.md</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>reasoning-flows.md</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr"/>
-      <c r="F278" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/INDEX.md</t>
+          <t>docs/ontology/ontology-data-sources.md</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>INDEX.md</t>
+          <t>ontology-data-sources.md</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>INDEX.md</t>
-        </is>
-      </c>
-      <c r="E279" s="3" t="inlineStr"/>
+          <t>Ontology data sources</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>Primary and secondary sources per domain-model class.</t>
+        </is>
+      </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
           <t>English</t>
@@ -10727,197 +10751,209 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/README.md</t>
+          <t>docs/ontology/ontology-mvp.md</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>ontology-mvp.md</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
-        </is>
-      </c>
-      <c r="E280" s="3" t="inlineStr"/>
-      <c r="F280" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>Ontology — MVP reference (Spanish)</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>Preserved MVP ontology: KB mapping, reasoning flows, treaties, enum glossary. Reference; the applied ontology is argentine-legal-ontology.md.</t>
+        </is>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/accordion.md</t>
+          <t>docs/ontology/source-ontology-kb-field-origins.mermaid</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>accordion.md</t>
+          <t>source-ontology-kb-field-origins.mermaid</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>accordion.md</t>
+          <t>source-ontology-kb-field-origins.mermaid</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr"/>
-      <c r="F281" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/avatar.md</t>
+          <t>docs/ontology/source-ontology-kb-mapping.md</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>avatar.md</t>
+          <t>source-ontology-kb-mapping.md</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>avatar.md</t>
-        </is>
-      </c>
-      <c r="E282" s="3" t="inlineStr"/>
-      <c r="F282" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>Sources → Ontology → KB mapping (ported reference)</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>How semi-structured sources are transformed through the ontology into the KB. Ported MVP reference (Spanish).</t>
+        </is>
+      </c>
+      <c r="F282" s="6" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/badge.md</t>
+          <t>docs/ontology/source-ontology-kb-multi-source.mermaid</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>badge.md</t>
+          <t>source-ontology-kb-multi-source.mermaid</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>badge.md</t>
+          <t>source-ontology-kb-multi-source.mermaid</t>
         </is>
       </c>
       <c r="E283" s="3" t="inlineStr"/>
-      <c r="F283" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Ontology</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/breadcrumb.md</t>
+          <t>docs/ontology/source-ontology-kb-overview.mermaid</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>breadcrumb.md</t>
+          <t>source-ontology-kb-overview.mermaid</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>breadcrumb.md</t>
+          <t>source-ontology-kb-overview.mermaid</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr"/>
-      <c r="F284" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Reference (MVP)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Delivery doc</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/button.md</t>
+          <t>docs/deployment/gcaas-hosting.md</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>button.md</t>
+          <t>gcaas-hosting.md</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>button.md</t>
-        </is>
-      </c>
-      <c r="E285" s="3" t="inlineStr"/>
+          <t>GCaaS Hosting</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>PwC corporate hosting: Knative/Istio Helm deploy, Entra SSO (id_token cookie), Vault secrets, session model. Self-contained; replaces the MVP gcaas-usage doc.</t>
+        </is>
+      </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
           <t>English</t>
@@ -10925,32 +10961,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>AppKit (UI library)</t>
+          <t>Delivery doc</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/checkbox.md</t>
+          <t>docs/deployment/github-delivery.md</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>checkbox.md</t>
+          <t>github-delivery.md</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>checkbox.md</t>
-        </is>
-      </c>
-      <c r="E286" s="3" t="inlineStr"/>
+          <t>GitHub Delivery</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>Source control, CI quality gates, and CD to Azure staging (API + SPA). Self-contained; replaces the MVP github-usage doc.</t>
+        </is>
+      </c>
       <c r="F286" s="4" t="inlineStr">
         <is>
           <t>English</t>
@@ -10958,7 +10998,7 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Vendor (AppKit 4)</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -10970,17 +11010,17 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/datepicker.md</t>
+          <t>docs/appkit4/AGENTS.md</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>datepicker.md</t>
+          <t>AGENTS.md</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>datepicker.md</t>
+          <t>AGENTS.md</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr"/>
@@ -11003,17 +11043,17 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/drawer.md</t>
+          <t>docs/appkit4/INDEX.md</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>drawer.md</t>
+          <t>INDEX.md</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>drawer.md</t>
+          <t>INDEX.md</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr"/>
@@ -11036,17 +11076,17 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/dropdown.md</t>
+          <t>docs/appkit4/README.md</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>dropdown.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>dropdown.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr"/>
@@ -11069,17 +11109,17 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/feeds-comments.md</t>
+          <t>docs/appkit4/accessibility/README.md</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>feeds-comments.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>feeds-comments.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr"/>
@@ -11102,17 +11142,17 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/field.md</t>
+          <t>docs/appkit4/components/INDEX.md</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>field.md</t>
+          <t>INDEX.md</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>field.md</t>
+          <t>INDEX.md</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr"/>
@@ -11135,17 +11175,17 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/file-upload.md</t>
+          <t>docs/appkit4/components/README.md</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>file-upload.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>file-upload.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr"/>
@@ -11168,17 +11208,17 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/filter.md</t>
+          <t>docs/appkit4/components/accordion.md</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>filter.md</t>
+          <t>accordion.md</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>filter.md</t>
+          <t>accordion.md</t>
         </is>
       </c>
       <c r="E293" s="3" t="inlineStr"/>
@@ -11201,17 +11241,17 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/footer.md</t>
+          <t>docs/appkit4/components/avatar.md</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>footer.md</t>
+          <t>avatar.md</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>footer.md</t>
+          <t>avatar.md</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr"/>
@@ -11234,17 +11274,17 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/header.md</t>
+          <t>docs/appkit4/components/badge.md</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>header.md</t>
+          <t>badge.md</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>header.md</t>
+          <t>badge.md</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr"/>
@@ -11267,17 +11307,17 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/list.md</t>
+          <t>docs/appkit4/components/breadcrumb.md</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>list.md</t>
+          <t>breadcrumb.md</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>list.md</t>
+          <t>breadcrumb.md</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr"/>
@@ -11300,17 +11340,17 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/loading.md</t>
+          <t>docs/appkit4/components/button.md</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>loading.md</t>
+          <t>button.md</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>loading.md</t>
+          <t>button.md</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr"/>
@@ -11333,17 +11373,17 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/modal.md</t>
+          <t>docs/appkit4/components/checkbox.md</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>modal.md</t>
+          <t>checkbox.md</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>modal.md</t>
+          <t>checkbox.md</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr"/>
@@ -11366,17 +11406,17 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/navigation.md</t>
+          <t>docs/appkit4/components/datepicker.md</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>navigation.md</t>
+          <t>datepicker.md</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>navigation.md</t>
+          <t>datepicker.md</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr"/>
@@ -11399,17 +11439,17 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/notice.md</t>
+          <t>docs/appkit4/components/drawer.md</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>notice.md</t>
+          <t>drawer.md</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>notice.md</t>
+          <t>drawer.md</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr"/>
@@ -11432,17 +11472,17 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/notification.md</t>
+          <t>docs/appkit4/components/dropdown.md</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>notification.md</t>
+          <t>dropdown.md</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>notification.md</t>
+          <t>dropdown.md</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr"/>
@@ -11465,17 +11505,17 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/pagination.md</t>
+          <t>docs/appkit4/components/feeds-comments.md</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>pagination.md</t>
+          <t>feeds-comments.md</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>pagination.md</t>
+          <t>feeds-comments.md</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr"/>
@@ -11498,17 +11538,17 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/panel.md</t>
+          <t>docs/appkit4/components/field.md</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>panel.md</t>
+          <t>field.md</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>panel.md</t>
+          <t>field.md</t>
         </is>
       </c>
       <c r="E303" s="3" t="inlineStr"/>
@@ -11531,17 +11571,17 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/progress.md</t>
+          <t>docs/appkit4/components/file-upload.md</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>progress.md</t>
+          <t>file-upload.md</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>progress.md</t>
+          <t>file-upload.md</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr"/>
@@ -11564,17 +11604,17 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/radio.md</t>
+          <t>docs/appkit4/components/filter.md</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>radio.md</t>
+          <t>filter.md</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>radio.md</t>
+          <t>filter.md</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr"/>
@@ -11597,17 +11637,17 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/ratings.md</t>
+          <t>docs/appkit4/components/footer.md</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>ratings.md</t>
+          <t>footer.md</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>ratings.md</t>
+          <t>footer.md</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr"/>
@@ -11630,17 +11670,17 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/accordion.md</t>
+          <t>docs/appkit4/components/header.md</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>accordion.md</t>
+          <t>header.md</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
         <is>
-          <t>accordion.md</t>
+          <t>header.md</t>
         </is>
       </c>
       <c r="E307" s="3" t="inlineStr"/>
@@ -11663,17 +11703,17 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/avatar.md</t>
+          <t>docs/appkit4/components/list.md</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>avatar.md</t>
+          <t>list.md</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>avatar.md</t>
+          <t>list.md</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr"/>
@@ -11696,17 +11736,17 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/badge.md</t>
+          <t>docs/appkit4/components/loading.md</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>badge.md</t>
+          <t>loading.md</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>badge.md</t>
+          <t>loading.md</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr"/>
@@ -11729,17 +11769,17 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/breadcrumb.md</t>
+          <t>docs/appkit4/components/modal.md</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>breadcrumb.md</t>
+          <t>modal.md</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>breadcrumb.md</t>
+          <t>modal.md</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr"/>
@@ -11762,17 +11802,17 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/button.md</t>
+          <t>docs/appkit4/components/navigation.md</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>button.md</t>
+          <t>navigation.md</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>button.md</t>
+          <t>navigation.md</t>
         </is>
       </c>
       <c r="E311" s="3" t="inlineStr"/>
@@ -11795,17 +11835,17 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/checkbox.md</t>
+          <t>docs/appkit4/components/notice.md</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>checkbox.md</t>
+          <t>notice.md</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>checkbox.md</t>
+          <t>notice.md</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr"/>
@@ -11828,17 +11868,17 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/datepicker.md</t>
+          <t>docs/appkit4/components/notification.md</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>datepicker.md</t>
+          <t>notification.md</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
         <is>
-          <t>datepicker.md</t>
+          <t>notification.md</t>
         </is>
       </c>
       <c r="E313" s="3" t="inlineStr"/>
@@ -11861,17 +11901,17 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/drawer.md</t>
+          <t>docs/appkit4/components/pagination.md</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>drawer.md</t>
+          <t>pagination.md</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>drawer.md</t>
+          <t>pagination.md</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr"/>
@@ -11894,17 +11934,17 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/dropdown.md</t>
+          <t>docs/appkit4/components/panel.md</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>dropdown.md</t>
+          <t>panel.md</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>dropdown.md</t>
+          <t>panel.md</t>
         </is>
       </c>
       <c r="E315" s="3" t="inlineStr"/>
@@ -11927,17 +11967,17 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/feeds-comments.md</t>
+          <t>docs/appkit4/components/progress.md</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>feeds-comments.md</t>
+          <t>progress.md</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>feeds-comments.md</t>
+          <t>progress.md</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr"/>
@@ -11960,17 +12000,17 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/field.md</t>
+          <t>docs/appkit4/components/radio.md</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>field.md</t>
+          <t>radio.md</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>field.md</t>
+          <t>radio.md</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr"/>
@@ -11993,17 +12033,17 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/file-upload.md</t>
+          <t>docs/appkit4/components/ratings.md</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>file-upload.md</t>
+          <t>ratings.md</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>file-upload.md</t>
+          <t>ratings.md</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr"/>
@@ -12026,17 +12066,17 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/filter.md</t>
+          <t>docs/appkit4/components/reference/accordion.md</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>filter.md</t>
+          <t>accordion.md</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>filter.md</t>
+          <t>accordion.md</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr"/>
@@ -12059,17 +12099,17 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/footer.md</t>
+          <t>docs/appkit4/components/reference/avatar.md</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>footer.md</t>
+          <t>avatar.md</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>footer.md</t>
+          <t>avatar.md</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr"/>
@@ -12092,17 +12132,17 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/header.md</t>
+          <t>docs/appkit4/components/reference/badge.md</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>header.md</t>
+          <t>badge.md</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>header.md</t>
+          <t>badge.md</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr"/>
@@ -12125,17 +12165,17 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/list.md</t>
+          <t>docs/appkit4/components/reference/breadcrumb.md</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>list.md</t>
+          <t>breadcrumb.md</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>list.md</t>
+          <t>breadcrumb.md</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr"/>
@@ -12158,17 +12198,17 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/loading.md</t>
+          <t>docs/appkit4/components/reference/button.md</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>loading.md</t>
+          <t>button.md</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>loading.md</t>
+          <t>button.md</t>
         </is>
       </c>
       <c r="E323" s="3" t="inlineStr"/>
@@ -12191,17 +12231,17 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/modal.md</t>
+          <t>docs/appkit4/components/reference/checkbox.md</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>modal.md</t>
+          <t>checkbox.md</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>modal.md</t>
+          <t>checkbox.md</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr"/>
@@ -12224,17 +12264,17 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/navigation.md</t>
+          <t>docs/appkit4/components/reference/datepicker.md</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>navigation.md</t>
+          <t>datepicker.md</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>navigation.md</t>
+          <t>datepicker.md</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr"/>
@@ -12257,17 +12297,17 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/notice.md</t>
+          <t>docs/appkit4/components/reference/drawer.md</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>notice.md</t>
+          <t>drawer.md</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>notice.md</t>
+          <t>drawer.md</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr"/>
@@ -12290,17 +12330,17 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/notification.md</t>
+          <t>docs/appkit4/components/reference/dropdown.md</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>notification.md</t>
+          <t>dropdown.md</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>notification.md</t>
+          <t>dropdown.md</t>
         </is>
       </c>
       <c r="E327" s="3" t="inlineStr"/>
@@ -12323,17 +12363,17 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/pagination.md</t>
+          <t>docs/appkit4/components/reference/feeds-comments.md</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>pagination.md</t>
+          <t>feeds-comments.md</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>pagination.md</t>
+          <t>feeds-comments.md</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr"/>
@@ -12356,17 +12396,17 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/panel.md</t>
+          <t>docs/appkit4/components/reference/field.md</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>panel.md</t>
+          <t>field.md</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>panel.md</t>
+          <t>field.md</t>
         </is>
       </c>
       <c r="E329" s="3" t="inlineStr"/>
@@ -12389,17 +12429,17 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/progress.md</t>
+          <t>docs/appkit4/components/reference/file-upload.md</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>progress.md</t>
+          <t>file-upload.md</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>progress.md</t>
+          <t>file-upload.md</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr"/>
@@ -12422,17 +12462,17 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/radio.md</t>
+          <t>docs/appkit4/components/reference/filter.md</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>radio.md</t>
+          <t>filter.md</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>radio.md</t>
+          <t>filter.md</t>
         </is>
       </c>
       <c r="E331" s="3" t="inlineStr"/>
@@ -12455,17 +12495,17 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/ratings.md</t>
+          <t>docs/appkit4/components/reference/footer.md</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>ratings.md</t>
+          <t>footer.md</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>ratings.md</t>
+          <t>footer.md</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr"/>
@@ -12488,17 +12528,17 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/search.md</t>
+          <t>docs/appkit4/components/reference/header.md</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>search.md</t>
+          <t>header.md</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>search.md</t>
+          <t>header.md</t>
         </is>
       </c>
       <c r="E333" s="3" t="inlineStr"/>
@@ -12521,17 +12561,17 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/slider.md</t>
+          <t>docs/appkit4/components/reference/list.md</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>slider.md</t>
+          <t>list.md</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>slider.md</t>
+          <t>list.md</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr"/>
@@ -12554,17 +12594,17 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/table.md</t>
+          <t>docs/appkit4/components/reference/loading.md</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>table.md</t>
+          <t>loading.md</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>table.md</t>
+          <t>loading.md</t>
         </is>
       </c>
       <c r="E335" s="3" t="inlineStr"/>
@@ -12587,17 +12627,17 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/tabs.md</t>
+          <t>docs/appkit4/components/reference/modal.md</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>tabs.md</t>
+          <t>modal.md</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>tabs.md</t>
+          <t>modal.md</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr"/>
@@ -12620,17 +12660,17 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/tag.md</t>
+          <t>docs/appkit4/components/reference/navigation.md</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>tag.md</t>
+          <t>navigation.md</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>tag.md</t>
+          <t>navigation.md</t>
         </is>
       </c>
       <c r="E337" s="3" t="inlineStr"/>
@@ -12653,17 +12693,17 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/texteditor.md</t>
+          <t>docs/appkit4/components/reference/notice.md</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>texteditor.md</t>
+          <t>notice.md</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>texteditor.md</t>
+          <t>notice.md</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr"/>
@@ -12686,17 +12726,17 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/toggle.md</t>
+          <t>docs/appkit4/components/reference/notification.md</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>toggle.md</t>
+          <t>notification.md</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>toggle.md</t>
+          <t>notification.md</t>
         </is>
       </c>
       <c r="E339" s="3" t="inlineStr"/>
@@ -12719,17 +12759,17 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/tooltip.md</t>
+          <t>docs/appkit4/components/reference/pagination.md</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>tooltip.md</t>
+          <t>pagination.md</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>tooltip.md</t>
+          <t>pagination.md</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr"/>
@@ -12752,17 +12792,17 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/reference/tree.md</t>
+          <t>docs/appkit4/components/reference/panel.md</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>tree.md</t>
+          <t>panel.md</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>tree.md</t>
+          <t>panel.md</t>
         </is>
       </c>
       <c r="E341" s="3" t="inlineStr"/>
@@ -12785,17 +12825,17 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/search.md</t>
+          <t>docs/appkit4/components/reference/progress.md</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>search.md</t>
+          <t>progress.md</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>search.md</t>
+          <t>progress.md</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr"/>
@@ -12818,17 +12858,17 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/slider.md</t>
+          <t>docs/appkit4/components/reference/radio.md</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>slider.md</t>
+          <t>radio.md</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
         <is>
-          <t>slider.md</t>
+          <t>radio.md</t>
         </is>
       </c>
       <c r="E343" s="3" t="inlineStr"/>
@@ -12851,17 +12891,17 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/table.md</t>
+          <t>docs/appkit4/components/reference/ratings.md</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>table.md</t>
+          <t>ratings.md</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>table.md</t>
+          <t>ratings.md</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr"/>
@@ -12884,17 +12924,17 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/tabs.md</t>
+          <t>docs/appkit4/components/reference/search.md</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>tabs.md</t>
+          <t>search.md</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>tabs.md</t>
+          <t>search.md</t>
         </is>
       </c>
       <c r="E345" s="3" t="inlineStr"/>
@@ -12917,17 +12957,17 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/tag.md</t>
+          <t>docs/appkit4/components/reference/slider.md</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>tag.md</t>
+          <t>slider.md</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>tag.md</t>
+          <t>slider.md</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr"/>
@@ -12950,17 +12990,17 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/texteditor.md</t>
+          <t>docs/appkit4/components/reference/table.md</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>texteditor.md</t>
+          <t>table.md</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>texteditor.md</t>
+          <t>table.md</t>
         </is>
       </c>
       <c r="E347" s="3" t="inlineStr"/>
@@ -12983,17 +13023,17 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/toggle.md</t>
+          <t>docs/appkit4/components/reference/tabs.md</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>toggle.md</t>
+          <t>tabs.md</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>toggle.md</t>
+          <t>tabs.md</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr"/>
@@ -13016,17 +13056,17 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/tooltip.md</t>
+          <t>docs/appkit4/components/reference/tag.md</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>tooltip.md</t>
+          <t>tag.md</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>tooltip.md</t>
+          <t>tag.md</t>
         </is>
       </c>
       <c r="E349" s="3" t="inlineStr"/>
@@ -13049,17 +13089,17 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/components/tree.md</t>
+          <t>docs/appkit4/components/reference/texteditor.md</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>tree.md</t>
+          <t>texteditor.md</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>tree.md</t>
+          <t>texteditor.md</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr"/>
@@ -13082,17 +13122,17 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/README.md</t>
+          <t>docs/appkit4/components/reference/toggle.md</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>toggle.md</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>toggle.md</t>
         </is>
       </c>
       <c r="E351" s="3" t="inlineStr"/>
@@ -13115,17 +13155,17 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/all.md</t>
+          <t>docs/appkit4/components/reference/tooltip.md</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>all.md</t>
+          <t>tooltip.md</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>all.md</t>
+          <t>tooltip.md</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr"/>
@@ -13148,17 +13188,17 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/blur.md</t>
+          <t>docs/appkit4/components/reference/tree.md</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>blur.md</t>
+          <t>tree.md</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>blur.md</t>
+          <t>tree.md</t>
         </is>
       </c>
       <c r="E353" s="3" t="inlineStr"/>
@@ -13181,17 +13221,17 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/border-radius.md</t>
+          <t>docs/appkit4/components/search.md</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>border-radius.md</t>
+          <t>search.md</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>border-radius.md</t>
+          <t>search.md</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr"/>
@@ -13214,17 +13254,17 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/data.md</t>
+          <t>docs/appkit4/components/slider.md</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>data.md</t>
+          <t>slider.md</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>data.md</t>
+          <t>slider.md</t>
         </is>
       </c>
       <c r="E355" s="3" t="inlineStr"/>
@@ -13247,17 +13287,17 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/elevation.md</t>
+          <t>docs/appkit4/components/table.md</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>elevation.md</t>
+          <t>table.md</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>elevation.md</t>
+          <t>table.md</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr"/>
@@ -13280,17 +13320,17 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/neutral.md</t>
+          <t>docs/appkit4/components/tabs.md</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>neutral.md</t>
+          <t>tabs.md</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>neutral.md</t>
+          <t>tabs.md</t>
         </is>
       </c>
       <c r="E357" s="3" t="inlineStr"/>
@@ -13313,17 +13353,17 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/opacity.md</t>
+          <t>docs/appkit4/components/tag.md</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>opacity.md</t>
+          <t>tag.md</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>opacity.md</t>
+          <t>tag.md</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr"/>
@@ -13346,17 +13386,17 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/primary.md</t>
+          <t>docs/appkit4/components/texteditor.md</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>primary.md</t>
+          <t>texteditor.md</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>primary.md</t>
+          <t>texteditor.md</t>
         </is>
       </c>
       <c r="E359" s="3" t="inlineStr"/>
@@ -13379,17 +13419,17 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/spacing.md</t>
+          <t>docs/appkit4/components/toggle.md</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>spacing.md</t>
+          <t>toggle.md</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>spacing.md</t>
+          <t>toggle.md</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr"/>
@@ -13412,17 +13452,17 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/status.md</t>
+          <t>docs/appkit4/components/tooltip.md</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>status.md</t>
+          <t>tooltip.md</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>status.md</t>
+          <t>tooltip.md</t>
         </is>
       </c>
       <c r="E361" s="3" t="inlineStr"/>
@@ -13445,17 +13485,17 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/typography.md</t>
+          <t>docs/appkit4/components/tree.md</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>typography.md</t>
+          <t>tree.md</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>typography.md</t>
+          <t>tree.md</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr"/>
@@ -13478,17 +13518,17 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/design-tokens/utility.md</t>
+          <t>docs/appkit4/design-tokens/README.md</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>utility.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>utility.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E363" s="3" t="inlineStr"/>
@@ -13511,17 +13551,17 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/ecosystems/README.md</t>
+          <t>docs/appkit4/design-tokens/all.md</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>all.md</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>all.md</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr"/>
@@ -13544,17 +13584,17 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/ecosystems/appkit4-classic.md</t>
+          <t>docs/appkit4/design-tokens/blur.md</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>appkit4-classic.md</t>
+          <t>blur.md</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>appkit4-classic.md</t>
+          <t>blur.md</t>
         </is>
       </c>
       <c r="E365" s="3" t="inlineStr"/>
@@ -13577,17 +13617,17 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/ecosystems/appkit4-rebranded.md</t>
+          <t>docs/appkit4/design-tokens/border-radius.md</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>appkit4-rebranded.md</t>
+          <t>border-radius.md</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>appkit4-rebranded.md</t>
+          <t>border-radius.md</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr"/>
@@ -13610,17 +13650,17 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/getting-started/README.md</t>
+          <t>docs/appkit4/design-tokens/data.md</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>data.md</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>data.md</t>
         </is>
       </c>
       <c r="E367" s="3" t="inlineStr"/>
@@ -13643,17 +13683,17 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/getting-started/installation.md</t>
+          <t>docs/appkit4/design-tokens/elevation.md</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>installation.md</t>
+          <t>elevation.md</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>installation.md</t>
+          <t>elevation.md</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr"/>
@@ -13676,17 +13716,17 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/getting-started/new-angular-spa.md</t>
+          <t>docs/appkit4/design-tokens/neutral.md</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>new-angular-spa.md</t>
+          <t>neutral.md</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>new-angular-spa.md</t>
+          <t>neutral.md</t>
         </is>
       </c>
       <c r="E369" s="3" t="inlineStr"/>
@@ -13709,17 +13749,17 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/getting-started/versions-and-compatibility.md</t>
+          <t>docs/appkit4/design-tokens/opacity.md</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>versions-and-compatibility.md</t>
+          <t>opacity.md</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>versions-and-compatibility.md</t>
+          <t>opacity.md</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr"/>
@@ -13742,17 +13782,17 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/guides/source/accessibility.md</t>
+          <t>docs/appkit4/design-tokens/primary.md</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>accessibility.md</t>
+          <t>primary.md</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>accessibility.md</t>
+          <t>primary.md</t>
         </is>
       </c>
       <c r="E371" s="3" t="inlineStr"/>
@@ -13775,17 +13815,17 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/guides/source/installation-angular.md</t>
+          <t>docs/appkit4/design-tokens/spacing.md</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>installation-angular.md</t>
+          <t>spacing.md</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>installation-angular.md</t>
+          <t>spacing.md</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr"/>
@@ -13808,17 +13848,17 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/guides/source/mcp-instructions.md</t>
+          <t>docs/appkit4/design-tokens/status.md</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>mcp-instructions.md</t>
+          <t>status.md</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>mcp-instructions.md</t>
+          <t>status.md</t>
         </is>
       </c>
       <c r="E373" s="3" t="inlineStr"/>
@@ -13841,17 +13881,17 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/guides/source/overview-angular.md</t>
+          <t>docs/appkit4/design-tokens/typography.md</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>overview-angular.md</t>
+          <t>typography.md</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>overview-angular.md</t>
+          <t>typography.md</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr"/>
@@ -13874,17 +13914,17 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/guides/source/versions.md</t>
+          <t>docs/appkit4/design-tokens/utility.md</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>versions.md</t>
+          <t>utility.md</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>versions.md</t>
+          <t>utility.md</t>
         </is>
       </c>
       <c r="E375" s="3" t="inlineStr"/>
@@ -13907,7 +13947,7 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/README.md</t>
+          <t>docs/appkit4/ecosystems/README.md</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -13940,17 +13980,17 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-a.md</t>
+          <t>docs/appkit4/ecosystems/appkit4-classic.md</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>icons-a.md</t>
+          <t>appkit4-classic.md</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>icons-a.md</t>
+          <t>appkit4-classic.md</t>
         </is>
       </c>
       <c r="E377" s="3" t="inlineStr"/>
@@ -13973,17 +14013,17 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-b.md</t>
+          <t>docs/appkit4/ecosystems/appkit4-rebranded.md</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>icons-b.md</t>
+          <t>appkit4-rebranded.md</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>icons-b.md</t>
+          <t>appkit4-rebranded.md</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr"/>
@@ -14006,17 +14046,17 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-c.md</t>
+          <t>docs/appkit4/getting-started/README.md</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>icons-c.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>icons-c.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr"/>
@@ -14039,17 +14079,17 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-d.md</t>
+          <t>docs/appkit4/getting-started/installation.md</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>icons-d.md</t>
+          <t>installation.md</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>icons-d.md</t>
+          <t>installation.md</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr"/>
@@ -14072,17 +14112,17 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-e.md</t>
+          <t>docs/appkit4/getting-started/new-angular-spa.md</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>icons-e.md</t>
+          <t>new-angular-spa.md</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>icons-e.md</t>
+          <t>new-angular-spa.md</t>
         </is>
       </c>
       <c r="E381" s="3" t="inlineStr"/>
@@ -14105,17 +14145,17 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-f.md</t>
+          <t>docs/appkit4/getting-started/versions-and-compatibility.md</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>icons-f.md</t>
+          <t>versions-and-compatibility.md</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>icons-f.md</t>
+          <t>versions-and-compatibility.md</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr"/>
@@ -14138,17 +14178,17 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-g.md</t>
+          <t>docs/appkit4/guides/source/accessibility.md</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>icons-g.md</t>
+          <t>accessibility.md</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>icons-g.md</t>
+          <t>accessibility.md</t>
         </is>
       </c>
       <c r="E383" s="3" t="inlineStr"/>
@@ -14171,17 +14211,17 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-h.md</t>
+          <t>docs/appkit4/guides/source/installation-angular.md</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>icons-h.md</t>
+          <t>installation-angular.md</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>icons-h.md</t>
+          <t>installation-angular.md</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr"/>
@@ -14204,17 +14244,17 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-i.md</t>
+          <t>docs/appkit4/guides/source/mcp-instructions.md</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>icons-i.md</t>
+          <t>mcp-instructions.md</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>icons-i.md</t>
+          <t>mcp-instructions.md</t>
         </is>
       </c>
       <c r="E385" s="3" t="inlineStr"/>
@@ -14237,17 +14277,17 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-j.md</t>
+          <t>docs/appkit4/guides/source/overview-angular.md</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>icons-j.md</t>
+          <t>overview-angular.md</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>icons-j.md</t>
+          <t>overview-angular.md</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr"/>
@@ -14270,17 +14310,17 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-k.md</t>
+          <t>docs/appkit4/guides/source/versions.md</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>icons-k.md</t>
+          <t>versions.md</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>icons-k.md</t>
+          <t>versions.md</t>
         </is>
       </c>
       <c r="E387" s="3" t="inlineStr"/>
@@ -14303,17 +14343,17 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-l.md</t>
+          <t>docs/appkit4/icons/README.md</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>icons-l.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>icons-l.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr"/>
@@ -14336,17 +14376,17 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-m.md</t>
+          <t>docs/appkit4/icons/icons-a.md</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>icons-m.md</t>
+          <t>icons-a.md</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
         <is>
-          <t>icons-m.md</t>
+          <t>icons-a.md</t>
         </is>
       </c>
       <c r="E389" s="3" t="inlineStr"/>
@@ -14369,17 +14409,17 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-n.md</t>
+          <t>docs/appkit4/icons/icons-b.md</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>icons-n.md</t>
+          <t>icons-b.md</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>icons-n.md</t>
+          <t>icons-b.md</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr"/>
@@ -14402,17 +14442,17 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-o.md</t>
+          <t>docs/appkit4/icons/icons-c.md</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>icons-o.md</t>
+          <t>icons-c.md</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>icons-o.md</t>
+          <t>icons-c.md</t>
         </is>
       </c>
       <c r="E391" s="3" t="inlineStr"/>
@@ -14435,17 +14475,17 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-p.md</t>
+          <t>docs/appkit4/icons/icons-d.md</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>icons-p.md</t>
+          <t>icons-d.md</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>icons-p.md</t>
+          <t>icons-d.md</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr"/>
@@ -14468,17 +14508,17 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-q.md</t>
+          <t>docs/appkit4/icons/icons-e.md</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>icons-q.md</t>
+          <t>icons-e.md</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>icons-q.md</t>
+          <t>icons-e.md</t>
         </is>
       </c>
       <c r="E393" s="3" t="inlineStr"/>
@@ -14501,17 +14541,17 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-r.md</t>
+          <t>docs/appkit4/icons/icons-f.md</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>icons-r.md</t>
+          <t>icons-f.md</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>icons-r.md</t>
+          <t>icons-f.md</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr"/>
@@ -14534,17 +14574,17 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-s.md</t>
+          <t>docs/appkit4/icons/icons-g.md</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>icons-s.md</t>
+          <t>icons-g.md</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>icons-s.md</t>
+          <t>icons-g.md</t>
         </is>
       </c>
       <c r="E395" s="3" t="inlineStr"/>
@@ -14567,17 +14607,17 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-t.md</t>
+          <t>docs/appkit4/icons/icons-h.md</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>icons-t.md</t>
+          <t>icons-h.md</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>icons-t.md</t>
+          <t>icons-h.md</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr"/>
@@ -14600,17 +14640,17 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-u.md</t>
+          <t>docs/appkit4/icons/icons-i.md</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>icons-u.md</t>
+          <t>icons-i.md</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>icons-u.md</t>
+          <t>icons-i.md</t>
         </is>
       </c>
       <c r="E397" s="3" t="inlineStr"/>
@@ -14633,17 +14673,17 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-v.md</t>
+          <t>docs/appkit4/icons/icons-j.md</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>icons-v.md</t>
+          <t>icons-j.md</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>icons-v.md</t>
+          <t>icons-j.md</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr"/>
@@ -14666,17 +14706,17 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-w.md</t>
+          <t>docs/appkit4/icons/icons-k.md</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>icons-w.md</t>
+          <t>icons-k.md</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>icons-w.md</t>
+          <t>icons-k.md</t>
         </is>
       </c>
       <c r="E399" s="3" t="inlineStr"/>
@@ -14699,17 +14739,17 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-x.md</t>
+          <t>docs/appkit4/icons/icons-l.md</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>icons-x.md</t>
+          <t>icons-l.md</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>icons-x.md</t>
+          <t>icons-l.md</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr"/>
@@ -14732,17 +14772,17 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-y.md</t>
+          <t>docs/appkit4/icons/icons-m.md</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>icons-y.md</t>
+          <t>icons-m.md</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>icons-y.md</t>
+          <t>icons-m.md</t>
         </is>
       </c>
       <c r="E401" s="3" t="inlineStr"/>
@@ -14765,17 +14805,17 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/icons/icons-z.md</t>
+          <t>docs/appkit4/icons/icons-n.md</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>icons-z.md</t>
+          <t>icons-n.md</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>icons-z.md</t>
+          <t>icons-n.md</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr"/>
@@ -14798,17 +14838,17 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/layout-shell/README.md</t>
+          <t>docs/appkit4/icons/icons-o.md</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>icons-o.md</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>icons-o.md</t>
         </is>
       </c>
       <c r="E403" s="3" t="inlineStr"/>
@@ -14831,17 +14871,17 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/404-500-error-page.md</t>
+          <t>docs/appkit4/icons/icons-p.md</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>404-500-error-page.md</t>
+          <t>icons-p.md</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>404-500-error-page.md</t>
+          <t>icons-p.md</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr"/>
@@ -14864,17 +14904,17 @@
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/INDEX.md</t>
+          <t>docs/appkit4/icons/icons-q.md</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>INDEX.md</t>
+          <t>icons-q.md</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>INDEX.md</t>
+          <t>icons-q.md</t>
         </is>
       </c>
       <c r="E405" s="3" t="inlineStr"/>
@@ -14897,17 +14937,17 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/PATTERNS_STATUS.md</t>
+          <t>docs/appkit4/icons/icons-r.md</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>PATTERNS_STATUS.md</t>
+          <t>icons-r.md</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>PATTERNS_STATUS.md</t>
+          <t>icons-r.md</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr"/>
@@ -14930,17 +14970,17 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/README.md</t>
+          <t>docs/appkit4/icons/icons-s.md</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>icons-s.md</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>icons-s.md</t>
         </is>
       </c>
       <c r="E407" s="3" t="inlineStr"/>
@@ -14963,17 +15003,17 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/card.md</t>
+          <t>docs/appkit4/icons/icons-t.md</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>card.md</t>
+          <t>icons-t.md</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>card.md</t>
+          <t>icons-t.md</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr"/>
@@ -14996,17 +15036,17 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/dashboard-builder.md</t>
+          <t>docs/appkit4/icons/icons-u.md</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>dashboard-builder.md</t>
+          <t>icons-u.md</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>dashboard-builder.md</t>
+          <t>icons-u.md</t>
         </is>
       </c>
       <c r="E409" s="3" t="inlineStr"/>
@@ -15029,17 +15069,17 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/data-list-header.md</t>
+          <t>docs/appkit4/icons/icons-v.md</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>data-list-header.md</t>
+          <t>icons-v.md</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>data-list-header.md</t>
+          <t>icons-v.md</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr"/>
@@ -15062,17 +15102,17 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/delete-confirmation.md</t>
+          <t>docs/appkit4/icons/icons-w.md</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>delete-confirmation.md</t>
+          <t>icons-w.md</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>delete-confirmation.md</t>
+          <t>icons-w.md</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr"/>
@@ -15095,17 +15135,17 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/faqs.md</t>
+          <t>docs/appkit4/icons/icons-x.md</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>faqs.md</t>
+          <t>icons-x.md</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>faqs.md</t>
+          <t>icons-x.md</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr"/>
@@ -15128,17 +15168,17 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/form-template.md</t>
+          <t>docs/appkit4/icons/icons-y.md</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>form-template.md</t>
+          <t>icons-y.md</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>form-template.md</t>
+          <t>icons-y.md</t>
         </is>
       </c>
       <c r="E413" s="3" t="inlineStr"/>
@@ -15161,17 +15201,17 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/hero-banner.md</t>
+          <t>docs/appkit4/icons/icons-z.md</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>hero-banner.md</t>
+          <t>icons-z.md</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>hero-banner.md</t>
+          <t>icons-z.md</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr"/>
@@ -15194,17 +15234,17 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/login-page.md</t>
+          <t>docs/appkit4/layout-shell/README.md</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>login-page.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>login-page.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E415" s="3" t="inlineStr"/>
@@ -15227,17 +15267,17 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/multi-purpose-action-menu.md</t>
+          <t>docs/appkit4/patterns/404-500-error-page.md</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>multi-purpose-action-menu.md</t>
+          <t>404-500-error-page.md</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>multi-purpose-action-menu.md</t>
+          <t>404-500-error-page.md</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr"/>
@@ -15260,17 +15300,17 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/page-anchors.md</t>
+          <t>docs/appkit4/patterns/INDEX.md</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>page-anchors.md</t>
+          <t>INDEX.md</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>page-anchors.md</t>
+          <t>INDEX.md</t>
         </is>
       </c>
       <c r="E417" s="3" t="inlineStr"/>
@@ -15293,17 +15333,17 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/page-header-with-back-button.md</t>
+          <t>docs/appkit4/patterns/PATTERNS_STATUS.md</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>page-header-with-back-button.md</t>
+          <t>PATTERNS_STATUS.md</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>page-header-with-back-button.md</t>
+          <t>PATTERNS_STATUS.md</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr"/>
@@ -15326,17 +15366,17 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/page-templates.md</t>
+          <t>docs/appkit4/patterns/README.md</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>page-templates.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>page-templates.md</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E419" s="3" t="inlineStr"/>
@@ -15359,23 +15399,23 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/pattern-catalog.json</t>
+          <t>docs/appkit4/patterns/card.md</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>pattern-catalog.json</t>
+          <t>card.md</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>pattern-catalog.json</t>
+          <t>card.md</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr"/>
-      <c r="F420" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F420" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G420" s="2" t="inlineStr">
@@ -15392,17 +15432,17 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/search-filter.md</t>
+          <t>docs/appkit4/patterns/dashboard-builder.md</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>search-filter.md</t>
+          <t>dashboard-builder.md</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>search-filter.md</t>
+          <t>dashboard-builder.md</t>
         </is>
       </c>
       <c r="E421" s="3" t="inlineStr"/>
@@ -15425,17 +15465,17 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/README.md</t>
+          <t>docs/appkit4/patterns/data-list-header.md</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>data-list-header.md</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>data-list-header.md</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr"/>
@@ -15458,23 +15498,23 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/ErrorPage.tsx</t>
+          <t>docs/appkit4/patterns/delete-confirmation.md</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>ErrorPage.tsx</t>
+          <t>delete-confirmation.md</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>ErrorPage.tsx</t>
+          <t>delete-confirmation.md</t>
         </is>
       </c>
       <c r="E423" s="3" t="inlineStr"/>
-      <c r="F423" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F423" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr">
@@ -15491,23 +15531,23 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/ErrorPage404.tsx</t>
+          <t>docs/appkit4/patterns/faqs.md</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>ErrorPage404.tsx</t>
+          <t>faqs.md</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>ErrorPage404.tsx</t>
+          <t>faqs.md</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr"/>
-      <c r="F424" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F424" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G424" s="2" t="inlineStr">
@@ -15524,23 +15564,23 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/error-page.scss</t>
+          <t>docs/appkit4/patterns/form-template.md</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>error-page.scss</t>
+          <t>form-template.md</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
         <is>
-          <t>error-page.scss</t>
+          <t>form-template.md</t>
         </is>
       </c>
       <c r="E425" s="3" t="inlineStr"/>
-      <c r="F425" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F425" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G425" s="2" t="inlineStr">
@@ -15557,23 +15597,23 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/svg/error-404.svg</t>
+          <t>docs/appkit4/patterns/hero-banner.md</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>error-404.svg</t>
+          <t>hero-banner.md</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>error-404.svg</t>
+          <t>hero-banner.md</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr"/>
-      <c r="F426" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F426" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G426" s="2" t="inlineStr">
@@ -15590,23 +15630,23 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/svg/logo.svg</t>
+          <t>docs/appkit4/patterns/login-page.md</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>login-page.md</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>login-page.md</t>
         </is>
       </c>
       <c r="E427" s="3" t="inlineStr"/>
-      <c r="F427" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F427" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G427" s="2" t="inlineStr">
@@ -15623,23 +15663,23 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/ErrorPage.tsx</t>
+          <t>docs/appkit4/patterns/multi-purpose-action-menu.md</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>ErrorPage.tsx</t>
+          <t>multi-purpose-action-menu.md</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>ErrorPage.tsx</t>
+          <t>multi-purpose-action-menu.md</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr"/>
-      <c r="F428" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F428" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G428" s="2" t="inlineStr">
@@ -15656,23 +15696,23 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/ErrorPage500.tsx</t>
+          <t>docs/appkit4/patterns/page-anchors.md</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>ErrorPage500.tsx</t>
+          <t>page-anchors.md</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>ErrorPage500.tsx</t>
+          <t>page-anchors.md</t>
         </is>
       </c>
       <c r="E429" s="3" t="inlineStr"/>
-      <c r="F429" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F429" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G429" s="2" t="inlineStr">
@@ -15689,23 +15729,23 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/error-page.scss</t>
+          <t>docs/appkit4/patterns/page-header-with-back-button.md</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>error-page.scss</t>
+          <t>page-header-with-back-button.md</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>error-page.scss</t>
+          <t>page-header-with-back-button.md</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr"/>
-      <c r="F430" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F430" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G430" s="2" t="inlineStr">
@@ -15722,23 +15762,23 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/svg/error-500.svg</t>
+          <t>docs/appkit4/patterns/page-templates.md</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>error-500.svg</t>
+          <t>page-templates.md</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
         <is>
-          <t>error-500.svg</t>
+          <t>page-templates.md</t>
         </is>
       </c>
       <c r="E431" s="3" t="inlineStr"/>
-      <c r="F431" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F431" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
@@ -15755,17 +15795,17 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/svg/logo.svg</t>
+          <t>docs/appkit4/patterns/pattern-catalog.json</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>pattern-catalog.json</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>pattern-catalog.json</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr"/>
@@ -15788,23 +15828,23 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/Card.tsx</t>
+          <t>docs/appkit4/patterns/search-filter.md</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>Card.tsx</t>
+          <t>search-filter.md</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
         <is>
-          <t>Card.tsx</t>
+          <t>search-filter.md</t>
         </is>
       </c>
       <c r="E433" s="3" t="inlineStr"/>
-      <c r="F433" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F433" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G433" s="2" t="inlineStr">
@@ -15821,23 +15861,23 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/CardGrid.tsx</t>
+          <t>docs/appkit4/patterns/source/README.md</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>CardGrid.tsx</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>CardGrid.tsx</t>
+          <t>README.md</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr"/>
-      <c r="F434" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F434" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
@@ -15854,17 +15894,17 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card-grid.scss</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/ErrorPage.tsx</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>card-grid.scss</t>
+          <t>ErrorPage.tsx</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
         <is>
-          <t>card-grid.scss</t>
+          <t>ErrorPage.tsx</t>
         </is>
       </c>
       <c r="E435" s="3" t="inlineStr"/>
@@ -15887,17 +15927,17 @@
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card.scss</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/ErrorPage404.tsx</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>card.scss</t>
+          <t>ErrorPage404.tsx</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>card.scss</t>
+          <t>ErrorPage404.tsx</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr"/>
@@ -15920,17 +15960,17 @@
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card/Card.tsx</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/error-page.scss</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>Card.tsx</t>
+          <t>error-page.scss</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
         <is>
-          <t>Card.tsx</t>
+          <t>error-page.scss</t>
         </is>
       </c>
       <c r="E437" s="3" t="inlineStr"/>
@@ -15953,17 +15993,17 @@
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card/CardGrid.tsx</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/svg/error-404.svg</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>CardGrid.tsx</t>
+          <t>error-404.svg</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>CardGrid.tsx</t>
+          <t>error-404.svg</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr"/>
@@ -15986,17 +16026,17 @@
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card/card-grid.scss</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-404/svg/logo.svg</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>card-grid.scss</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
         <is>
-          <t>card-grid.scss</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="E439" s="3" t="inlineStr"/>
@@ -16019,17 +16059,17 @@
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card/card.scss</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/ErrorPage.tsx</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>card.scss</t>
+          <t>ErrorPage.tsx</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>card.scss</t>
+          <t>ErrorPage.tsx</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr"/>
@@ -16052,17 +16092,17 @@
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card/placeholder-first-wider.svg</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/ErrorPage500.tsx</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>placeholder-first-wider.svg</t>
+          <t>ErrorPage500.tsx</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
         <is>
-          <t>placeholder-first-wider.svg</t>
+          <t>ErrorPage500.tsx</t>
         </is>
       </c>
       <c r="E441" s="3" t="inlineStr"/>
@@ -16085,17 +16125,17 @@
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card/placeholder-first.svg</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/error-page.scss</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>placeholder-first.svg</t>
+          <t>error-page.scss</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>placeholder-first.svg</t>
+          <t>error-page.scss</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr"/>
@@ -16118,17 +16158,17 @@
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card/placeholder-second-wider.svg</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/svg/error-500.svg</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>placeholder-second-wider.svg</t>
+          <t>error-500.svg</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
         <is>
-          <t>placeholder-second-wider.svg</t>
+          <t>error-500.svg</t>
         </is>
       </c>
       <c r="E443" s="3" t="inlineStr"/>
@@ -16151,17 +16191,17 @@
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/card/placeholder-second.svg</t>
+          <t>docs/appkit4/patterns/source/react/404-500-error-page/error-page-500/svg/logo.svg</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>placeholder-second.svg</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>placeholder-second.svg</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr"/>
@@ -16184,17 +16224,17 @@
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/placeholder-first-wider.svg</t>
+          <t>docs/appkit4/patterns/source/react/card/Card.tsx</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>placeholder-first-wider.svg</t>
+          <t>Card.tsx</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
         <is>
-          <t>placeholder-first-wider.svg</t>
+          <t>Card.tsx</t>
         </is>
       </c>
       <c r="E445" s="3" t="inlineStr"/>
@@ -16217,17 +16257,17 @@
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/placeholder-first.svg</t>
+          <t>docs/appkit4/patterns/source/react/card/CardGrid.tsx</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>placeholder-first.svg</t>
+          <t>CardGrid.tsx</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>placeholder-first.svg</t>
+          <t>CardGrid.tsx</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr"/>
@@ -16250,17 +16290,17 @@
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/placeholder-second-wider.svg</t>
+          <t>docs/appkit4/patterns/source/react/card/card-grid.scss</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>placeholder-second-wider.svg</t>
+          <t>card-grid.scss</t>
         </is>
       </c>
       <c r="D447" s="3" t="inlineStr">
         <is>
-          <t>placeholder-second-wider.svg</t>
+          <t>card-grid.scss</t>
         </is>
       </c>
       <c r="E447" s="3" t="inlineStr"/>
@@ -16283,17 +16323,17 @@
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/card/placeholder-second.svg</t>
+          <t>docs/appkit4/patterns/source/react/card/card.scss</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>placeholder-second.svg</t>
+          <t>card.scss</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>placeholder-second.svg</t>
+          <t>card.scss</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr"/>
@@ -16316,17 +16356,17 @@
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-default/DataListHeader.tsx</t>
+          <t>docs/appkit4/patterns/source/react/card/card/Card.tsx</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>DataListHeader.tsx</t>
+          <t>Card.tsx</t>
         </is>
       </c>
       <c r="D449" s="3" t="inlineStr">
         <is>
-          <t>DataListHeader.tsx</t>
+          <t>Card.tsx</t>
         </is>
       </c>
       <c r="E449" s="3" t="inlineStr"/>
@@ -16349,17 +16389,17 @@
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-default/DataListHeaderDefault.tsx</t>
+          <t>docs/appkit4/patterns/source/react/card/card/CardGrid.tsx</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>DataListHeaderDefault.tsx</t>
+          <t>CardGrid.tsx</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>DataListHeaderDefault.tsx</t>
+          <t>CardGrid.tsx</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr"/>
@@ -16382,17 +16422,17 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-default/datalist-header.scss</t>
+          <t>docs/appkit4/patterns/source/react/card/card/card-grid.scss</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>datalist-header.scss</t>
+          <t>card-grid.scss</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
         <is>
-          <t>datalist-header.scss</t>
+          <t>card-grid.scss</t>
         </is>
       </c>
       <c r="E451" s="3" t="inlineStr"/>
@@ -16415,17 +16455,17 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-solid/DataListHeader.tsx</t>
+          <t>docs/appkit4/patterns/source/react/card/card/card.scss</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>DataListHeader.tsx</t>
+          <t>card.scss</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>DataListHeader.tsx</t>
+          <t>card.scss</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr"/>
@@ -16448,17 +16488,17 @@
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-solid/DataListHeaderSolid.tsx</t>
+          <t>docs/appkit4/patterns/source/react/card/card/placeholder-first-wider.svg</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>DataListHeaderSolid.tsx</t>
+          <t>placeholder-first-wider.svg</t>
         </is>
       </c>
       <c r="D453" s="3" t="inlineStr">
         <is>
-          <t>DataListHeaderSolid.tsx</t>
+          <t>placeholder-first-wider.svg</t>
         </is>
       </c>
       <c r="E453" s="3" t="inlineStr"/>
@@ -16481,17 +16521,17 @@
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-solid/datalist-header.scss</t>
+          <t>docs/appkit4/patterns/source/react/card/card/placeholder-first.svg</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>datalist-header.scss</t>
+          <t>placeholder-first.svg</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>datalist-header.scss</t>
+          <t>placeholder-first.svg</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr"/>
@@ -16514,17 +16554,17 @@
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/delete-confirmation/confirmation-additional/ConfirmationAdditional.tsx</t>
+          <t>docs/appkit4/patterns/source/react/card/card/placeholder-second-wider.svg</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>ConfirmationAdditional.tsx</t>
+          <t>placeholder-second-wider.svg</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
         <is>
-          <t>ConfirmationAdditional.tsx</t>
+          <t>placeholder-second-wider.svg</t>
         </is>
       </c>
       <c r="E455" s="3" t="inlineStr"/>
@@ -16547,17 +16587,17 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/delete-confirmation/confirmation-additional/index.scss</t>
+          <t>docs/appkit4/patterns/source/react/card/card/placeholder-second.svg</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>index.scss</t>
+          <t>placeholder-second.svg</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>index.scss</t>
+          <t>placeholder-second.svg</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr"/>
@@ -16580,17 +16620,17 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/delete-confirmation/confirmation-default/ConfirmationDefault.tsx</t>
+          <t>docs/appkit4/patterns/source/react/card/placeholder-first-wider.svg</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>ConfirmationDefault.tsx</t>
+          <t>placeholder-first-wider.svg</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
         <is>
-          <t>ConfirmationDefault.tsx</t>
+          <t>placeholder-first-wider.svg</t>
         </is>
       </c>
       <c r="E457" s="3" t="inlineStr"/>
@@ -16613,17 +16653,17 @@
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/delete-confirmation/confirmation-default/index.scss</t>
+          <t>docs/appkit4/patterns/source/react/card/placeholder-first.svg</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>index.scss</t>
+          <t>placeholder-first.svg</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>index.scss</t>
+          <t>placeholder-first.svg</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr"/>
@@ -16646,17 +16686,17 @@
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/faqs/faq-default/Faq.tsx</t>
+          <t>docs/appkit4/patterns/source/react/card/placeholder-second-wider.svg</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>Faq.tsx</t>
+          <t>placeholder-second-wider.svg</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
         <is>
-          <t>Faq.tsx</t>
+          <t>placeholder-second-wider.svg</t>
         </is>
       </c>
       <c r="E459" s="3" t="inlineStr"/>
@@ -16679,17 +16719,17 @@
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/faqs/faq-default/FaqDefault.tsx</t>
+          <t>docs/appkit4/patterns/source/react/card/placeholder-second.svg</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>FaqDefault.tsx</t>
+          <t>placeholder-second.svg</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>FaqDefault.tsx</t>
+          <t>placeholder-second.svg</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr"/>
@@ -16712,17 +16752,17 @@
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/faqs/faq-default/faq.scss</t>
+          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-default/DataListHeader.tsx</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>faq.scss</t>
+          <t>DataListHeader.tsx</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
         <is>
-          <t>faq.scss</t>
+          <t>DataListHeader.tsx</t>
         </is>
       </c>
       <c r="E461" s="3" t="inlineStr"/>
@@ -16745,17 +16785,17 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-2col/Form.tsx</t>
+          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-default/DataListHeaderDefault.tsx</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>DataListHeaderDefault.tsx</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>DataListHeaderDefault.tsx</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr"/>
@@ -16778,17 +16818,17 @@
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-2col/FormCol2.tsx</t>
+          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-default/datalist-header.scss</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>FormCol2.tsx</t>
+          <t>datalist-header.scss</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
         <is>
-          <t>FormCol2.tsx</t>
+          <t>datalist-header.scss</t>
         </is>
       </c>
       <c r="E463" s="3" t="inlineStr"/>
@@ -16811,17 +16851,17 @@
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-2col/Language.tsx</t>
+          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-solid/DataListHeader.tsx</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>DataListHeader.tsx</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>DataListHeader.tsx</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr"/>
@@ -16844,17 +16884,17 @@
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-2col/data.ts</t>
+          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-solid/DataListHeaderSolid.tsx</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>data.ts</t>
+          <t>DataListHeaderSolid.tsx</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
         <is>
-          <t>data.ts</t>
+          <t>DataListHeaderSolid.tsx</t>
         </is>
       </c>
       <c r="E465" s="3" t="inlineStr"/>
@@ -16877,17 +16917,17 @@
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-2col/form.scss</t>
+          <t>docs/appkit4/patterns/source/react/data-list-header/data-list-header-solid/datalist-header.scss</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>datalist-header.scss</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>datalist-header.scss</t>
         </is>
       </c>
       <c r="E466" s="3" t="inlineStr"/>
@@ -16910,17 +16950,17 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-2col/useFormValidator.tsx</t>
+          <t>docs/appkit4/patterns/source/react/delete-confirmation/confirmation-additional/ConfirmationAdditional.tsx</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>useFormValidator.tsx</t>
+          <t>ConfirmationAdditional.tsx</t>
         </is>
       </c>
       <c r="D467" s="3" t="inlineStr">
         <is>
-          <t>useFormValidator.tsx</t>
+          <t>ConfirmationAdditional.tsx</t>
         </is>
       </c>
       <c r="E467" s="3" t="inlineStr"/>
@@ -16943,17 +16983,17 @@
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-2col/validators.ts</t>
+          <t>docs/appkit4/patterns/source/react/delete-confirmation/confirmation-additional/index.scss</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>validators.ts</t>
+          <t>index.scss</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
         <is>
-          <t>validators.ts</t>
+          <t>index.scss</t>
         </is>
       </c>
       <c r="E468" s="3" t="inlineStr"/>
@@ -16976,17 +17016,17 @@
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-default/Form.tsx</t>
+          <t>docs/appkit4/patterns/source/react/delete-confirmation/confirmation-default/ConfirmationDefault.tsx</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>ConfirmationDefault.tsx</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>ConfirmationDefault.tsx</t>
         </is>
       </c>
       <c r="E469" s="3" t="inlineStr"/>
@@ -17009,17 +17049,17 @@
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-default/FormDefault.tsx</t>
+          <t>docs/appkit4/patterns/source/react/delete-confirmation/confirmation-default/index.scss</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>FormDefault.tsx</t>
+          <t>index.scss</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>FormDefault.tsx</t>
+          <t>index.scss</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr"/>
@@ -17042,17 +17082,17 @@
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-default/data.ts</t>
+          <t>docs/appkit4/patterns/source/react/faqs/faq-default/Faq.tsx</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>data.ts</t>
+          <t>Faq.tsx</t>
         </is>
       </c>
       <c r="D471" s="3" t="inlineStr">
         <is>
-          <t>data.ts</t>
+          <t>Faq.tsx</t>
         </is>
       </c>
       <c r="E471" s="3" t="inlineStr"/>
@@ -17075,17 +17115,17 @@
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-default/form.scss</t>
+          <t>docs/appkit4/patterns/source/react/faqs/faq-default/FaqDefault.tsx</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>FaqDefault.tsx</t>
         </is>
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>FaqDefault.tsx</t>
         </is>
       </c>
       <c r="E472" s="3" t="inlineStr"/>
@@ -17108,17 +17148,17 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-default/useFormValidator.tsx</t>
+          <t>docs/appkit4/patterns/source/react/faqs/faq-default/faq.scss</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>useFormValidator.tsx</t>
+          <t>faq.scss</t>
         </is>
       </c>
       <c r="D473" s="3" t="inlineStr">
         <is>
-          <t>useFormValidator.tsx</t>
+          <t>faq.scss</t>
         </is>
       </c>
       <c r="E473" s="3" t="inlineStr"/>
@@ -17141,17 +17181,17 @@
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-default/validators.ts</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-2col/Form.tsx</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>validators.ts</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>validators.ts</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr"/>
@@ -17174,17 +17214,17 @@
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-login/Form.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-2col/FormCol2.tsx</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>FormCol2.tsx</t>
         </is>
       </c>
       <c r="D475" s="3" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>FormCol2.tsx</t>
         </is>
       </c>
       <c r="E475" s="3" t="inlineStr"/>
@@ -17207,17 +17247,17 @@
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-login/FormLogin.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-2col/Language.tsx</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>FormLogin.tsx</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>FormLogin.tsx</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr"/>
@@ -17240,17 +17280,17 @@
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-login/Language.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-2col/data.ts</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>data.ts</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>data.ts</t>
         </is>
       </c>
       <c r="E477" s="3" t="inlineStr"/>
@@ -17273,17 +17313,17 @@
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-login/data.ts</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-2col/form.scss</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>data.ts</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>data.ts</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="E478" s="3" t="inlineStr"/>
@@ -17306,17 +17346,17 @@
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-login/form.scss</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-2col/useFormValidator.tsx</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>useFormValidator.tsx</t>
         </is>
       </c>
       <c r="D479" s="3" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>useFormValidator.tsx</t>
         </is>
       </c>
       <c r="E479" s="3" t="inlineStr"/>
@@ -17339,17 +17379,17 @@
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-login/useFormValidator.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-2col/validators.ts</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>useFormValidator.tsx</t>
+          <t>validators.ts</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>useFormValidator.tsx</t>
+          <t>validators.ts</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr"/>
@@ -17372,17 +17412,17 @@
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-login/validators.ts</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-default/Form.tsx</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>validators.ts</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="D481" s="3" t="inlineStr">
         <is>
-          <t>validators.ts</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="E481" s="3" t="inlineStr"/>
@@ -17405,17 +17445,17 @@
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-register/Form.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-default/FormDefault.tsx</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>FormDefault.tsx</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>FormDefault.tsx</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr"/>
@@ -17438,17 +17478,17 @@
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-register/FormRegister.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-default/data.ts</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>FormRegister.tsx</t>
+          <t>data.ts</t>
         </is>
       </c>
       <c r="D483" s="3" t="inlineStr">
         <is>
-          <t>FormRegister.tsx</t>
+          <t>data.ts</t>
         </is>
       </c>
       <c r="E483" s="3" t="inlineStr"/>
@@ -17471,17 +17511,17 @@
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-register/Language.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-default/form.scss</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr"/>
@@ -17504,17 +17544,17 @@
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-register/data.ts</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-default/useFormValidator.tsx</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>data.ts</t>
+          <t>useFormValidator.tsx</t>
         </is>
       </c>
       <c r="D485" s="3" t="inlineStr">
         <is>
-          <t>data.ts</t>
+          <t>useFormValidator.tsx</t>
         </is>
       </c>
       <c r="E485" s="3" t="inlineStr"/>
@@ -17537,17 +17577,17 @@
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-register/form.scss</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-default/validators.ts</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>validators.ts</t>
         </is>
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>validators.ts</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr"/>
@@ -17570,17 +17610,17 @@
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-register/useFormValidator.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-login/Form.tsx</t>
         </is>
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>useFormValidator.tsx</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="D487" s="3" t="inlineStr">
         <is>
-          <t>useFormValidator.tsx</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="E487" s="3" t="inlineStr"/>
@@ -17603,17 +17643,17 @@
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/form-template/form-register/validators.ts</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-login/FormLogin.tsx</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>validators.ts</t>
+          <t>FormLogin.tsx</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>validators.ts</t>
+          <t>FormLogin.tsx</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr"/>
@@ -17636,17 +17676,17 @@
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-left-right/HeroBanner.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-login/Language.tsx</t>
         </is>
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>HeroBanner.tsx</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="D489" s="3" t="inlineStr">
         <is>
-          <t>HeroBanner.tsx</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="E489" s="3" t="inlineStr"/>
@@ -17669,17 +17709,17 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-left-right/HeroBannerNeutralLeftRight.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-login/data.ts</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>HeroBannerNeutralLeftRight.tsx</t>
+          <t>data.ts</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>HeroBannerNeutralLeftRight.tsx</t>
+          <t>data.ts</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr"/>
@@ -17702,17 +17742,17 @@
       </c>
       <c r="B491" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-left-right/hero-banner.scss</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-login/form.scss</t>
         </is>
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>hero-banner.scss</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="D491" s="3" t="inlineStr">
         <is>
-          <t>hero-banner.scss</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="E491" s="3" t="inlineStr"/>
@@ -17735,17 +17775,17 @@
       </c>
       <c r="B492" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-left-right/svg/discover.svg</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-login/useFormValidator.tsx</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>discover.svg</t>
+          <t>useFormValidator.tsx</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>discover.svg</t>
+          <t>useFormValidator.tsx</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr"/>
@@ -17768,17 +17808,17 @@
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-right-left/HeroBanner.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-login/validators.ts</t>
         </is>
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>HeroBanner.tsx</t>
+          <t>validators.ts</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
         <is>
-          <t>HeroBanner.tsx</t>
+          <t>validators.ts</t>
         </is>
       </c>
       <c r="E493" s="3" t="inlineStr"/>
@@ -17801,17 +17841,17 @@
       </c>
       <c r="B494" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-right-left/HeroBannerNeutralRightLeft.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-register/Form.tsx</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>HeroBannerNeutralRightLeft.tsx</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>HeroBannerNeutralRightLeft.tsx</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr"/>
@@ -17834,17 +17874,17 @@
       </c>
       <c r="B495" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-right-left/hero-banner.scss</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-register/FormRegister.tsx</t>
         </is>
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>hero-banner.scss</t>
+          <t>FormRegister.tsx</t>
         </is>
       </c>
       <c r="D495" s="3" t="inlineStr">
         <is>
-          <t>hero-banner.scss</t>
+          <t>FormRegister.tsx</t>
         </is>
       </c>
       <c r="E495" s="3" t="inlineStr"/>
@@ -17867,17 +17907,17 @@
       </c>
       <c r="B496" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-right-left/svg/discover.svg</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-register/Language.tsx</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>discover.svg</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>discover.svg</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr"/>
@@ -17900,17 +17940,17 @@
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-left-right/HeroBanner.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-register/data.ts</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>HeroBanner.tsx</t>
+          <t>data.ts</t>
         </is>
       </c>
       <c r="D497" s="3" t="inlineStr">
         <is>
-          <t>HeroBanner.tsx</t>
+          <t>data.ts</t>
         </is>
       </c>
       <c r="E497" s="3" t="inlineStr"/>
@@ -17933,17 +17973,17 @@
       </c>
       <c r="B498" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-left-right/HeroBannerPrimaryLeftRight.tsx</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-register/form.scss</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>HeroBannerPrimaryLeftRight.tsx</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
-          <t>HeroBannerPrimaryLeftRight.tsx</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="E498" s="3" t="inlineStr"/>
@@ -17966,17 +18006,17 @@
       </c>
       <c r="B499" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-left-right/hero-banner.scss</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-register/useFormValidator.tsx</t>
         </is>
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>hero-banner.scss</t>
+          <t>useFormValidator.tsx</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
         <is>
-          <t>hero-banner.scss</t>
+          <t>useFormValidator.tsx</t>
         </is>
       </c>
       <c r="E499" s="3" t="inlineStr"/>
@@ -17999,17 +18039,17 @@
       </c>
       <c r="B500" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-left-right/svg/discover.svg</t>
+          <t>docs/appkit4/patterns/source/react/form-template/form-register/validators.ts</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>discover.svg</t>
+          <t>validators.ts</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>discover.svg</t>
+          <t>validators.ts</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr"/>
@@ -18032,7 +18072,7 @@
       </c>
       <c r="B501" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-right-left/HeroBanner.tsx</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-left-right/HeroBanner.tsx</t>
         </is>
       </c>
       <c r="C501" s="2" t="inlineStr">
@@ -18065,17 +18105,17 @@
       </c>
       <c r="B502" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-right-left/HeroBannerPrimaryRightLeft.tsx</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-left-right/HeroBannerNeutralLeftRight.tsx</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>HeroBannerPrimaryRightLeft.tsx</t>
+          <t>HeroBannerNeutralLeftRight.tsx</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>HeroBannerPrimaryRightLeft.tsx</t>
+          <t>HeroBannerNeutralLeftRight.tsx</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr"/>
@@ -18098,7 +18138,7 @@
       </c>
       <c r="B503" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-right-left/hero-banner.scss</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-left-right/hero-banner.scss</t>
         </is>
       </c>
       <c r="C503" s="2" t="inlineStr">
@@ -18131,7 +18171,7 @@
       </c>
       <c r="B504" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-right-left/svg/discover.svg</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-left-right/svg/discover.svg</t>
         </is>
       </c>
       <c r="C504" s="2" t="inlineStr">
@@ -18164,17 +18204,17 @@
       </c>
       <c r="B505" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/Form.tsx</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-right-left/HeroBanner.tsx</t>
         </is>
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>HeroBanner.tsx</t>
         </is>
       </c>
       <c r="D505" s="3" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>HeroBanner.tsx</t>
         </is>
       </c>
       <c r="E505" s="3" t="inlineStr"/>
@@ -18197,17 +18237,17 @@
       </c>
       <c r="B506" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/Language.tsx</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-right-left/HeroBannerNeutralRightLeft.tsx</t>
         </is>
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>HeroBannerNeutralRightLeft.tsx</t>
         </is>
       </c>
       <c r="D506" s="3" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>HeroBannerNeutralRightLeft.tsx</t>
         </is>
       </c>
       <c r="E506" s="3" t="inlineStr"/>
@@ -18230,17 +18270,17 @@
       </c>
       <c r="B507" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/Login.tsx</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-right-left/hero-banner.scss</t>
         </is>
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>Login.tsx</t>
+          <t>hero-banner.scss</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
         <is>
-          <t>Login.tsx</t>
+          <t>hero-banner.scss</t>
         </is>
       </c>
       <c r="E507" s="3" t="inlineStr"/>
@@ -18263,17 +18303,17 @@
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/LoginDefault.tsx</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-neutral-right-left/svg/discover.svg</t>
         </is>
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>LoginDefault.tsx</t>
+          <t>discover.svg</t>
         </is>
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>LoginDefault.tsx</t>
+          <t>discover.svg</t>
         </is>
       </c>
       <c r="E508" s="3" t="inlineStr"/>
@@ -18296,17 +18336,17 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/form.scss</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-left-right/HeroBanner.tsx</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>HeroBanner.tsx</t>
         </is>
       </c>
       <c r="D509" s="3" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>HeroBanner.tsx</t>
         </is>
       </c>
       <c r="E509" s="3" t="inlineStr"/>
@@ -18329,17 +18369,17 @@
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/login-default.scss</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-left-right/HeroBannerPrimaryLeftRight.tsx</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>login-default.scss</t>
+          <t>HeroBannerPrimaryLeftRight.tsx</t>
         </is>
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>login-default.scss</t>
+          <t>HeroBannerPrimaryLeftRight.tsx</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr"/>
@@ -18362,17 +18402,17 @@
       </c>
       <c r="B511" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/login.scss</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-left-right/hero-banner.scss</t>
         </is>
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>login.scss</t>
+          <t>hero-banner.scss</t>
         </is>
       </c>
       <c r="D511" s="3" t="inlineStr">
         <is>
-          <t>login.scss</t>
+          <t>hero-banner.scss</t>
         </is>
       </c>
       <c r="E511" s="3" t="inlineStr"/>
@@ -18395,17 +18435,17 @@
       </c>
       <c r="B512" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/svg/logo-white.svg</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-left-right/svg/discover.svg</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>logo-white.svg</t>
+          <t>discover.svg</t>
         </is>
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>logo-white.svg</t>
+          <t>discover.svg</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr"/>
@@ -18428,17 +18468,17 @@
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/svg/logo.svg</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-right-left/HeroBanner.tsx</t>
         </is>
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>HeroBanner.tsx</t>
         </is>
       </c>
       <c r="D513" s="3" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>HeroBanner.tsx</t>
         </is>
       </c>
       <c r="E513" s="3" t="inlineStr"/>
@@ -18461,17 +18501,17 @@
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-default/svg/svg-risk-management-1.svg</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-right-left/HeroBannerPrimaryRightLeft.tsx</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>svg-risk-management-1.svg</t>
+          <t>HeroBannerPrimaryRightLeft.tsx</t>
         </is>
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>svg-risk-management-1.svg</t>
+          <t>HeroBannerPrimaryRightLeft.tsx</t>
         </is>
       </c>
       <c r="E514" s="3" t="inlineStr"/>
@@ -18494,17 +18534,17 @@
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/Form.tsx</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-right-left/hero-banner.scss</t>
         </is>
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>hero-banner.scss</t>
         </is>
       </c>
       <c r="D515" s="3" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>hero-banner.scss</t>
         </is>
       </c>
       <c r="E515" s="3" t="inlineStr"/>
@@ -18527,17 +18567,17 @@
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/Language.tsx</t>
+          <t>docs/appkit4/patterns/source/react/hero-banner/hero-banner-primary-right-left/svg/discover.svg</t>
         </is>
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>discover.svg</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>discover.svg</t>
         </is>
       </c>
       <c r="E516" s="3" t="inlineStr"/>
@@ -18560,17 +18600,17 @@
       </c>
       <c r="B517" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/Login.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/Form.tsx</t>
         </is>
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>Login.tsx</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="D517" s="3" t="inlineStr">
         <is>
-          <t>Login.tsx</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="E517" s="3" t="inlineStr"/>
@@ -18593,17 +18633,17 @@
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/LoginFractional.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/Language.tsx</t>
         </is>
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>LoginFractional.tsx</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="D518" s="3" t="inlineStr">
         <is>
-          <t>LoginFractional.tsx</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="E518" s="3" t="inlineStr"/>
@@ -18626,17 +18666,17 @@
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/form.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/Login.tsx</t>
         </is>
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>Login.tsx</t>
         </is>
       </c>
       <c r="D519" s="3" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>Login.tsx</t>
         </is>
       </c>
       <c r="E519" s="3" t="inlineStr"/>
@@ -18659,17 +18699,17 @@
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/login-fractional.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/LoginDefault.tsx</t>
         </is>
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>login-fractional.scss</t>
+          <t>LoginDefault.tsx</t>
         </is>
       </c>
       <c r="D520" s="3" t="inlineStr">
         <is>
-          <t>login-fractional.scss</t>
+          <t>LoginDefault.tsx</t>
         </is>
       </c>
       <c r="E520" s="3" t="inlineStr"/>
@@ -18692,17 +18732,17 @@
       </c>
       <c r="B521" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/login.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/form.scss</t>
         </is>
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>login.scss</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="D521" s="3" t="inlineStr">
         <is>
-          <t>login.scss</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="E521" s="3" t="inlineStr"/>
@@ -18725,17 +18765,17 @@
       </c>
       <c r="B522" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/svg/logo-white.svg</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/login-default.scss</t>
         </is>
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>logo-white.svg</t>
+          <t>login-default.scss</t>
         </is>
       </c>
       <c r="D522" s="3" t="inlineStr">
         <is>
-          <t>logo-white.svg</t>
+          <t>login-default.scss</t>
         </is>
       </c>
       <c r="E522" s="3" t="inlineStr"/>
@@ -18758,17 +18798,17 @@
       </c>
       <c r="B523" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/svg/logo.svg</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/login.scss</t>
         </is>
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>login.scss</t>
         </is>
       </c>
       <c r="D523" s="3" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>login.scss</t>
         </is>
       </c>
       <c r="E523" s="3" t="inlineStr"/>
@@ -18791,17 +18831,17 @@
       </c>
       <c r="B524" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/svg/svg-risk-management-fractional-1.svg</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/svg/logo-white.svg</t>
         </is>
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>svg-risk-management-fractional-1.svg</t>
+          <t>logo-white.svg</t>
         </is>
       </c>
       <c r="D524" s="3" t="inlineStr">
         <is>
-          <t>svg-risk-management-fractional-1.svg</t>
+          <t>logo-white.svg</t>
         </is>
       </c>
       <c r="E524" s="3" t="inlineStr"/>
@@ -18824,17 +18864,17 @@
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/svg/svg-workforce-experience-fractional-1.svg</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/svg/logo.svg</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>svg-workforce-experience-fractional-1.svg</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="D525" s="3" t="inlineStr">
         <is>
-          <t>svg-workforce-experience-fractional-1.svg</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="E525" s="3" t="inlineStr"/>
@@ -18857,17 +18897,17 @@
       </c>
       <c r="B526" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/Form.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-default/svg/svg-risk-management-1.svg</t>
         </is>
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>svg-risk-management-1.svg</t>
         </is>
       </c>
       <c r="D526" s="3" t="inlineStr">
         <is>
-          <t>Form.tsx</t>
+          <t>svg-risk-management-1.svg</t>
         </is>
       </c>
       <c r="E526" s="3" t="inlineStr"/>
@@ -18890,17 +18930,17 @@
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/Language.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/Form.tsx</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="D527" s="3" t="inlineStr">
         <is>
-          <t>Language.tsx</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="E527" s="3" t="inlineStr"/>
@@ -18923,17 +18963,17 @@
       </c>
       <c r="B528" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/Login.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/Language.tsx</t>
         </is>
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>Login.tsx</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="D528" s="3" t="inlineStr">
         <is>
-          <t>Login.tsx</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="E528" s="3" t="inlineStr"/>
@@ -18956,17 +18996,17 @@
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/LoginGeneric.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/Login.tsx</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>LoginGeneric.tsx</t>
+          <t>Login.tsx</t>
         </is>
       </c>
       <c r="D529" s="3" t="inlineStr">
         <is>
-          <t>LoginGeneric.tsx</t>
+          <t>Login.tsx</t>
         </is>
       </c>
       <c r="E529" s="3" t="inlineStr"/>
@@ -18989,17 +19029,17 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/form.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/LoginFractional.tsx</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>LoginFractional.tsx</t>
         </is>
       </c>
       <c r="D530" s="3" t="inlineStr">
         <is>
-          <t>form.scss</t>
+          <t>LoginFractional.tsx</t>
         </is>
       </c>
       <c r="E530" s="3" t="inlineStr"/>
@@ -19022,17 +19062,17 @@
       </c>
       <c r="B531" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/login-generic.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/form.scss</t>
         </is>
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>login-generic.scss</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="D531" s="3" t="inlineStr">
         <is>
-          <t>login-generic.scss</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="E531" s="3" t="inlineStr"/>
@@ -19055,17 +19095,17 @@
       </c>
       <c r="B532" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/login.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/login-fractional.scss</t>
         </is>
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>login.scss</t>
+          <t>login-fractional.scss</t>
         </is>
       </c>
       <c r="D532" s="3" t="inlineStr">
         <is>
-          <t>login.scss</t>
+          <t>login-fractional.scss</t>
         </is>
       </c>
       <c r="E532" s="3" t="inlineStr"/>
@@ -19088,17 +19128,17 @@
       </c>
       <c r="B533" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/svg/logo-white.svg</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/login.scss</t>
         </is>
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>logo-white.svg</t>
+          <t>login.scss</t>
         </is>
       </c>
       <c r="D533" s="3" t="inlineStr">
         <is>
-          <t>logo-white.svg</t>
+          <t>login.scss</t>
         </is>
       </c>
       <c r="E533" s="3" t="inlineStr"/>
@@ -19121,17 +19161,17 @@
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/svg/logo.svg</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/svg/logo-white.svg</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>logo-white.svg</t>
         </is>
       </c>
       <c r="D534" s="3" t="inlineStr">
         <is>
-          <t>logo.svg</t>
+          <t>logo-white.svg</t>
         </is>
       </c>
       <c r="E534" s="3" t="inlineStr"/>
@@ -19154,17 +19194,17 @@
       </c>
       <c r="B535" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/login-page/login-generic/svg/svg-generic-1.svg</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/svg/logo.svg</t>
         </is>
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>svg-generic-1.svg</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="D535" s="3" t="inlineStr">
         <is>
-          <t>svg-generic-1.svg</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="E535" s="3" t="inlineStr"/>
@@ -19187,17 +19227,17 @@
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/FloatButton.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/svg/svg-risk-management-fractional-1.svg</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>FloatButton.tsx</t>
+          <t>svg-risk-management-fractional-1.svg</t>
         </is>
       </c>
       <c r="D536" s="3" t="inlineStr">
         <is>
-          <t>FloatButton.tsx</t>
+          <t>svg-risk-management-fractional-1.svg</t>
         </is>
       </c>
       <c r="E536" s="3" t="inlineStr"/>
@@ -19220,17 +19260,17 @@
       </c>
       <c r="B537" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/MultipleActionMenu.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-fractional/svg/svg-workforce-experience-fractional-1.svg</t>
         </is>
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>MultipleActionMenu.tsx</t>
+          <t>svg-workforce-experience-fractional-1.svg</t>
         </is>
       </c>
       <c r="D537" s="3" t="inlineStr">
         <is>
-          <t>MultipleActionMenu.tsx</t>
+          <t>svg-workforce-experience-fractional-1.svg</t>
         </is>
       </c>
       <c r="E537" s="3" t="inlineStr"/>
@@ -19253,17 +19293,17 @@
       </c>
       <c r="B538" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/float-button.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/Form.tsx</t>
         </is>
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>float-button.scss</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="D538" s="3" t="inlineStr">
         <is>
-          <t>float-button.scss</t>
+          <t>Form.tsx</t>
         </is>
       </c>
       <c r="E538" s="3" t="inlineStr"/>
@@ -19286,17 +19326,17 @@
       </c>
       <c r="B539" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/multiple-action-menu.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/Language.tsx</t>
         </is>
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>multiple-action-menu.scss</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="D539" s="3" t="inlineStr">
         <is>
-          <t>multiple-action-menu.scss</t>
+          <t>Language.tsx</t>
         </is>
       </c>
       <c r="E539" s="3" t="inlineStr"/>
@@ -19319,17 +19359,17 @@
       </c>
       <c r="B540" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/useClickOutside.ts</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/Login.tsx</t>
         </is>
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>useClickOutside.ts</t>
+          <t>Login.tsx</t>
         </is>
       </c>
       <c r="D540" s="3" t="inlineStr">
         <is>
-          <t>useClickOutside.ts</t>
+          <t>Login.tsx</t>
         </is>
       </c>
       <c r="E540" s="3" t="inlineStr"/>
@@ -19352,17 +19392,17 @@
       </c>
       <c r="B541" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-anchors/page-anchors-default/PageAnchors.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/LoginGeneric.tsx</t>
         </is>
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>PageAnchors.tsx</t>
+          <t>LoginGeneric.tsx</t>
         </is>
       </c>
       <c r="D541" s="3" t="inlineStr">
         <is>
-          <t>PageAnchors.tsx</t>
+          <t>LoginGeneric.tsx</t>
         </is>
       </c>
       <c r="E541" s="3" t="inlineStr"/>
@@ -19385,17 +19425,17 @@
       </c>
       <c r="B542" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-anchors/page-anchors-default/PageAnchorsDefault.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/form.scss</t>
         </is>
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>PageAnchorsDefault.tsx</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="D542" s="3" t="inlineStr">
         <is>
-          <t>PageAnchorsDefault.tsx</t>
+          <t>form.scss</t>
         </is>
       </c>
       <c r="E542" s="3" t="inlineStr"/>
@@ -19418,17 +19458,17 @@
       </c>
       <c r="B543" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-anchors/page-anchors-default/page-anchors.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/login-generic.scss</t>
         </is>
       </c>
       <c r="C543" s="2" t="inlineStr">
         <is>
-          <t>page-anchors.scss</t>
+          <t>login-generic.scss</t>
         </is>
       </c>
       <c r="D543" s="3" t="inlineStr">
         <is>
-          <t>page-anchors.scss</t>
+          <t>login-generic.scss</t>
         </is>
       </c>
       <c r="E543" s="3" t="inlineStr"/>
@@ -19451,17 +19491,17 @@
       </c>
       <c r="B544" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-large/PageHeaderWithBackButton.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/login.scss</t>
         </is>
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButton.tsx</t>
+          <t>login.scss</t>
         </is>
       </c>
       <c r="D544" s="3" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButton.tsx</t>
+          <t>login.scss</t>
         </is>
       </c>
       <c r="E544" s="3" t="inlineStr"/>
@@ -19484,17 +19524,17 @@
       </c>
       <c r="B545" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-large/PageHeaderWithBackButtonLarge.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/svg/logo-white.svg</t>
         </is>
       </c>
       <c r="C545" s="2" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButtonLarge.tsx</t>
+          <t>logo-white.svg</t>
         </is>
       </c>
       <c r="D545" s="3" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButtonLarge.tsx</t>
+          <t>logo-white.svg</t>
         </is>
       </c>
       <c r="E545" s="3" t="inlineStr"/>
@@ -19517,17 +19557,17 @@
       </c>
       <c r="B546" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-large/header-with-back.scss</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/svg/logo.svg</t>
         </is>
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>header-with-back.scss</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="D546" s="3" t="inlineStr">
         <is>
-          <t>header-with-back.scss</t>
+          <t>logo.svg</t>
         </is>
       </c>
       <c r="E546" s="3" t="inlineStr"/>
@@ -19550,17 +19590,17 @@
       </c>
       <c r="B547" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-medium/PageHeaderWithBackButton.tsx</t>
+          <t>docs/appkit4/patterns/source/react/login-page/login-generic/svg/svg-generic-1.svg</t>
         </is>
       </c>
       <c r="C547" s="2" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButton.tsx</t>
+          <t>svg-generic-1.svg</t>
         </is>
       </c>
       <c r="D547" s="3" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButton.tsx</t>
+          <t>svg-generic-1.svg</t>
         </is>
       </c>
       <c r="E547" s="3" t="inlineStr"/>
@@ -19583,17 +19623,17 @@
       </c>
       <c r="B548" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-medium/PageHeaderWithBackButtonMedium.tsx</t>
+          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/FloatButton.tsx</t>
         </is>
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButtonMedium.tsx</t>
+          <t>FloatButton.tsx</t>
         </is>
       </c>
       <c r="D548" s="3" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButtonMedium.tsx</t>
+          <t>FloatButton.tsx</t>
         </is>
       </c>
       <c r="E548" s="3" t="inlineStr"/>
@@ -19616,17 +19656,17 @@
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-medium/header-with-back.scss</t>
+          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/MultipleActionMenu.tsx</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
         <is>
-          <t>header-with-back.scss</t>
+          <t>MultipleActionMenu.tsx</t>
         </is>
       </c>
       <c r="D549" s="3" t="inlineStr">
         <is>
-          <t>header-with-back.scss</t>
+          <t>MultipleActionMenu.tsx</t>
         </is>
       </c>
       <c r="E549" s="3" t="inlineStr"/>
@@ -19649,17 +19689,17 @@
       </c>
       <c r="B550" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-small/PageHeaderWithBackButton.tsx</t>
+          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/float-button.scss</t>
         </is>
       </c>
       <c r="C550" s="2" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButton.tsx</t>
+          <t>float-button.scss</t>
         </is>
       </c>
       <c r="D550" s="3" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButton.tsx</t>
+          <t>float-button.scss</t>
         </is>
       </c>
       <c r="E550" s="3" t="inlineStr"/>
@@ -19682,17 +19722,17 @@
       </c>
       <c r="B551" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-small/PageHeaderWithBackButtonSmall.tsx</t>
+          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/multiple-action-menu.scss</t>
         </is>
       </c>
       <c r="C551" s="2" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButtonSmall.tsx</t>
+          <t>multiple-action-menu.scss</t>
         </is>
       </c>
       <c r="D551" s="3" t="inlineStr">
         <is>
-          <t>PageHeaderWithBackButtonSmall.tsx</t>
+          <t>multiple-action-menu.scss</t>
         </is>
       </c>
       <c r="E551" s="3" t="inlineStr"/>
@@ -19715,17 +19755,17 @@
       </c>
       <c r="B552" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-small/header-with-back.scss</t>
+          <t>docs/appkit4/patterns/source/react/multi-purpose-action-menu/multiple-action-menu/useClickOutside.ts</t>
         </is>
       </c>
       <c r="C552" s="2" t="inlineStr">
         <is>
-          <t>header-with-back.scss</t>
+          <t>useClickOutside.ts</t>
         </is>
       </c>
       <c r="D552" s="3" t="inlineStr">
         <is>
-          <t>header-with-back.scss</t>
+          <t>useClickOutside.ts</t>
         </is>
       </c>
       <c r="E552" s="3" t="inlineStr"/>
@@ -19748,17 +19788,17 @@
       </c>
       <c r="B553" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/search-filter/search-filter-solid/SearchFilter.tsx</t>
+          <t>docs/appkit4/patterns/source/react/page-anchors/page-anchors-default/PageAnchors.tsx</t>
         </is>
       </c>
       <c r="C553" s="2" t="inlineStr">
         <is>
-          <t>SearchFilter.tsx</t>
+          <t>PageAnchors.tsx</t>
         </is>
       </c>
       <c r="D553" s="3" t="inlineStr">
         <is>
-          <t>SearchFilter.tsx</t>
+          <t>PageAnchors.tsx</t>
         </is>
       </c>
       <c r="E553" s="3" t="inlineStr"/>
@@ -19781,17 +19821,17 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/search-filter/search-filter-solid/SearchFilterSolid.tsx</t>
+          <t>docs/appkit4/patterns/source/react/page-anchors/page-anchors-default/PageAnchorsDefault.tsx</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>SearchFilterSolid.tsx</t>
+          <t>PageAnchorsDefault.tsx</t>
         </is>
       </c>
       <c r="D554" s="3" t="inlineStr">
         <is>
-          <t>SearchFilterSolid.tsx</t>
+          <t>PageAnchorsDefault.tsx</t>
         </is>
       </c>
       <c r="E554" s="3" t="inlineStr"/>
@@ -19814,17 +19854,17 @@
       </c>
       <c r="B555" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/source/react/search-filter/search-filter-solid/search-filter.scss</t>
+          <t>docs/appkit4/patterns/source/react/page-anchors/page-anchors-default/page-anchors.scss</t>
         </is>
       </c>
       <c r="C555" s="2" t="inlineStr">
         <is>
-          <t>search-filter.scss</t>
+          <t>page-anchors.scss</t>
         </is>
       </c>
       <c r="D555" s="3" t="inlineStr">
         <is>
-          <t>search-filter.scss</t>
+          <t>page-anchors.scss</t>
         </is>
       </c>
       <c r="E555" s="3" t="inlineStr"/>
@@ -19847,23 +19887,23 @@
       </c>
       <c r="B556" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/patterns/table-row-actions.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-large/PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>table-row-actions.md</t>
+          <t>PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="D556" s="3" t="inlineStr">
         <is>
-          <t>table-row-actions.md</t>
+          <t>PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="E556" s="3" t="inlineStr"/>
-      <c r="F556" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G556" s="2" t="inlineStr">
@@ -19880,23 +19920,23 @@
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/references/README.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-large/PageHeaderWithBackButtonLarge.tsx</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>PageHeaderWithBackButtonLarge.tsx</t>
         </is>
       </c>
       <c r="D557" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>PageHeaderWithBackButtonLarge.tsx</t>
         </is>
       </c>
       <c r="E557" s="3" t="inlineStr"/>
-      <c r="F557" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G557" s="2" t="inlineStr">
@@ -19913,23 +19953,23 @@
       </c>
       <c r="B558" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/references/offline-archive.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-large/header-with-back.scss</t>
         </is>
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>offline-archive.md</t>
+          <t>header-with-back.scss</t>
         </is>
       </c>
       <c r="D558" s="3" t="inlineStr">
         <is>
-          <t>offline-archive.md</t>
+          <t>header-with-back.scss</t>
         </is>
       </c>
       <c r="E558" s="3" t="inlineStr"/>
-      <c r="F558" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G558" s="2" t="inlineStr">
@@ -19946,23 +19986,23 @@
       </c>
       <c r="B559" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/references/portal-links.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-medium/PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="C559" s="2" t="inlineStr">
         <is>
-          <t>portal-links.md</t>
+          <t>PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="D559" s="3" t="inlineStr">
         <is>
-          <t>portal-links.md</t>
+          <t>PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="E559" s="3" t="inlineStr"/>
-      <c r="F559" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G559" s="2" t="inlineStr">
@@ -19979,23 +20019,23 @@
       </c>
       <c r="B560" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/styles/README.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-medium/PageHeaderWithBackButtonMedium.tsx</t>
         </is>
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>PageHeaderWithBackButtonMedium.tsx</t>
         </is>
       </c>
       <c r="D560" s="3" t="inlineStr">
         <is>
-          <t>README.md</t>
+          <t>PageHeaderWithBackButtonMedium.tsx</t>
         </is>
       </c>
       <c r="E560" s="3" t="inlineStr"/>
-      <c r="F560" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G560" s="2" t="inlineStr">
@@ -20012,23 +20052,23 @@
       </c>
       <c r="B561" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/styles/colors.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-medium/header-with-back.scss</t>
         </is>
       </c>
       <c r="C561" s="2" t="inlineStr">
         <is>
-          <t>colors.md</t>
+          <t>header-with-back.scss</t>
         </is>
       </c>
       <c r="D561" s="3" t="inlineStr">
         <is>
-          <t>colors.md</t>
+          <t>header-with-back.scss</t>
         </is>
       </c>
       <c r="E561" s="3" t="inlineStr"/>
-      <c r="F561" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G561" s="2" t="inlineStr">
@@ -20045,23 +20085,23 @@
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/styles/elevation.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-small/PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>elevation.md</t>
+          <t>PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="D562" s="3" t="inlineStr">
         <is>
-          <t>elevation.md</t>
+          <t>PageHeaderWithBackButton.tsx</t>
         </is>
       </c>
       <c r="E562" s="3" t="inlineStr"/>
-      <c r="F562" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G562" s="2" t="inlineStr">
@@ -20078,23 +20118,23 @@
       </c>
       <c r="B563" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/styles/grid.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-small/PageHeaderWithBackButtonSmall.tsx</t>
         </is>
       </c>
       <c r="C563" s="2" t="inlineStr">
         <is>
-          <t>grid.md</t>
+          <t>PageHeaderWithBackButtonSmall.tsx</t>
         </is>
       </c>
       <c r="D563" s="3" t="inlineStr">
         <is>
-          <t>grid.md</t>
+          <t>PageHeaderWithBackButtonSmall.tsx</t>
         </is>
       </c>
       <c r="E563" s="3" t="inlineStr"/>
-      <c r="F563" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G563" s="2" t="inlineStr">
@@ -20111,23 +20151,23 @@
       </c>
       <c r="B564" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/styles/styles.md</t>
+          <t>docs/appkit4/patterns/source/react/page-header-with-back-button/page-header-with-back-button-small/header-with-back.scss</t>
         </is>
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>styles.md</t>
+          <t>header-with-back.scss</t>
         </is>
       </c>
       <c r="D564" s="3" t="inlineStr">
         <is>
-          <t>styles.md</t>
+          <t>header-with-back.scss</t>
         </is>
       </c>
       <c r="E564" s="3" t="inlineStr"/>
-      <c r="F564" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G564" s="2" t="inlineStr">
@@ -20144,23 +20184,23 @@
       </c>
       <c r="B565" s="2" t="inlineStr">
         <is>
-          <t>docs/appkit4/styles/typography.md</t>
+          <t>docs/appkit4/patterns/source/react/search-filter/search-filter-solid/SearchFilter.tsx</t>
         </is>
       </c>
       <c r="C565" s="2" t="inlineStr">
         <is>
-          <t>typography.md</t>
+          <t>SearchFilter.tsx</t>
         </is>
       </c>
       <c r="D565" s="3" t="inlineStr">
         <is>
-          <t>typography.md</t>
+          <t>SearchFilter.tsx</t>
         </is>
       </c>
       <c r="E565" s="3" t="inlineStr"/>
-      <c r="F565" s="4" t="inlineStr">
-        <is>
-          <t>English</t>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G565" s="2" t="inlineStr">
@@ -20172,22 +20212,22 @@
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>AppKit (UI library)</t>
         </is>
       </c>
       <c r="B566" s="2" t="inlineStr">
         <is>
-          <t>.editorconfig</t>
+          <t>docs/appkit4/patterns/source/react/search-filter/search-filter-solid/SearchFilterSolid.tsx</t>
         </is>
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>.editorconfig</t>
+          <t>SearchFilterSolid.tsx</t>
         </is>
       </c>
       <c r="D566" s="3" t="inlineStr">
         <is>
-          <t>.editorconfig</t>
+          <t>SearchFilterSolid.tsx</t>
         </is>
       </c>
       <c r="E566" s="3" t="inlineStr"/>
@@ -20198,12 +20238,408 @@
       </c>
       <c r="G566" s="2" t="inlineStr">
         <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/patterns/source/react/search-filter/search-filter-solid/search-filter.scss</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>search-filter.scss</t>
+        </is>
+      </c>
+      <c r="D567" s="3" t="inlineStr">
+        <is>
+          <t>search-filter.scss</t>
+        </is>
+      </c>
+      <c r="E567" s="3" t="inlineStr"/>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/patterns/table-row-actions.md</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>table-row-actions.md</t>
+        </is>
+      </c>
+      <c r="D568" s="3" t="inlineStr">
+        <is>
+          <t>table-row-actions.md</t>
+        </is>
+      </c>
+      <c r="E568" s="3" t="inlineStr"/>
+      <c r="F568" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/references/README.md</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="D569" s="3" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="E569" s="3" t="inlineStr"/>
+      <c r="F569" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/references/offline-archive.md</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>offline-archive.md</t>
+        </is>
+      </c>
+      <c r="D570" s="3" t="inlineStr">
+        <is>
+          <t>offline-archive.md</t>
+        </is>
+      </c>
+      <c r="E570" s="3" t="inlineStr"/>
+      <c r="F570" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/references/portal-links.md</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>portal-links.md</t>
+        </is>
+      </c>
+      <c r="D571" s="3" t="inlineStr">
+        <is>
+          <t>portal-links.md</t>
+        </is>
+      </c>
+      <c r="E571" s="3" t="inlineStr"/>
+      <c r="F571" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/styles/README.md</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="D572" s="3" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="E572" s="3" t="inlineStr"/>
+      <c r="F572" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/styles/colors.md</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>colors.md</t>
+        </is>
+      </c>
+      <c r="D573" s="3" t="inlineStr">
+        <is>
+          <t>colors.md</t>
+        </is>
+      </c>
+      <c r="E573" s="3" t="inlineStr"/>
+      <c r="F573" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/styles/elevation.md</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>elevation.md</t>
+        </is>
+      </c>
+      <c r="D574" s="3" t="inlineStr">
+        <is>
+          <t>elevation.md</t>
+        </is>
+      </c>
+      <c r="E574" s="3" t="inlineStr"/>
+      <c r="F574" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/styles/grid.md</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>grid.md</t>
+        </is>
+      </c>
+      <c r="D575" s="3" t="inlineStr">
+        <is>
+          <t>grid.md</t>
+        </is>
+      </c>
+      <c r="E575" s="3" t="inlineStr"/>
+      <c r="F575" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G575" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/styles/styles.md</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>styles.md</t>
+        </is>
+      </c>
+      <c r="D576" s="3" t="inlineStr">
+        <is>
+          <t>styles.md</t>
+        </is>
+      </c>
+      <c r="E576" s="3" t="inlineStr"/>
+      <c r="F576" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>AppKit (UI library)</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>docs/appkit4/styles/typography.md</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>typography.md</t>
+        </is>
+      </c>
+      <c r="D577" s="3" t="inlineStr">
+        <is>
+          <t>typography.md</t>
+        </is>
+      </c>
+      <c r="E577" s="3" t="inlineStr"/>
+      <c r="F577" s="4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>Vendor (AppKit 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>.editorconfig</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>.editorconfig</t>
+        </is>
+      </c>
+      <c r="D578" s="3" t="inlineStr">
+        <is>
+          <t>.editorconfig</t>
+        </is>
+      </c>
+      <c r="E578" s="3" t="inlineStr"/>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
           <t>Project</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G566"/>
+  <autoFilter ref="A1:G578"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20236,7 +20672,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>565</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3"/>
@@ -20349,7 +20785,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -20359,7 +20795,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -20412,7 +20848,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22">
@@ -20422,7 +20858,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -20442,7 +20878,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25"/>
@@ -20465,7 +20901,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28">
@@ -20475,7 +20911,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -20485,7 +20921,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
